--- a/_Learn/Packaging.tutorial/OS.11/23H2/Expand/Install/Report/zh-TW.xlsx
+++ b/_Learn/Packaging.tutorial/OS.11/23H2/Expand/Install/Report/zh-TW.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\OneDrive\Documents\_Learn\Packaging.tutorial\OS.11\23H2\Expand\Install\Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A66D6070-CCB8-4B33-97C1-92D867E63107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F4A645-927D-40D6-BDF2-801766CF9CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="27634" windowHeight="16629" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="5" r:id="rId1"/>
@@ -4378,22 +4378,22 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L34"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="8" customWidth="1"/>
-    <col min="2" max="2" width="0.84375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="84.69140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="50.3828125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="20.61328125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="16.69140625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="0.86328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="84.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="50.3984375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="20.59765625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" style="3" customWidth="1"/>
     <col min="7" max="7" width="122" style="3" customWidth="1"/>
-    <col min="8" max="10" width="16.69140625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="16.69140625" style="8" customWidth="1"/>
-    <col min="12" max="12" width="2.69140625" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.15234375" style="1" hidden="1"/>
+    <col min="8" max="10" width="16.6640625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="16.6640625" style="8" customWidth="1"/>
+    <col min="12" max="12" width="2.6640625" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.1328125" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4406,7 +4406,7 @@
       <c r="J1" s="2"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:12" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12" ht="80.2" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="1"/>
       <c r="C2" s="4" t="s">
         <v>263</v>
@@ -4421,7 +4421,7 @@
       <c r="J2" s="2"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="1"/>
       <c r="C3" s="7"/>
       <c r="D3" s="5"/>
@@ -4433,7 +4433,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:12" ht="5.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" ht="5.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -4443,7 +4443,7 @@
       <c r="I4" s="10"/>
       <c r="J4" s="11"/>
     </row>
-    <row r="5" spans="1:12" ht="62.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" ht="62.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B5" s="12"/>
       <c r="C5" s="12" t="s">
         <v>9</v>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="L5" s="8"/>
     </row>
-    <row r="6" spans="1:12" ht="111" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" ht="110.25" x14ac:dyDescent="0.45">
       <c r="B6" s="14"/>
       <c r="C6" s="15" t="s">
         <v>267</v>
@@ -4503,7 +4503,7 @@
       <c r="K6" s="14"/>
       <c r="L6" s="8"/>
     </row>
-    <row r="7" spans="1:12" ht="79.3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" ht="78.75" x14ac:dyDescent="0.45">
       <c r="B7" s="14"/>
       <c r="C7" s="42" t="s">
         <v>264</v>
@@ -4532,7 +4532,7 @@
       <c r="K7" s="43"/>
       <c r="L7" s="8"/>
     </row>
-    <row r="8" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" ht="20.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C8" s="14"/>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
@@ -4542,7 +4542,7 @@
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
     </row>
-    <row r="9" spans="1:12" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:12" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B9" s="17"/>
       <c r="C9" s="18" t="s">
         <v>2</v>
@@ -4551,7 +4551,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:12" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B10" s="20"/>
       <c r="C10" s="21" t="s">
         <v>0</v>
@@ -4566,7 +4566,7 @@
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
     </row>
-    <row r="11" spans="1:12" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:12" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B11" s="22"/>
       <c r="C11" s="21" t="s">
         <v>1</v>
@@ -4581,7 +4581,7 @@
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
     </row>
-    <row r="12" spans="1:12" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="8"/>
@@ -4591,14 +4591,14 @@
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
     </row>
-    <row r="13" spans="1:12" ht="30" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:12" ht="30" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
     </row>
-    <row r="14" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -4609,7 +4609,7 @@
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
     </row>
-    <row r="15" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -4620,7 +4620,7 @@
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
     </row>
-    <row r="16" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -4631,7 +4631,7 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -4642,7 +4642,7 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
     </row>
-    <row r="18" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -4653,7 +4653,7 @@
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -4664,7 +4664,7 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
     </row>
-    <row r="20" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -4675,7 +4675,7 @@
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
     </row>
-    <row r="21" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
@@ -4686,7 +4686,7 @@
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
     </row>
-    <row r="22" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -4697,7 +4697,7 @@
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -4708,7 +4708,7 @@
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
     </row>
-    <row r="24" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
@@ -4719,7 +4719,7 @@
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -4730,7 +4730,7 @@
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
@@ -4741,7 +4741,7 @@
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
@@ -4752,7 +4752,7 @@
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
@@ -4763,7 +4763,7 @@
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
@@ -4774,7 +4774,7 @@
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
@@ -4785,7 +4785,7 @@
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
@@ -4796,7 +4796,7 @@
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
@@ -4807,7 +4807,7 @@
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
@@ -4818,7 +4818,7 @@
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
@@ -4877,29 +4877,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R137"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C2" s="4" t="s">
         <v>257</v>
       </c>
@@ -4907,7 +4907,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -4915,7 +4915,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -4923,7 +4923,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -4931,13 +4931,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -4945,7 +4945,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -4960,7 +4960,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -4974,7 +4974,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -4988,7 +4988,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -5002,7 +5002,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -5016,7 +5016,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -5030,7 +5030,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -5044,7 +5044,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -5058,7 +5058,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -5072,7 +5072,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -5086,7 +5086,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -5100,7 +5100,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -5114,7 +5114,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -5128,7 +5128,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -5142,7 +5142,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -5156,7 +5156,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -5170,7 +5170,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -5184,7 +5184,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -5198,7 +5198,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -5212,7 +5212,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -5226,7 +5226,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -5240,7 +5240,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -5254,7 +5254,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -5268,7 +5268,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -5282,7 +5282,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -5296,7 +5296,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -5310,7 +5310,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -5324,7 +5324,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -5338,7 +5338,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -5352,7 +5352,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -5366,7 +5366,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -5380,7 +5380,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -5394,7 +5394,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -5408,7 +5408,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -5422,7 +5422,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -5436,7 +5436,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -5450,7 +5450,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -5464,7 +5464,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -5478,7 +5478,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -5492,7 +5492,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -5506,7 +5506,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -5520,7 +5520,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -5534,7 +5534,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -5548,7 +5548,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -5562,7 +5562,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -5576,7 +5576,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -5590,7 +5590,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="54" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -5604,7 +5604,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="55" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C55" s="3">
         <v>47</v>
       </c>
@@ -5618,12 +5618,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="57" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C57" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C58" s="34" t="s">
         <v>7</v>
       </c>
@@ -5637,7 +5637,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="59" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C59" s="36">
         <v>1</v>
       </c>
@@ -5651,7 +5651,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C60" s="39">
         <v>2</v>
       </c>
@@ -5665,7 +5665,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="61" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C61" s="36">
         <v>3</v>
       </c>
@@ -5679,7 +5679,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="62" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C62" s="39">
         <v>4</v>
       </c>
@@ -5693,7 +5693,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C63" s="36">
         <v>5</v>
       </c>
@@ -5707,7 +5707,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C64" s="39">
         <v>6</v>
       </c>
@@ -5721,7 +5721,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="65" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C65" s="36">
         <v>7</v>
       </c>
@@ -5735,7 +5735,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="66" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C66" s="39">
         <v>8</v>
       </c>
@@ -5749,7 +5749,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="67" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C67" s="36">
         <v>9</v>
       </c>
@@ -5763,7 +5763,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="68" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C68" s="39">
         <v>10</v>
       </c>
@@ -5777,7 +5777,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="69" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C69" s="36">
         <v>11</v>
       </c>
@@ -5791,7 +5791,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="70" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C70" s="39">
         <v>12</v>
       </c>
@@ -5805,7 +5805,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="71" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C71" s="36">
         <v>13</v>
       </c>
@@ -5819,7 +5819,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="72" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C72" s="39">
         <v>14</v>
       </c>
@@ -5833,7 +5833,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="73" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C73" s="36">
         <v>15</v>
       </c>
@@ -5847,7 +5847,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="74" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C74" s="39">
         <v>16</v>
       </c>
@@ -5861,7 +5861,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="75" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C75" s="36">
         <v>17</v>
       </c>
@@ -5875,7 +5875,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="76" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C76" s="39">
         <v>18</v>
       </c>
@@ -5889,7 +5889,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="77" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C77" s="36">
         <v>19</v>
       </c>
@@ -5903,7 +5903,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="78" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C78" s="39">
         <v>20</v>
       </c>
@@ -5917,7 +5917,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="79" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C79" s="36">
         <v>21</v>
       </c>
@@ -5931,7 +5931,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="80" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C80" s="39">
         <v>22</v>
       </c>
@@ -5945,7 +5945,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="81" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C81" s="36">
         <v>23</v>
       </c>
@@ -5959,7 +5959,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="82" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C82" s="39">
         <v>24</v>
       </c>
@@ -5973,7 +5973,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="83" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C83" s="36">
         <v>25</v>
       </c>
@@ -5987,7 +5987,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="84" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C84" s="39">
         <v>26</v>
       </c>
@@ -6001,7 +6001,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="85" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C85" s="36">
         <v>27</v>
       </c>
@@ -6015,7 +6015,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="86" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C86" s="39">
         <v>28</v>
       </c>
@@ -6029,7 +6029,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="87" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C87" s="36">
         <v>29</v>
       </c>
@@ -6043,7 +6043,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="88" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C88" s="39">
         <v>30</v>
       </c>
@@ -6057,7 +6057,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="89" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C89" s="36">
         <v>31</v>
       </c>
@@ -6071,7 +6071,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="90" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C90" s="39">
         <v>32</v>
       </c>
@@ -6085,7 +6085,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="91" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C91" s="36">
         <v>33</v>
       </c>
@@ -6099,7 +6099,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="92" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C92" s="39">
         <v>34</v>
       </c>
@@ -6113,7 +6113,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="93" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C93" s="36">
         <v>35</v>
       </c>
@@ -6127,7 +6127,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="94" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C94" s="39">
         <v>36</v>
       </c>
@@ -6141,7 +6141,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="95" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C95" s="36">
         <v>37</v>
       </c>
@@ -6155,7 +6155,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="96" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C96" s="39">
         <v>38</v>
       </c>
@@ -6169,7 +6169,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="97" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C97" s="36">
         <v>39</v>
       </c>
@@ -6183,7 +6183,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="98" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C98" s="39">
         <v>40</v>
       </c>
@@ -6197,7 +6197,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="99" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C99" s="36">
         <v>41</v>
       </c>
@@ -6211,7 +6211,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="100" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C100" s="39">
         <v>42</v>
       </c>
@@ -6225,7 +6225,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="101" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C101" s="36">
         <v>43</v>
       </c>
@@ -6239,7 +6239,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="102" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C102" s="39">
         <v>44</v>
       </c>
@@ -6253,7 +6253,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="103" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C103" s="36">
         <v>45</v>
       </c>
@@ -6267,7 +6267,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="104" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C104" s="39">
         <v>46</v>
       </c>
@@ -6281,7 +6281,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="105" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C105" s="36">
         <v>47</v>
       </c>
@@ -6295,7 +6295,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="106" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C106" s="39">
         <v>48</v>
       </c>
@@ -6309,7 +6309,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="107" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C107" s="36">
         <v>49</v>
       </c>
@@ -6323,7 +6323,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="108" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C108" s="39">
         <v>50</v>
       </c>
@@ -6337,7 +6337,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="109" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C109" s="36">
         <v>51</v>
       </c>
@@ -6351,7 +6351,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="110" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C110" s="39">
         <v>52</v>
       </c>
@@ -6365,7 +6365,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="111" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C111" s="36">
         <v>53</v>
       </c>
@@ -6379,7 +6379,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="112" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C112" s="39">
         <v>54</v>
       </c>
@@ -6393,7 +6393,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="113" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C113" s="36">
         <v>55</v>
       </c>
@@ -6407,7 +6407,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="114" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C114" s="39">
         <v>56</v>
       </c>
@@ -6421,7 +6421,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="115" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C115" s="36">
         <v>57</v>
       </c>
@@ -6435,7 +6435,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="116" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C116" s="39">
         <v>58</v>
       </c>
@@ -6449,7 +6449,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="117" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C117" s="36">
         <v>59</v>
       </c>
@@ -6463,7 +6463,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="118" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C118" s="39">
         <v>60</v>
       </c>
@@ -6477,7 +6477,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="119" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C119" s="36">
         <v>61</v>
       </c>
@@ -6491,7 +6491,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="120" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C120" s="39">
         <v>62</v>
       </c>
@@ -6505,7 +6505,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="121" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C121" s="36">
         <v>63</v>
       </c>
@@ -6519,7 +6519,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="122" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C122" s="39">
         <v>64</v>
       </c>
@@ -6533,7 +6533,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="123" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C123" s="36">
         <v>65</v>
       </c>
@@ -6547,7 +6547,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="124" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C124" s="39">
         <v>66</v>
       </c>
@@ -6561,7 +6561,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="125" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C125" s="36">
         <v>67</v>
       </c>
@@ -6575,7 +6575,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="126" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C126" s="39">
         <v>68</v>
       </c>
@@ -6589,7 +6589,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="127" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C127" s="36">
         <v>69</v>
       </c>
@@ -6603,7 +6603,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="128" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C128" s="39">
         <v>70</v>
       </c>
@@ -6617,7 +6617,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="129" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C129" s="36">
         <v>71</v>
       </c>
@@ -6631,7 +6631,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="130" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C130" s="39">
         <v>72</v>
       </c>
@@ -6645,7 +6645,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="131" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C131" s="36">
         <v>73</v>
       </c>
@@ -6659,7 +6659,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="132" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C132" s="39">
         <v>74</v>
       </c>
@@ -6673,7 +6673,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="133" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C133" s="36">
         <v>75</v>
       </c>
@@ -6687,7 +6687,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="134" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C134" s="39">
         <v>76</v>
       </c>
@@ -6701,7 +6701,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="135" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C135" s="36">
         <v>77</v>
       </c>
@@ -6715,7 +6715,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="136" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C136" s="39">
         <v>78</v>
       </c>
@@ -6729,7 +6729,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="137" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C137" s="3">
         <v>79</v>
       </c>
@@ -6766,29 +6766,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R138"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="13" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="14" max="15" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="14" max="15" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="16" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C2" s="4" t="s">
         <v>258</v>
       </c>
@@ -6796,7 +6796,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -6804,7 +6804,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -6812,7 +6812,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -6820,13 +6820,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -6834,7 +6834,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -6849,7 +6849,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -6863,7 +6863,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -6877,7 +6877,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -6891,7 +6891,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -6905,7 +6905,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -6919,7 +6919,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -6933,7 +6933,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -6947,7 +6947,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -6961,7 +6961,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -6975,7 +6975,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -6989,7 +6989,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -7003,7 +7003,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -7017,7 +7017,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -7031,7 +7031,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -7045,7 +7045,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -7059,7 +7059,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -7073,7 +7073,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -7087,7 +7087,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -7101,7 +7101,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -7115,7 +7115,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -7129,7 +7129,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -7143,7 +7143,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -7157,7 +7157,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -7171,7 +7171,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -7185,7 +7185,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -7199,7 +7199,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -7213,7 +7213,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -7227,7 +7227,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -7241,7 +7241,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -7255,7 +7255,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -7269,7 +7269,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -7283,7 +7283,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -7297,7 +7297,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -7311,7 +7311,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -7325,7 +7325,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -7339,7 +7339,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -7353,7 +7353,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -7367,7 +7367,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -7381,7 +7381,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -7395,7 +7395,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -7409,7 +7409,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -7423,7 +7423,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -7437,7 +7437,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -7451,7 +7451,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -7465,7 +7465,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -7479,7 +7479,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -7493,12 +7493,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C57" s="34" t="s">
         <v>7</v>
       </c>
@@ -7512,7 +7512,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C58" s="36">
         <v>1</v>
       </c>
@@ -7526,7 +7526,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C59" s="39">
         <v>2</v>
       </c>
@@ -7540,7 +7540,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C60" s="36">
         <v>3</v>
       </c>
@@ -7554,7 +7554,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C61" s="39">
         <v>4</v>
       </c>
@@ -7568,7 +7568,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C62" s="36">
         <v>5</v>
       </c>
@@ -7582,7 +7582,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C63" s="39">
         <v>6</v>
       </c>
@@ -7596,7 +7596,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="30"/>
       <c r="B64" s="28"/>
       <c r="C64" s="36">
@@ -7617,7 +7617,7 @@
       <c r="J64" s="30"/>
       <c r="K64" s="30"/>
     </row>
-    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="30"/>
       <c r="B65" s="28"/>
       <c r="C65" s="39">
@@ -7638,7 +7638,7 @@
       <c r="J65" s="30"/>
       <c r="K65" s="30"/>
     </row>
-    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="30"/>
       <c r="B66" s="28"/>
       <c r="C66" s="36">
@@ -7659,7 +7659,7 @@
       <c r="J66" s="30"/>
       <c r="K66" s="30"/>
     </row>
-    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="30"/>
       <c r="B67" s="28"/>
       <c r="C67" s="39">
@@ -7680,7 +7680,7 @@
       <c r="J67" s="30"/>
       <c r="K67" s="30"/>
     </row>
-    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="30"/>
       <c r="B68" s="28"/>
       <c r="C68" s="36">
@@ -7701,7 +7701,7 @@
       <c r="J68" s="30"/>
       <c r="K68" s="30"/>
     </row>
-    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="30"/>
       <c r="B69" s="28"/>
       <c r="C69" s="39">
@@ -7722,7 +7722,7 @@
       <c r="J69" s="30"/>
       <c r="K69" s="30"/>
     </row>
-    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="30"/>
       <c r="B70" s="28"/>
       <c r="C70" s="36">
@@ -7743,7 +7743,7 @@
       <c r="J70" s="30"/>
       <c r="K70" s="30"/>
     </row>
-    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="30"/>
       <c r="B71" s="28"/>
       <c r="C71" s="39">
@@ -7764,7 +7764,7 @@
       <c r="J71" s="30"/>
       <c r="K71" s="30"/>
     </row>
-    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="30"/>
       <c r="B72" s="28"/>
       <c r="C72" s="36">
@@ -7785,7 +7785,7 @@
       <c r="J72" s="30"/>
       <c r="K72" s="30"/>
     </row>
-    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="30"/>
       <c r="B73" s="28"/>
       <c r="C73" s="39">
@@ -7806,7 +7806,7 @@
       <c r="J73" s="30"/>
       <c r="K73" s="30"/>
     </row>
-    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="30"/>
       <c r="B74" s="28"/>
       <c r="C74" s="36">
@@ -7827,7 +7827,7 @@
       <c r="J74" s="30"/>
       <c r="K74" s="30"/>
     </row>
-    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="30"/>
       <c r="B75" s="28"/>
       <c r="C75" s="39">
@@ -7848,7 +7848,7 @@
       <c r="J75" s="30"/>
       <c r="K75" s="30"/>
     </row>
-    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="30"/>
       <c r="B76" s="28"/>
       <c r="C76" s="36">
@@ -7869,7 +7869,7 @@
       <c r="J76" s="30"/>
       <c r="K76" s="30"/>
     </row>
-    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="30"/>
       <c r="B77" s="28"/>
       <c r="C77" s="39">
@@ -7890,7 +7890,7 @@
       <c r="J77" s="30"/>
       <c r="K77" s="30"/>
     </row>
-    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="30"/>
       <c r="B78" s="28"/>
       <c r="C78" s="36">
@@ -7911,7 +7911,7 @@
       <c r="J78" s="30"/>
       <c r="K78" s="30"/>
     </row>
-    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="30"/>
       <c r="B79" s="28"/>
       <c r="C79" s="39">
@@ -7932,7 +7932,7 @@
       <c r="J79" s="30"/>
       <c r="K79" s="30"/>
     </row>
-    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="30"/>
       <c r="B80" s="28"/>
       <c r="C80" s="36">
@@ -7953,7 +7953,7 @@
       <c r="J80" s="30"/>
       <c r="K80" s="30"/>
     </row>
-    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" s="30"/>
       <c r="B81" s="28"/>
       <c r="C81" s="39">
@@ -7974,7 +7974,7 @@
       <c r="J81" s="30"/>
       <c r="K81" s="30"/>
     </row>
-    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="30"/>
       <c r="B82" s="28"/>
       <c r="C82" s="36">
@@ -7995,7 +7995,7 @@
       <c r="J82" s="30"/>
       <c r="K82" s="30"/>
     </row>
-    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="30"/>
       <c r="B83" s="28"/>
       <c r="C83" s="39">
@@ -8016,7 +8016,7 @@
       <c r="J83" s="30"/>
       <c r="K83" s="30"/>
     </row>
-    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="30"/>
       <c r="B84" s="28"/>
       <c r="C84" s="36">
@@ -8037,7 +8037,7 @@
       <c r="J84" s="30"/>
       <c r="K84" s="30"/>
     </row>
-    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="30"/>
       <c r="B85" s="28"/>
       <c r="C85" s="39">
@@ -8058,7 +8058,7 @@
       <c r="J85" s="30"/>
       <c r="K85" s="30"/>
     </row>
-    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="30"/>
       <c r="B86" s="28"/>
       <c r="C86" s="36">
@@ -8079,7 +8079,7 @@
       <c r="J86" s="30"/>
       <c r="K86" s="30"/>
     </row>
-    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" s="30"/>
       <c r="B87" s="28"/>
       <c r="C87" s="39">
@@ -8100,7 +8100,7 @@
       <c r="J87" s="30"/>
       <c r="K87" s="30"/>
     </row>
-    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="30"/>
       <c r="B88" s="28"/>
       <c r="C88" s="36">
@@ -8121,7 +8121,7 @@
       <c r="J88" s="30"/>
       <c r="K88" s="30"/>
     </row>
-    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="30"/>
       <c r="B89" s="28"/>
       <c r="C89" s="39">
@@ -8142,7 +8142,7 @@
       <c r="J89" s="30"/>
       <c r="K89" s="30"/>
     </row>
-    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="30"/>
       <c r="B90" s="28"/>
       <c r="C90" s="36">
@@ -8163,7 +8163,7 @@
       <c r="J90" s="30"/>
       <c r="K90" s="30"/>
     </row>
-    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A91" s="30"/>
       <c r="B91" s="28"/>
       <c r="C91" s="39">
@@ -8184,7 +8184,7 @@
       <c r="J91" s="30"/>
       <c r="K91" s="30"/>
     </row>
-    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" s="30"/>
       <c r="B92" s="28"/>
       <c r="C92" s="36">
@@ -8205,7 +8205,7 @@
       <c r="J92" s="30"/>
       <c r="K92" s="30"/>
     </row>
-    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A93" s="30"/>
       <c r="B93" s="28"/>
       <c r="C93" s="39">
@@ -8226,7 +8226,7 @@
       <c r="J93" s="30"/>
       <c r="K93" s="30"/>
     </row>
-    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A94" s="30"/>
       <c r="B94" s="28"/>
       <c r="C94" s="36">
@@ -8247,7 +8247,7 @@
       <c r="J94" s="30"/>
       <c r="K94" s="30"/>
     </row>
-    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A95" s="30"/>
       <c r="B95" s="28"/>
       <c r="C95" s="39">
@@ -8268,7 +8268,7 @@
       <c r="J95" s="30"/>
       <c r="K95" s="30"/>
     </row>
-    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" s="30"/>
       <c r="B96" s="28"/>
       <c r="C96" s="36">
@@ -8289,7 +8289,7 @@
       <c r="J96" s="30"/>
       <c r="K96" s="30"/>
     </row>
-    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" s="30"/>
       <c r="B97" s="28"/>
       <c r="C97" s="39">
@@ -8310,7 +8310,7 @@
       <c r="J97" s="30"/>
       <c r="K97" s="30"/>
     </row>
-    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A98" s="30"/>
       <c r="B98" s="28"/>
       <c r="C98" s="36">
@@ -8331,7 +8331,7 @@
       <c r="J98" s="30"/>
       <c r="K98" s="30"/>
     </row>
-    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" s="30"/>
       <c r="B99" s="28"/>
       <c r="C99" s="39">
@@ -8352,7 +8352,7 @@
       <c r="J99" s="30"/>
       <c r="K99" s="30"/>
     </row>
-    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="30"/>
       <c r="B100" s="28"/>
       <c r="C100" s="36">
@@ -8373,7 +8373,7 @@
       <c r="J100" s="30"/>
       <c r="K100" s="30"/>
     </row>
-    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="30"/>
       <c r="B101" s="28"/>
       <c r="C101" s="39">
@@ -8394,7 +8394,7 @@
       <c r="J101" s="30"/>
       <c r="K101" s="30"/>
     </row>
-    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="30"/>
       <c r="B102" s="28"/>
       <c r="C102" s="36">
@@ -8415,7 +8415,7 @@
       <c r="J102" s="30"/>
       <c r="K102" s="30"/>
     </row>
-    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A103" s="30"/>
       <c r="B103" s="28"/>
       <c r="C103" s="39">
@@ -8436,7 +8436,7 @@
       <c r="J103" s="30"/>
       <c r="K103" s="30"/>
     </row>
-    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A104" s="30"/>
       <c r="B104" s="28"/>
       <c r="C104" s="36">
@@ -8457,7 +8457,7 @@
       <c r="J104" s="30"/>
       <c r="K104" s="30"/>
     </row>
-    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A105" s="30"/>
       <c r="B105" s="28"/>
       <c r="C105" s="39">
@@ -8478,7 +8478,7 @@
       <c r="J105" s="30"/>
       <c r="K105" s="30"/>
     </row>
-    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A106" s="30"/>
       <c r="B106" s="28"/>
       <c r="C106" s="36">
@@ -8499,7 +8499,7 @@
       <c r="J106" s="30"/>
       <c r="K106" s="30"/>
     </row>
-    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" s="30"/>
       <c r="B107" s="28"/>
       <c r="C107" s="39">
@@ -8520,7 +8520,7 @@
       <c r="J107" s="30"/>
       <c r="K107" s="30"/>
     </row>
-    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" s="30"/>
       <c r="B108" s="28"/>
       <c r="C108" s="36">
@@ -8541,7 +8541,7 @@
       <c r="J108" s="30"/>
       <c r="K108" s="30"/>
     </row>
-    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="30"/>
       <c r="B109" s="28"/>
       <c r="C109" s="39">
@@ -8562,7 +8562,7 @@
       <c r="J109" s="30"/>
       <c r="K109" s="30"/>
     </row>
-    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A110" s="30"/>
       <c r="B110" s="28"/>
       <c r="C110" s="36">
@@ -8583,7 +8583,7 @@
       <c r="J110" s="30"/>
       <c r="K110" s="30"/>
     </row>
-    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A111" s="30"/>
       <c r="B111" s="28"/>
       <c r="C111" s="39">
@@ -8604,7 +8604,7 @@
       <c r="J111" s="30"/>
       <c r="K111" s="30"/>
     </row>
-    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A112" s="30"/>
       <c r="B112" s="28"/>
       <c r="C112" s="36">
@@ -8625,7 +8625,7 @@
       <c r="J112" s="30"/>
       <c r="K112" s="30"/>
     </row>
-    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="30"/>
       <c r="B113" s="28"/>
       <c r="C113" s="39">
@@ -8646,7 +8646,7 @@
       <c r="J113" s="30"/>
       <c r="K113" s="30"/>
     </row>
-    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A114" s="30"/>
       <c r="B114" s="28"/>
       <c r="C114" s="36">
@@ -8667,7 +8667,7 @@
       <c r="J114" s="30"/>
       <c r="K114" s="30"/>
     </row>
-    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A115" s="30"/>
       <c r="B115" s="28"/>
       <c r="C115" s="39">
@@ -8688,7 +8688,7 @@
       <c r="J115" s="30"/>
       <c r="K115" s="30"/>
     </row>
-    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" s="30"/>
       <c r="B116" s="28"/>
       <c r="C116" s="36">
@@ -8709,7 +8709,7 @@
       <c r="J116" s="30"/>
       <c r="K116" s="30"/>
     </row>
-    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A117" s="30"/>
       <c r="B117" s="28"/>
       <c r="C117" s="39">
@@ -8730,7 +8730,7 @@
       <c r="J117" s="30"/>
       <c r="K117" s="30"/>
     </row>
-    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A118" s="30"/>
       <c r="B118" s="28"/>
       <c r="C118" s="36">
@@ -8751,7 +8751,7 @@
       <c r="J118" s="30"/>
       <c r="K118" s="30"/>
     </row>
-    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A119" s="30"/>
       <c r="B119" s="28"/>
       <c r="C119" s="39">
@@ -8772,7 +8772,7 @@
       <c r="J119" s="30"/>
       <c r="K119" s="30"/>
     </row>
-    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A120" s="30"/>
       <c r="B120" s="28"/>
       <c r="C120" s="36">
@@ -8793,7 +8793,7 @@
       <c r="J120" s="30"/>
       <c r="K120" s="30"/>
     </row>
-    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A121" s="30"/>
       <c r="B121" s="28"/>
       <c r="C121" s="39">
@@ -8814,7 +8814,7 @@
       <c r="J121" s="30"/>
       <c r="K121" s="30"/>
     </row>
-    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A122" s="30"/>
       <c r="B122" s="28"/>
       <c r="C122" s="36">
@@ -8835,7 +8835,7 @@
       <c r="J122" s="30"/>
       <c r="K122" s="30"/>
     </row>
-    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A123" s="30"/>
       <c r="B123" s="28"/>
       <c r="C123" s="39">
@@ -8856,7 +8856,7 @@
       <c r="J123" s="30"/>
       <c r="K123" s="30"/>
     </row>
-    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A124" s="30"/>
       <c r="B124" s="28"/>
       <c r="C124" s="36">
@@ -8877,7 +8877,7 @@
       <c r="J124" s="30"/>
       <c r="K124" s="30"/>
     </row>
-    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A125" s="30"/>
       <c r="B125" s="28"/>
       <c r="C125" s="39">
@@ -8898,7 +8898,7 @@
       <c r="J125" s="30"/>
       <c r="K125" s="30"/>
     </row>
-    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A126" s="30"/>
       <c r="B126" s="28"/>
       <c r="C126" s="36">
@@ -8919,7 +8919,7 @@
       <c r="J126" s="30"/>
       <c r="K126" s="30"/>
     </row>
-    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A127" s="30"/>
       <c r="B127" s="28"/>
       <c r="C127" s="39">
@@ -8940,7 +8940,7 @@
       <c r="J127" s="30"/>
       <c r="K127" s="30"/>
     </row>
-    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A128" s="30"/>
       <c r="B128" s="28"/>
       <c r="C128" s="36">
@@ -8961,7 +8961,7 @@
       <c r="J128" s="30"/>
       <c r="K128" s="30"/>
     </row>
-    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A129" s="30"/>
       <c r="B129" s="28"/>
       <c r="C129" s="39">
@@ -8982,7 +8982,7 @@
       <c r="J129" s="30"/>
       <c r="K129" s="30"/>
     </row>
-    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A130" s="30"/>
       <c r="B130" s="28"/>
       <c r="C130" s="36">
@@ -9003,7 +9003,7 @@
       <c r="J130" s="30"/>
       <c r="K130" s="30"/>
     </row>
-    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A131" s="30"/>
       <c r="B131" s="28"/>
       <c r="C131" s="39">
@@ -9024,7 +9024,7 @@
       <c r="J131" s="30"/>
       <c r="K131" s="30"/>
     </row>
-    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A132" s="30"/>
       <c r="B132" s="28"/>
       <c r="C132" s="36">
@@ -9045,7 +9045,7 @@
       <c r="J132" s="30"/>
       <c r="K132" s="30"/>
     </row>
-    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C133" s="39">
         <v>76</v>
       </c>
@@ -9059,7 +9059,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C134" s="36">
         <v>77</v>
       </c>
@@ -9073,7 +9073,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C135" s="39">
         <v>78</v>
       </c>
@@ -9087,7 +9087,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C136" s="36">
         <v>79</v>
       </c>
@@ -9101,7 +9101,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C137" s="39">
         <v>80</v>
       </c>
@@ -9115,7 +9115,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="138" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C138" s="36">
         <v>81</v>
       </c>
@@ -9152,29 +9152,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R138"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C2" s="4" t="s">
         <v>259</v>
       </c>
@@ -9182,7 +9182,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -9190,7 +9190,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -9198,7 +9198,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -9206,13 +9206,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -9220,7 +9220,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -9235,7 +9235,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -9249,7 +9249,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -9263,7 +9263,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -9277,7 +9277,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -9291,7 +9291,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -9305,7 +9305,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -9319,7 +9319,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -9333,7 +9333,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -9347,7 +9347,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -9361,7 +9361,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -9375,7 +9375,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -9389,7 +9389,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -9403,7 +9403,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -9417,7 +9417,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -9431,7 +9431,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -9445,7 +9445,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -9459,7 +9459,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -9473,7 +9473,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -9487,7 +9487,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -9501,7 +9501,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -9515,7 +9515,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -9529,7 +9529,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -9543,7 +9543,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -9557,7 +9557,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -9571,7 +9571,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -9585,7 +9585,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -9599,7 +9599,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -9613,7 +9613,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -9627,7 +9627,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -9641,7 +9641,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -9655,7 +9655,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -9669,7 +9669,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -9683,7 +9683,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -9697,7 +9697,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -9711,7 +9711,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -9725,7 +9725,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -9739,7 +9739,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -9753,7 +9753,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -9767,7 +9767,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -9781,7 +9781,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -9795,7 +9795,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -9809,7 +9809,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -9823,7 +9823,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -9837,7 +9837,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -9851,7 +9851,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -9865,7 +9865,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -9879,12 +9879,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C57" s="34" t="s">
         <v>7</v>
       </c>
@@ -9898,7 +9898,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C58" s="36">
         <v>1</v>
       </c>
@@ -9912,7 +9912,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C59" s="39">
         <v>2</v>
       </c>
@@ -9926,7 +9926,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C60" s="36">
         <v>3</v>
       </c>
@@ -9940,7 +9940,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C61" s="39">
         <v>4</v>
       </c>
@@ -9954,7 +9954,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C62" s="36">
         <v>5</v>
       </c>
@@ -9968,7 +9968,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C63" s="39">
         <v>6</v>
       </c>
@@ -9982,7 +9982,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="30"/>
       <c r="B64" s="28"/>
       <c r="C64" s="36">
@@ -10003,7 +10003,7 @@
       <c r="J64" s="30"/>
       <c r="K64" s="30"/>
     </row>
-    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="30"/>
       <c r="B65" s="28"/>
       <c r="C65" s="39">
@@ -10024,7 +10024,7 @@
       <c r="J65" s="30"/>
       <c r="K65" s="30"/>
     </row>
-    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="30"/>
       <c r="B66" s="28"/>
       <c r="C66" s="36">
@@ -10045,7 +10045,7 @@
       <c r="J66" s="30"/>
       <c r="K66" s="30"/>
     </row>
-    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="30"/>
       <c r="B67" s="28"/>
       <c r="C67" s="39">
@@ -10066,7 +10066,7 @@
       <c r="J67" s="30"/>
       <c r="K67" s="30"/>
     </row>
-    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="30"/>
       <c r="B68" s="28"/>
       <c r="C68" s="36">
@@ -10087,7 +10087,7 @@
       <c r="J68" s="30"/>
       <c r="K68" s="30"/>
     </row>
-    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="30"/>
       <c r="B69" s="28"/>
       <c r="C69" s="39">
@@ -10108,7 +10108,7 @@
       <c r="J69" s="30"/>
       <c r="K69" s="30"/>
     </row>
-    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="30"/>
       <c r="B70" s="28"/>
       <c r="C70" s="36">
@@ -10129,7 +10129,7 @@
       <c r="J70" s="30"/>
       <c r="K70" s="30"/>
     </row>
-    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="30"/>
       <c r="B71" s="28"/>
       <c r="C71" s="39">
@@ -10150,7 +10150,7 @@
       <c r="J71" s="30"/>
       <c r="K71" s="30"/>
     </row>
-    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="30"/>
       <c r="B72" s="28"/>
       <c r="C72" s="36">
@@ -10171,7 +10171,7 @@
       <c r="J72" s="30"/>
       <c r="K72" s="30"/>
     </row>
-    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="30"/>
       <c r="B73" s="28"/>
       <c r="C73" s="39">
@@ -10192,7 +10192,7 @@
       <c r="J73" s="30"/>
       <c r="K73" s="30"/>
     </row>
-    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="30"/>
       <c r="B74" s="28"/>
       <c r="C74" s="36">
@@ -10213,7 +10213,7 @@
       <c r="J74" s="30"/>
       <c r="K74" s="30"/>
     </row>
-    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="30"/>
       <c r="B75" s="28"/>
       <c r="C75" s="39">
@@ -10234,7 +10234,7 @@
       <c r="J75" s="30"/>
       <c r="K75" s="30"/>
     </row>
-    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="30"/>
       <c r="B76" s="28"/>
       <c r="C76" s="36">
@@ -10255,7 +10255,7 @@
       <c r="J76" s="30"/>
       <c r="K76" s="30"/>
     </row>
-    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="30"/>
       <c r="B77" s="28"/>
       <c r="C77" s="39">
@@ -10276,7 +10276,7 @@
       <c r="J77" s="30"/>
       <c r="K77" s="30"/>
     </row>
-    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="30"/>
       <c r="B78" s="28"/>
       <c r="C78" s="36">
@@ -10297,7 +10297,7 @@
       <c r="J78" s="30"/>
       <c r="K78" s="30"/>
     </row>
-    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="30"/>
       <c r="B79" s="28"/>
       <c r="C79" s="39">
@@ -10318,7 +10318,7 @@
       <c r="J79" s="30"/>
       <c r="K79" s="30"/>
     </row>
-    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="30"/>
       <c r="B80" s="28"/>
       <c r="C80" s="36">
@@ -10339,7 +10339,7 @@
       <c r="J80" s="30"/>
       <c r="K80" s="30"/>
     </row>
-    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" s="30"/>
       <c r="B81" s="28"/>
       <c r="C81" s="39">
@@ -10360,7 +10360,7 @@
       <c r="J81" s="30"/>
       <c r="K81" s="30"/>
     </row>
-    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="30"/>
       <c r="B82" s="28"/>
       <c r="C82" s="36">
@@ -10381,7 +10381,7 @@
       <c r="J82" s="30"/>
       <c r="K82" s="30"/>
     </row>
-    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="30"/>
       <c r="B83" s="28"/>
       <c r="C83" s="39">
@@ -10402,7 +10402,7 @@
       <c r="J83" s="30"/>
       <c r="K83" s="30"/>
     </row>
-    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="30"/>
       <c r="B84" s="28"/>
       <c r="C84" s="36">
@@ -10423,7 +10423,7 @@
       <c r="J84" s="30"/>
       <c r="K84" s="30"/>
     </row>
-    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="30"/>
       <c r="B85" s="28"/>
       <c r="C85" s="39">
@@ -10444,7 +10444,7 @@
       <c r="J85" s="30"/>
       <c r="K85" s="30"/>
     </row>
-    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="30"/>
       <c r="B86" s="28"/>
       <c r="C86" s="36">
@@ -10465,7 +10465,7 @@
       <c r="J86" s="30"/>
       <c r="K86" s="30"/>
     </row>
-    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" s="30"/>
       <c r="B87" s="28"/>
       <c r="C87" s="39">
@@ -10486,7 +10486,7 @@
       <c r="J87" s="30"/>
       <c r="K87" s="30"/>
     </row>
-    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="30"/>
       <c r="B88" s="28"/>
       <c r="C88" s="36">
@@ -10507,7 +10507,7 @@
       <c r="J88" s="30"/>
       <c r="K88" s="30"/>
     </row>
-    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="30"/>
       <c r="B89" s="28"/>
       <c r="C89" s="39">
@@ -10528,7 +10528,7 @@
       <c r="J89" s="30"/>
       <c r="K89" s="30"/>
     </row>
-    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="30"/>
       <c r="B90" s="28"/>
       <c r="C90" s="36">
@@ -10549,7 +10549,7 @@
       <c r="J90" s="30"/>
       <c r="K90" s="30"/>
     </row>
-    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A91" s="30"/>
       <c r="B91" s="28"/>
       <c r="C91" s="39">
@@ -10570,7 +10570,7 @@
       <c r="J91" s="30"/>
       <c r="K91" s="30"/>
     </row>
-    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" s="30"/>
       <c r="B92" s="28"/>
       <c r="C92" s="36">
@@ -10591,7 +10591,7 @@
       <c r="J92" s="30"/>
       <c r="K92" s="30"/>
     </row>
-    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A93" s="30"/>
       <c r="B93" s="28"/>
       <c r="C93" s="39">
@@ -10612,7 +10612,7 @@
       <c r="J93" s="30"/>
       <c r="K93" s="30"/>
     </row>
-    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A94" s="30"/>
       <c r="B94" s="28"/>
       <c r="C94" s="36">
@@ -10633,7 +10633,7 @@
       <c r="J94" s="30"/>
       <c r="K94" s="30"/>
     </row>
-    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A95" s="30"/>
       <c r="B95" s="28"/>
       <c r="C95" s="39">
@@ -10654,7 +10654,7 @@
       <c r="J95" s="30"/>
       <c r="K95" s="30"/>
     </row>
-    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" s="30"/>
       <c r="B96" s="28"/>
       <c r="C96" s="36">
@@ -10675,7 +10675,7 @@
       <c r="J96" s="30"/>
       <c r="K96" s="30"/>
     </row>
-    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" s="30"/>
       <c r="B97" s="28"/>
       <c r="C97" s="39">
@@ -10696,7 +10696,7 @@
       <c r="J97" s="30"/>
       <c r="K97" s="30"/>
     </row>
-    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A98" s="30"/>
       <c r="B98" s="28"/>
       <c r="C98" s="36">
@@ -10717,7 +10717,7 @@
       <c r="J98" s="30"/>
       <c r="K98" s="30"/>
     </row>
-    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" s="30"/>
       <c r="B99" s="28"/>
       <c r="C99" s="39">
@@ -10738,7 +10738,7 @@
       <c r="J99" s="30"/>
       <c r="K99" s="30"/>
     </row>
-    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="30"/>
       <c r="B100" s="28"/>
       <c r="C100" s="36">
@@ -10759,7 +10759,7 @@
       <c r="J100" s="30"/>
       <c r="K100" s="30"/>
     </row>
-    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="30"/>
       <c r="B101" s="28"/>
       <c r="C101" s="39">
@@ -10780,7 +10780,7 @@
       <c r="J101" s="30"/>
       <c r="K101" s="30"/>
     </row>
-    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="30"/>
       <c r="B102" s="28"/>
       <c r="C102" s="36">
@@ -10801,7 +10801,7 @@
       <c r="J102" s="30"/>
       <c r="K102" s="30"/>
     </row>
-    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A103" s="30"/>
       <c r="B103" s="28"/>
       <c r="C103" s="39">
@@ -10822,7 +10822,7 @@
       <c r="J103" s="30"/>
       <c r="K103" s="30"/>
     </row>
-    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A104" s="30"/>
       <c r="B104" s="28"/>
       <c r="C104" s="36">
@@ -10843,7 +10843,7 @@
       <c r="J104" s="30"/>
       <c r="K104" s="30"/>
     </row>
-    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A105" s="30"/>
       <c r="B105" s="28"/>
       <c r="C105" s="39">
@@ -10864,7 +10864,7 @@
       <c r="J105" s="30"/>
       <c r="K105" s="30"/>
     </row>
-    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A106" s="30"/>
       <c r="B106" s="28"/>
       <c r="C106" s="36">
@@ -10885,7 +10885,7 @@
       <c r="J106" s="30"/>
       <c r="K106" s="30"/>
     </row>
-    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" s="30"/>
       <c r="B107" s="28"/>
       <c r="C107" s="39">
@@ -10906,7 +10906,7 @@
       <c r="J107" s="30"/>
       <c r="K107" s="30"/>
     </row>
-    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" s="30"/>
       <c r="B108" s="28"/>
       <c r="C108" s="36">
@@ -10927,7 +10927,7 @@
       <c r="J108" s="30"/>
       <c r="K108" s="30"/>
     </row>
-    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="30"/>
       <c r="B109" s="28"/>
       <c r="C109" s="39">
@@ -10948,7 +10948,7 @@
       <c r="J109" s="30"/>
       <c r="K109" s="30"/>
     </row>
-    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A110" s="30"/>
       <c r="B110" s="28"/>
       <c r="C110" s="36">
@@ -10969,7 +10969,7 @@
       <c r="J110" s="30"/>
       <c r="K110" s="30"/>
     </row>
-    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A111" s="30"/>
       <c r="B111" s="28"/>
       <c r="C111" s="39">
@@ -10990,7 +10990,7 @@
       <c r="J111" s="30"/>
       <c r="K111" s="30"/>
     </row>
-    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A112" s="30"/>
       <c r="B112" s="28"/>
       <c r="C112" s="36">
@@ -11011,7 +11011,7 @@
       <c r="J112" s="30"/>
       <c r="K112" s="30"/>
     </row>
-    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="30"/>
       <c r="B113" s="28"/>
       <c r="C113" s="39">
@@ -11032,7 +11032,7 @@
       <c r="J113" s="30"/>
       <c r="K113" s="30"/>
     </row>
-    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A114" s="30"/>
       <c r="B114" s="28"/>
       <c r="C114" s="36">
@@ -11053,7 +11053,7 @@
       <c r="J114" s="30"/>
       <c r="K114" s="30"/>
     </row>
-    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A115" s="30"/>
       <c r="B115" s="28"/>
       <c r="C115" s="39">
@@ -11074,7 +11074,7 @@
       <c r="J115" s="30"/>
       <c r="K115" s="30"/>
     </row>
-    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" s="30"/>
       <c r="B116" s="28"/>
       <c r="C116" s="36">
@@ -11095,7 +11095,7 @@
       <c r="J116" s="30"/>
       <c r="K116" s="30"/>
     </row>
-    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A117" s="30"/>
       <c r="B117" s="28"/>
       <c r="C117" s="39">
@@ -11116,7 +11116,7 @@
       <c r="J117" s="30"/>
       <c r="K117" s="30"/>
     </row>
-    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A118" s="30"/>
       <c r="B118" s="28"/>
       <c r="C118" s="36">
@@ -11137,7 +11137,7 @@
       <c r="J118" s="30"/>
       <c r="K118" s="30"/>
     </row>
-    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A119" s="30"/>
       <c r="B119" s="28"/>
       <c r="C119" s="39">
@@ -11158,7 +11158,7 @@
       <c r="J119" s="30"/>
       <c r="K119" s="30"/>
     </row>
-    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A120" s="30"/>
       <c r="B120" s="28"/>
       <c r="C120" s="36">
@@ -11179,7 +11179,7 @@
       <c r="J120" s="30"/>
       <c r="K120" s="30"/>
     </row>
-    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A121" s="30"/>
       <c r="B121" s="28"/>
       <c r="C121" s="39">
@@ -11200,7 +11200,7 @@
       <c r="J121" s="30"/>
       <c r="K121" s="30"/>
     </row>
-    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A122" s="30"/>
       <c r="B122" s="28"/>
       <c r="C122" s="36">
@@ -11221,7 +11221,7 @@
       <c r="J122" s="30"/>
       <c r="K122" s="30"/>
     </row>
-    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A123" s="30"/>
       <c r="B123" s="28"/>
       <c r="C123" s="39">
@@ -11242,7 +11242,7 @@
       <c r="J123" s="30"/>
       <c r="K123" s="30"/>
     </row>
-    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A124" s="30"/>
       <c r="B124" s="28"/>
       <c r="C124" s="36">
@@ -11263,7 +11263,7 @@
       <c r="J124" s="30"/>
       <c r="K124" s="30"/>
     </row>
-    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A125" s="30"/>
       <c r="B125" s="28"/>
       <c r="C125" s="39">
@@ -11284,7 +11284,7 @@
       <c r="J125" s="30"/>
       <c r="K125" s="30"/>
     </row>
-    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A126" s="30"/>
       <c r="B126" s="28"/>
       <c r="C126" s="36">
@@ -11305,7 +11305,7 @@
       <c r="J126" s="30"/>
       <c r="K126" s="30"/>
     </row>
-    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A127" s="30"/>
       <c r="B127" s="28"/>
       <c r="C127" s="39">
@@ -11326,7 +11326,7 @@
       <c r="J127" s="30"/>
       <c r="K127" s="30"/>
     </row>
-    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A128" s="30"/>
       <c r="B128" s="28"/>
       <c r="C128" s="36">
@@ -11347,7 +11347,7 @@
       <c r="J128" s="30"/>
       <c r="K128" s="30"/>
     </row>
-    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A129" s="30"/>
       <c r="B129" s="28"/>
       <c r="C129" s="39">
@@ -11368,7 +11368,7 @@
       <c r="J129" s="30"/>
       <c r="K129" s="30"/>
     </row>
-    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A130" s="30"/>
       <c r="B130" s="28"/>
       <c r="C130" s="36">
@@ -11389,7 +11389,7 @@
       <c r="J130" s="30"/>
       <c r="K130" s="30"/>
     </row>
-    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A131" s="30"/>
       <c r="B131" s="28"/>
       <c r="C131" s="39">
@@ -11410,7 +11410,7 @@
       <c r="J131" s="30"/>
       <c r="K131" s="30"/>
     </row>
-    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A132" s="30"/>
       <c r="B132" s="28"/>
       <c r="C132" s="36">
@@ -11431,7 +11431,7 @@
       <c r="J132" s="30"/>
       <c r="K132" s="30"/>
     </row>
-    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C133" s="39">
         <v>76</v>
       </c>
@@ -11445,7 +11445,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C134" s="36">
         <v>77</v>
       </c>
@@ -11459,7 +11459,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C135" s="39">
         <v>78</v>
       </c>
@@ -11473,7 +11473,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C136" s="36">
         <v>79</v>
       </c>
@@ -11487,7 +11487,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C137" s="39">
         <v>80</v>
       </c>
@@ -11501,7 +11501,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="138" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C138" s="36">
         <v>81</v>
       </c>
@@ -11538,29 +11538,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R138"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C2" s="4" t="s">
         <v>260</v>
       </c>
@@ -11568,7 +11568,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -11576,7 +11576,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -11584,7 +11584,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -11592,13 +11592,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -11606,7 +11606,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -11621,7 +11621,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -11635,7 +11635,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -11649,7 +11649,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -11663,7 +11663,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -11677,7 +11677,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -11691,7 +11691,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -11705,7 +11705,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -11719,7 +11719,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -11733,7 +11733,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -11747,7 +11747,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -11761,7 +11761,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -11775,7 +11775,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -11789,7 +11789,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -11803,7 +11803,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -11817,7 +11817,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -11831,7 +11831,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -11845,7 +11845,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -11859,7 +11859,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -11873,7 +11873,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -11887,7 +11887,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -11901,7 +11901,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -11915,7 +11915,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -11929,7 +11929,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -11943,7 +11943,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -11957,7 +11957,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -11971,7 +11971,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -11985,7 +11985,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -11999,7 +11999,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -12013,7 +12013,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -12027,7 +12027,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -12041,7 +12041,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -12055,7 +12055,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -12069,7 +12069,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -12083,7 +12083,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -12097,7 +12097,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -12111,7 +12111,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -12125,7 +12125,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -12139,7 +12139,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -12153,7 +12153,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -12167,7 +12167,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -12181,7 +12181,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -12195,7 +12195,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -12209,7 +12209,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -12223,7 +12223,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -12237,7 +12237,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -12251,7 +12251,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -12265,12 +12265,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C57" s="34" t="s">
         <v>7</v>
       </c>
@@ -12284,7 +12284,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C58" s="36">
         <v>1</v>
       </c>
@@ -12298,7 +12298,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C59" s="39">
         <v>2</v>
       </c>
@@ -12312,7 +12312,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C60" s="36">
         <v>3</v>
       </c>
@@ -12326,7 +12326,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C61" s="39">
         <v>4</v>
       </c>
@@ -12340,7 +12340,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C62" s="36">
         <v>5</v>
       </c>
@@ -12354,7 +12354,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C63" s="39">
         <v>6</v>
       </c>
@@ -12368,7 +12368,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="30"/>
       <c r="B64" s="28"/>
       <c r="C64" s="36">
@@ -12389,7 +12389,7 @@
       <c r="J64" s="30"/>
       <c r="K64" s="30"/>
     </row>
-    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="30"/>
       <c r="B65" s="28"/>
       <c r="C65" s="39">
@@ -12410,7 +12410,7 @@
       <c r="J65" s="30"/>
       <c r="K65" s="30"/>
     </row>
-    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="30"/>
       <c r="B66" s="28"/>
       <c r="C66" s="36">
@@ -12431,7 +12431,7 @@
       <c r="J66" s="30"/>
       <c r="K66" s="30"/>
     </row>
-    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="30"/>
       <c r="B67" s="28"/>
       <c r="C67" s="39">
@@ -12452,7 +12452,7 @@
       <c r="J67" s="30"/>
       <c r="K67" s="30"/>
     </row>
-    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="30"/>
       <c r="B68" s="28"/>
       <c r="C68" s="36">
@@ -12473,7 +12473,7 @@
       <c r="J68" s="30"/>
       <c r="K68" s="30"/>
     </row>
-    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="30"/>
       <c r="B69" s="28"/>
       <c r="C69" s="39">
@@ -12494,7 +12494,7 @@
       <c r="J69" s="30"/>
       <c r="K69" s="30"/>
     </row>
-    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="30"/>
       <c r="B70" s="28"/>
       <c r="C70" s="36">
@@ -12515,7 +12515,7 @@
       <c r="J70" s="30"/>
       <c r="K70" s="30"/>
     </row>
-    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="30"/>
       <c r="B71" s="28"/>
       <c r="C71" s="39">
@@ -12536,7 +12536,7 @@
       <c r="J71" s="30"/>
       <c r="K71" s="30"/>
     </row>
-    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="30"/>
       <c r="B72" s="28"/>
       <c r="C72" s="36">
@@ -12557,7 +12557,7 @@
       <c r="J72" s="30"/>
       <c r="K72" s="30"/>
     </row>
-    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="30"/>
       <c r="B73" s="28"/>
       <c r="C73" s="39">
@@ -12578,7 +12578,7 @@
       <c r="J73" s="30"/>
       <c r="K73" s="30"/>
     </row>
-    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="30"/>
       <c r="B74" s="28"/>
       <c r="C74" s="36">
@@ -12599,7 +12599,7 @@
       <c r="J74" s="30"/>
       <c r="K74" s="30"/>
     </row>
-    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="30"/>
       <c r="B75" s="28"/>
       <c r="C75" s="39">
@@ -12620,7 +12620,7 @@
       <c r="J75" s="30"/>
       <c r="K75" s="30"/>
     </row>
-    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="30"/>
       <c r="B76" s="28"/>
       <c r="C76" s="36">
@@ -12641,7 +12641,7 @@
       <c r="J76" s="30"/>
       <c r="K76" s="30"/>
     </row>
-    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="30"/>
       <c r="B77" s="28"/>
       <c r="C77" s="39">
@@ -12662,7 +12662,7 @@
       <c r="J77" s="30"/>
       <c r="K77" s="30"/>
     </row>
-    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="30"/>
       <c r="B78" s="28"/>
       <c r="C78" s="36">
@@ -12683,7 +12683,7 @@
       <c r="J78" s="30"/>
       <c r="K78" s="30"/>
     </row>
-    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="30"/>
       <c r="B79" s="28"/>
       <c r="C79" s="39">
@@ -12704,7 +12704,7 @@
       <c r="J79" s="30"/>
       <c r="K79" s="30"/>
     </row>
-    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="30"/>
       <c r="B80" s="28"/>
       <c r="C80" s="36">
@@ -12725,7 +12725,7 @@
       <c r="J80" s="30"/>
       <c r="K80" s="30"/>
     </row>
-    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" s="30"/>
       <c r="B81" s="28"/>
       <c r="C81" s="39">
@@ -12746,7 +12746,7 @@
       <c r="J81" s="30"/>
       <c r="K81" s="30"/>
     </row>
-    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="30"/>
       <c r="B82" s="28"/>
       <c r="C82" s="36">
@@ -12767,7 +12767,7 @@
       <c r="J82" s="30"/>
       <c r="K82" s="30"/>
     </row>
-    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="30"/>
       <c r="B83" s="28"/>
       <c r="C83" s="39">
@@ -12788,7 +12788,7 @@
       <c r="J83" s="30"/>
       <c r="K83" s="30"/>
     </row>
-    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="30"/>
       <c r="B84" s="28"/>
       <c r="C84" s="36">
@@ -12809,7 +12809,7 @@
       <c r="J84" s="30"/>
       <c r="K84" s="30"/>
     </row>
-    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="30"/>
       <c r="B85" s="28"/>
       <c r="C85" s="39">
@@ -12830,7 +12830,7 @@
       <c r="J85" s="30"/>
       <c r="K85" s="30"/>
     </row>
-    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="30"/>
       <c r="B86" s="28"/>
       <c r="C86" s="36">
@@ -12851,7 +12851,7 @@
       <c r="J86" s="30"/>
       <c r="K86" s="30"/>
     </row>
-    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" s="30"/>
       <c r="B87" s="28"/>
       <c r="C87" s="39">
@@ -12872,7 +12872,7 @@
       <c r="J87" s="30"/>
       <c r="K87" s="30"/>
     </row>
-    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="30"/>
       <c r="B88" s="28"/>
       <c r="C88" s="36">
@@ -12893,7 +12893,7 @@
       <c r="J88" s="30"/>
       <c r="K88" s="30"/>
     </row>
-    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="30"/>
       <c r="B89" s="28"/>
       <c r="C89" s="39">
@@ -12914,7 +12914,7 @@
       <c r="J89" s="30"/>
       <c r="K89" s="30"/>
     </row>
-    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="30"/>
       <c r="B90" s="28"/>
       <c r="C90" s="36">
@@ -12935,7 +12935,7 @@
       <c r="J90" s="30"/>
       <c r="K90" s="30"/>
     </row>
-    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A91" s="30"/>
       <c r="B91" s="28"/>
       <c r="C91" s="39">
@@ -12956,7 +12956,7 @@
       <c r="J91" s="30"/>
       <c r="K91" s="30"/>
     </row>
-    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" s="30"/>
       <c r="B92" s="28"/>
       <c r="C92" s="36">
@@ -12977,7 +12977,7 @@
       <c r="J92" s="30"/>
       <c r="K92" s="30"/>
     </row>
-    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A93" s="30"/>
       <c r="B93" s="28"/>
       <c r="C93" s="39">
@@ -12998,7 +12998,7 @@
       <c r="J93" s="30"/>
       <c r="K93" s="30"/>
     </row>
-    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A94" s="30"/>
       <c r="B94" s="28"/>
       <c r="C94" s="36">
@@ -13019,7 +13019,7 @@
       <c r="J94" s="30"/>
       <c r="K94" s="30"/>
     </row>
-    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A95" s="30"/>
       <c r="B95" s="28"/>
       <c r="C95" s="39">
@@ -13040,7 +13040,7 @@
       <c r="J95" s="30"/>
       <c r="K95" s="30"/>
     </row>
-    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" s="30"/>
       <c r="B96" s="28"/>
       <c r="C96" s="36">
@@ -13061,7 +13061,7 @@
       <c r="J96" s="30"/>
       <c r="K96" s="30"/>
     </row>
-    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" s="30"/>
       <c r="B97" s="28"/>
       <c r="C97" s="39">
@@ -13082,7 +13082,7 @@
       <c r="J97" s="30"/>
       <c r="K97" s="30"/>
     </row>
-    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A98" s="30"/>
       <c r="B98" s="28"/>
       <c r="C98" s="36">
@@ -13103,7 +13103,7 @@
       <c r="J98" s="30"/>
       <c r="K98" s="30"/>
     </row>
-    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" s="30"/>
       <c r="B99" s="28"/>
       <c r="C99" s="39">
@@ -13124,7 +13124,7 @@
       <c r="J99" s="30"/>
       <c r="K99" s="30"/>
     </row>
-    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="30"/>
       <c r="B100" s="28"/>
       <c r="C100" s="36">
@@ -13145,7 +13145,7 @@
       <c r="J100" s="30"/>
       <c r="K100" s="30"/>
     </row>
-    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="30"/>
       <c r="B101" s="28"/>
       <c r="C101" s="39">
@@ -13166,7 +13166,7 @@
       <c r="J101" s="30"/>
       <c r="K101" s="30"/>
     </row>
-    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="30"/>
       <c r="B102" s="28"/>
       <c r="C102" s="36">
@@ -13187,7 +13187,7 @@
       <c r="J102" s="30"/>
       <c r="K102" s="30"/>
     </row>
-    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A103" s="30"/>
       <c r="B103" s="28"/>
       <c r="C103" s="39">
@@ -13208,7 +13208,7 @@
       <c r="J103" s="30"/>
       <c r="K103" s="30"/>
     </row>
-    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A104" s="30"/>
       <c r="B104" s="28"/>
       <c r="C104" s="36">
@@ -13229,7 +13229,7 @@
       <c r="J104" s="30"/>
       <c r="K104" s="30"/>
     </row>
-    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A105" s="30"/>
       <c r="B105" s="28"/>
       <c r="C105" s="39">
@@ -13250,7 +13250,7 @@
       <c r="J105" s="30"/>
       <c r="K105" s="30"/>
     </row>
-    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A106" s="30"/>
       <c r="B106" s="28"/>
       <c r="C106" s="36">
@@ -13271,7 +13271,7 @@
       <c r="J106" s="30"/>
       <c r="K106" s="30"/>
     </row>
-    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" s="30"/>
       <c r="B107" s="28"/>
       <c r="C107" s="39">
@@ -13292,7 +13292,7 @@
       <c r="J107" s="30"/>
       <c r="K107" s="30"/>
     </row>
-    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" s="30"/>
       <c r="B108" s="28"/>
       <c r="C108" s="36">
@@ -13313,7 +13313,7 @@
       <c r="J108" s="30"/>
       <c r="K108" s="30"/>
     </row>
-    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="30"/>
       <c r="B109" s="28"/>
       <c r="C109" s="39">
@@ -13334,7 +13334,7 @@
       <c r="J109" s="30"/>
       <c r="K109" s="30"/>
     </row>
-    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A110" s="30"/>
       <c r="B110" s="28"/>
       <c r="C110" s="36">
@@ -13355,7 +13355,7 @@
       <c r="J110" s="30"/>
       <c r="K110" s="30"/>
     </row>
-    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A111" s="30"/>
       <c r="B111" s="28"/>
       <c r="C111" s="39">
@@ -13376,7 +13376,7 @@
       <c r="J111" s="30"/>
       <c r="K111" s="30"/>
     </row>
-    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A112" s="30"/>
       <c r="B112" s="28"/>
       <c r="C112" s="36">
@@ -13397,7 +13397,7 @@
       <c r="J112" s="30"/>
       <c r="K112" s="30"/>
     </row>
-    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="30"/>
       <c r="B113" s="28"/>
       <c r="C113" s="39">
@@ -13418,7 +13418,7 @@
       <c r="J113" s="30"/>
       <c r="K113" s="30"/>
     </row>
-    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A114" s="30"/>
       <c r="B114" s="28"/>
       <c r="C114" s="36">
@@ -13439,7 +13439,7 @@
       <c r="J114" s="30"/>
       <c r="K114" s="30"/>
     </row>
-    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A115" s="30"/>
       <c r="B115" s="28"/>
       <c r="C115" s="39">
@@ -13460,7 +13460,7 @@
       <c r="J115" s="30"/>
       <c r="K115" s="30"/>
     </row>
-    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" s="30"/>
       <c r="B116" s="28"/>
       <c r="C116" s="36">
@@ -13481,7 +13481,7 @@
       <c r="J116" s="30"/>
       <c r="K116" s="30"/>
     </row>
-    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A117" s="30"/>
       <c r="B117" s="28"/>
       <c r="C117" s="39">
@@ -13502,7 +13502,7 @@
       <c r="J117" s="30"/>
       <c r="K117" s="30"/>
     </row>
-    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A118" s="30"/>
       <c r="B118" s="28"/>
       <c r="C118" s="36">
@@ -13523,7 +13523,7 @@
       <c r="J118" s="30"/>
       <c r="K118" s="30"/>
     </row>
-    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A119" s="30"/>
       <c r="B119" s="28"/>
       <c r="C119" s="39">
@@ -13544,7 +13544,7 @@
       <c r="J119" s="30"/>
       <c r="K119" s="30"/>
     </row>
-    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A120" s="30"/>
       <c r="B120" s="28"/>
       <c r="C120" s="36">
@@ -13565,7 +13565,7 @@
       <c r="J120" s="30"/>
       <c r="K120" s="30"/>
     </row>
-    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A121" s="30"/>
       <c r="B121" s="28"/>
       <c r="C121" s="39">
@@ -13586,7 +13586,7 @@
       <c r="J121" s="30"/>
       <c r="K121" s="30"/>
     </row>
-    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A122" s="30"/>
       <c r="B122" s="28"/>
       <c r="C122" s="36">
@@ -13607,7 +13607,7 @@
       <c r="J122" s="30"/>
       <c r="K122" s="30"/>
     </row>
-    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A123" s="30"/>
       <c r="B123" s="28"/>
       <c r="C123" s="39">
@@ -13628,7 +13628,7 @@
       <c r="J123" s="30"/>
       <c r="K123" s="30"/>
     </row>
-    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A124" s="30"/>
       <c r="B124" s="28"/>
       <c r="C124" s="36">
@@ -13649,7 +13649,7 @@
       <c r="J124" s="30"/>
       <c r="K124" s="30"/>
     </row>
-    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A125" s="30"/>
       <c r="B125" s="28"/>
       <c r="C125" s="39">
@@ -13670,7 +13670,7 @@
       <c r="J125" s="30"/>
       <c r="K125" s="30"/>
     </row>
-    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A126" s="30"/>
       <c r="B126" s="28"/>
       <c r="C126" s="36">
@@ -13691,7 +13691,7 @@
       <c r="J126" s="30"/>
       <c r="K126" s="30"/>
     </row>
-    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A127" s="30"/>
       <c r="B127" s="28"/>
       <c r="C127" s="39">
@@ -13712,7 +13712,7 @@
       <c r="J127" s="30"/>
       <c r="K127" s="30"/>
     </row>
-    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A128" s="30"/>
       <c r="B128" s="28"/>
       <c r="C128" s="36">
@@ -13733,7 +13733,7 @@
       <c r="J128" s="30"/>
       <c r="K128" s="30"/>
     </row>
-    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A129" s="30"/>
       <c r="B129" s="28"/>
       <c r="C129" s="39">
@@ -13754,7 +13754,7 @@
       <c r="J129" s="30"/>
       <c r="K129" s="30"/>
     </row>
-    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A130" s="30"/>
       <c r="B130" s="28"/>
       <c r="C130" s="36">
@@ -13775,7 +13775,7 @@
       <c r="J130" s="30"/>
       <c r="K130" s="30"/>
     </row>
-    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A131" s="30"/>
       <c r="B131" s="28"/>
       <c r="C131" s="39">
@@ -13796,7 +13796,7 @@
       <c r="J131" s="30"/>
       <c r="K131" s="30"/>
     </row>
-    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A132" s="30"/>
       <c r="B132" s="28"/>
       <c r="C132" s="36">
@@ -13817,7 +13817,7 @@
       <c r="J132" s="30"/>
       <c r="K132" s="30"/>
     </row>
-    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C133" s="39">
         <v>76</v>
       </c>
@@ -13831,7 +13831,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C134" s="36">
         <v>77</v>
       </c>
@@ -13845,7 +13845,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C135" s="3">
         <v>78</v>
       </c>
@@ -13859,7 +13859,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C136" s="36">
         <v>79</v>
       </c>
@@ -13873,7 +13873,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C137" s="3">
         <v>80</v>
       </c>
@@ -13887,7 +13887,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="138" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C138" s="36">
         <v>81</v>
       </c>
@@ -13924,29 +13924,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R138"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C2" s="4" t="s">
         <v>261</v>
       </c>
@@ -13954,7 +13954,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -13962,7 +13962,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -13970,7 +13970,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -13978,13 +13978,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -13992,7 +13992,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -14007,7 +14007,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -14021,7 +14021,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -14035,7 +14035,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -14049,7 +14049,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -14063,7 +14063,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -14077,7 +14077,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -14091,7 +14091,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -14105,7 +14105,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -14119,7 +14119,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -14133,7 +14133,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -14147,7 +14147,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -14161,7 +14161,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -14175,7 +14175,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -14189,7 +14189,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -14203,7 +14203,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -14217,7 +14217,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -14231,7 +14231,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -14245,7 +14245,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -14259,7 +14259,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -14273,7 +14273,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -14287,7 +14287,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -14301,7 +14301,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -14315,7 +14315,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -14329,7 +14329,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -14343,7 +14343,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -14357,7 +14357,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -14371,7 +14371,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -14385,7 +14385,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -14399,7 +14399,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -14413,7 +14413,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -14427,7 +14427,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -14441,7 +14441,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -14455,7 +14455,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -14469,7 +14469,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -14483,7 +14483,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -14497,7 +14497,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -14511,7 +14511,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -14525,7 +14525,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -14539,7 +14539,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -14553,7 +14553,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -14567,7 +14567,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -14581,7 +14581,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -14595,7 +14595,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -14609,7 +14609,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -14623,7 +14623,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -14637,7 +14637,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -14651,12 +14651,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C57" s="34" t="s">
         <v>7</v>
       </c>
@@ -14670,7 +14670,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C58" s="36">
         <v>1</v>
       </c>
@@ -14684,7 +14684,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C59" s="39">
         <v>2</v>
       </c>
@@ -14698,7 +14698,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C60" s="36">
         <v>3</v>
       </c>
@@ -14712,7 +14712,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C61" s="39">
         <v>4</v>
       </c>
@@ -14726,7 +14726,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C62" s="36">
         <v>5</v>
       </c>
@@ -14740,7 +14740,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C63" s="39">
         <v>6</v>
       </c>
@@ -14754,7 +14754,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="30"/>
       <c r="B64" s="28"/>
       <c r="C64" s="36">
@@ -14775,7 +14775,7 @@
       <c r="J64" s="30"/>
       <c r="K64" s="30"/>
     </row>
-    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="30"/>
       <c r="B65" s="28"/>
       <c r="C65" s="39">
@@ -14796,7 +14796,7 @@
       <c r="J65" s="30"/>
       <c r="K65" s="30"/>
     </row>
-    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="30"/>
       <c r="B66" s="28"/>
       <c r="C66" s="36">
@@ -14817,7 +14817,7 @@
       <c r="J66" s="30"/>
       <c r="K66" s="30"/>
     </row>
-    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="30"/>
       <c r="B67" s="28"/>
       <c r="C67" s="39">
@@ -14838,7 +14838,7 @@
       <c r="J67" s="30"/>
       <c r="K67" s="30"/>
     </row>
-    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="30"/>
       <c r="B68" s="28"/>
       <c r="C68" s="36">
@@ -14859,7 +14859,7 @@
       <c r="J68" s="30"/>
       <c r="K68" s="30"/>
     </row>
-    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="30"/>
       <c r="B69" s="28"/>
       <c r="C69" s="39">
@@ -14880,7 +14880,7 @@
       <c r="J69" s="30"/>
       <c r="K69" s="30"/>
     </row>
-    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="30"/>
       <c r="B70" s="28"/>
       <c r="C70" s="36">
@@ -14901,7 +14901,7 @@
       <c r="J70" s="30"/>
       <c r="K70" s="30"/>
     </row>
-    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="30"/>
       <c r="B71" s="28"/>
       <c r="C71" s="39">
@@ -14922,7 +14922,7 @@
       <c r="J71" s="30"/>
       <c r="K71" s="30"/>
     </row>
-    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="30"/>
       <c r="B72" s="28"/>
       <c r="C72" s="36">
@@ -14943,7 +14943,7 @@
       <c r="J72" s="30"/>
       <c r="K72" s="30"/>
     </row>
-    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="30"/>
       <c r="B73" s="28"/>
       <c r="C73" s="39">
@@ -14964,7 +14964,7 @@
       <c r="J73" s="30"/>
       <c r="K73" s="30"/>
     </row>
-    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="30"/>
       <c r="B74" s="28"/>
       <c r="C74" s="36">
@@ -14985,7 +14985,7 @@
       <c r="J74" s="30"/>
       <c r="K74" s="30"/>
     </row>
-    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="30"/>
       <c r="B75" s="28"/>
       <c r="C75" s="39">
@@ -15006,7 +15006,7 @@
       <c r="J75" s="30"/>
       <c r="K75" s="30"/>
     </row>
-    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="30"/>
       <c r="B76" s="28"/>
       <c r="C76" s="36">
@@ -15027,7 +15027,7 @@
       <c r="J76" s="30"/>
       <c r="K76" s="30"/>
     </row>
-    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="30"/>
       <c r="B77" s="28"/>
       <c r="C77" s="39">
@@ -15048,7 +15048,7 @@
       <c r="J77" s="30"/>
       <c r="K77" s="30"/>
     </row>
-    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="30"/>
       <c r="B78" s="28"/>
       <c r="C78" s="36">
@@ -15069,7 +15069,7 @@
       <c r="J78" s="30"/>
       <c r="K78" s="30"/>
     </row>
-    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="30"/>
       <c r="B79" s="28"/>
       <c r="C79" s="39">
@@ -15090,7 +15090,7 @@
       <c r="J79" s="30"/>
       <c r="K79" s="30"/>
     </row>
-    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="30"/>
       <c r="B80" s="28"/>
       <c r="C80" s="36">
@@ -15111,7 +15111,7 @@
       <c r="J80" s="30"/>
       <c r="K80" s="30"/>
     </row>
-    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" s="30"/>
       <c r="B81" s="28"/>
       <c r="C81" s="39">
@@ -15132,7 +15132,7 @@
       <c r="J81" s="30"/>
       <c r="K81" s="30"/>
     </row>
-    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="30"/>
       <c r="B82" s="28"/>
       <c r="C82" s="36">
@@ -15153,7 +15153,7 @@
       <c r="J82" s="30"/>
       <c r="K82" s="30"/>
     </row>
-    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="30"/>
       <c r="B83" s="28"/>
       <c r="C83" s="39">
@@ -15174,7 +15174,7 @@
       <c r="J83" s="30"/>
       <c r="K83" s="30"/>
     </row>
-    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="30"/>
       <c r="B84" s="28"/>
       <c r="C84" s="36">
@@ -15195,7 +15195,7 @@
       <c r="J84" s="30"/>
       <c r="K84" s="30"/>
     </row>
-    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="30"/>
       <c r="B85" s="28"/>
       <c r="C85" s="39">
@@ -15216,7 +15216,7 @@
       <c r="J85" s="30"/>
       <c r="K85" s="30"/>
     </row>
-    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="30"/>
       <c r="B86" s="28"/>
       <c r="C86" s="36">
@@ -15237,7 +15237,7 @@
       <c r="J86" s="30"/>
       <c r="K86" s="30"/>
     </row>
-    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" s="30"/>
       <c r="B87" s="28"/>
       <c r="C87" s="39">
@@ -15258,7 +15258,7 @@
       <c r="J87" s="30"/>
       <c r="K87" s="30"/>
     </row>
-    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="30"/>
       <c r="B88" s="28"/>
       <c r="C88" s="36">
@@ -15279,7 +15279,7 @@
       <c r="J88" s="30"/>
       <c r="K88" s="30"/>
     </row>
-    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="30"/>
       <c r="B89" s="28"/>
       <c r="C89" s="39">
@@ -15300,7 +15300,7 @@
       <c r="J89" s="30"/>
       <c r="K89" s="30"/>
     </row>
-    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="30"/>
       <c r="B90" s="28"/>
       <c r="C90" s="36">
@@ -15321,7 +15321,7 @@
       <c r="J90" s="30"/>
       <c r="K90" s="30"/>
     </row>
-    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A91" s="30"/>
       <c r="B91" s="28"/>
       <c r="C91" s="39">
@@ -15342,7 +15342,7 @@
       <c r="J91" s="30"/>
       <c r="K91" s="30"/>
     </row>
-    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" s="30"/>
       <c r="B92" s="28"/>
       <c r="C92" s="36">
@@ -15363,7 +15363,7 @@
       <c r="J92" s="30"/>
       <c r="K92" s="30"/>
     </row>
-    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A93" s="30"/>
       <c r="B93" s="28"/>
       <c r="C93" s="39">
@@ -15384,7 +15384,7 @@
       <c r="J93" s="30"/>
       <c r="K93" s="30"/>
     </row>
-    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A94" s="30"/>
       <c r="B94" s="28"/>
       <c r="C94" s="36">
@@ -15405,7 +15405,7 @@
       <c r="J94" s="30"/>
       <c r="K94" s="30"/>
     </row>
-    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A95" s="30"/>
       <c r="B95" s="28"/>
       <c r="C95" s="39">
@@ -15426,7 +15426,7 @@
       <c r="J95" s="30"/>
       <c r="K95" s="30"/>
     </row>
-    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" s="30"/>
       <c r="B96" s="28"/>
       <c r="C96" s="36">
@@ -15447,7 +15447,7 @@
       <c r="J96" s="30"/>
       <c r="K96" s="30"/>
     </row>
-    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" s="30"/>
       <c r="B97" s="28"/>
       <c r="C97" s="39">
@@ -15468,7 +15468,7 @@
       <c r="J97" s="30"/>
       <c r="K97" s="30"/>
     </row>
-    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A98" s="30"/>
       <c r="B98" s="28"/>
       <c r="C98" s="36">
@@ -15489,7 +15489,7 @@
       <c r="J98" s="30"/>
       <c r="K98" s="30"/>
     </row>
-    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" s="30"/>
       <c r="B99" s="28"/>
       <c r="C99" s="39">
@@ -15510,7 +15510,7 @@
       <c r="J99" s="30"/>
       <c r="K99" s="30"/>
     </row>
-    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="30"/>
       <c r="B100" s="28"/>
       <c r="C100" s="36">
@@ -15531,7 +15531,7 @@
       <c r="J100" s="30"/>
       <c r="K100" s="30"/>
     </row>
-    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="30"/>
       <c r="B101" s="28"/>
       <c r="C101" s="39">
@@ -15552,7 +15552,7 @@
       <c r="J101" s="30"/>
       <c r="K101" s="30"/>
     </row>
-    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="30"/>
       <c r="B102" s="28"/>
       <c r="C102" s="36">
@@ -15573,7 +15573,7 @@
       <c r="J102" s="30"/>
       <c r="K102" s="30"/>
     </row>
-    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A103" s="30"/>
       <c r="B103" s="28"/>
       <c r="C103" s="39">
@@ -15594,7 +15594,7 @@
       <c r="J103" s="30"/>
       <c r="K103" s="30"/>
     </row>
-    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A104" s="30"/>
       <c r="B104" s="28"/>
       <c r="C104" s="36">
@@ -15615,7 +15615,7 @@
       <c r="J104" s="30"/>
       <c r="K104" s="30"/>
     </row>
-    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A105" s="30"/>
       <c r="B105" s="28"/>
       <c r="C105" s="39">
@@ -15636,7 +15636,7 @@
       <c r="J105" s="30"/>
       <c r="K105" s="30"/>
     </row>
-    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A106" s="30"/>
       <c r="B106" s="28"/>
       <c r="C106" s="36">
@@ -15657,7 +15657,7 @@
       <c r="J106" s="30"/>
       <c r="K106" s="30"/>
     </row>
-    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" s="30"/>
       <c r="B107" s="28"/>
       <c r="C107" s="39">
@@ -15678,7 +15678,7 @@
       <c r="J107" s="30"/>
       <c r="K107" s="30"/>
     </row>
-    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" s="30"/>
       <c r="B108" s="28"/>
       <c r="C108" s="36">
@@ -15699,7 +15699,7 @@
       <c r="J108" s="30"/>
       <c r="K108" s="30"/>
     </row>
-    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="30"/>
       <c r="B109" s="28"/>
       <c r="C109" s="39">
@@ -15720,7 +15720,7 @@
       <c r="J109" s="30"/>
       <c r="K109" s="30"/>
     </row>
-    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A110" s="30"/>
       <c r="B110" s="28"/>
       <c r="C110" s="36">
@@ -15741,7 +15741,7 @@
       <c r="J110" s="30"/>
       <c r="K110" s="30"/>
     </row>
-    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A111" s="30"/>
       <c r="B111" s="28"/>
       <c r="C111" s="39">
@@ -15762,7 +15762,7 @@
       <c r="J111" s="30"/>
       <c r="K111" s="30"/>
     </row>
-    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A112" s="30"/>
       <c r="B112" s="28"/>
       <c r="C112" s="36">
@@ -15783,7 +15783,7 @@
       <c r="J112" s="30"/>
       <c r="K112" s="30"/>
     </row>
-    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="30"/>
       <c r="B113" s="28"/>
       <c r="C113" s="39">
@@ -15804,7 +15804,7 @@
       <c r="J113" s="30"/>
       <c r="K113" s="30"/>
     </row>
-    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A114" s="30"/>
       <c r="B114" s="28"/>
       <c r="C114" s="36">
@@ -15825,7 +15825,7 @@
       <c r="J114" s="30"/>
       <c r="K114" s="30"/>
     </row>
-    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A115" s="30"/>
       <c r="B115" s="28"/>
       <c r="C115" s="39">
@@ -15846,7 +15846,7 @@
       <c r="J115" s="30"/>
       <c r="K115" s="30"/>
     </row>
-    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" s="30"/>
       <c r="B116" s="28"/>
       <c r="C116" s="36">
@@ -15867,7 +15867,7 @@
       <c r="J116" s="30"/>
       <c r="K116" s="30"/>
     </row>
-    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A117" s="30"/>
       <c r="B117" s="28"/>
       <c r="C117" s="39">
@@ -15888,7 +15888,7 @@
       <c r="J117" s="30"/>
       <c r="K117" s="30"/>
     </row>
-    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A118" s="30"/>
       <c r="B118" s="28"/>
       <c r="C118" s="36">
@@ -15909,7 +15909,7 @@
       <c r="J118" s="30"/>
       <c r="K118" s="30"/>
     </row>
-    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A119" s="30"/>
       <c r="B119" s="28"/>
       <c r="C119" s="39">
@@ -15930,7 +15930,7 @@
       <c r="J119" s="30"/>
       <c r="K119" s="30"/>
     </row>
-    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A120" s="30"/>
       <c r="B120" s="28"/>
       <c r="C120" s="36">
@@ -15951,7 +15951,7 @@
       <c r="J120" s="30"/>
       <c r="K120" s="30"/>
     </row>
-    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A121" s="30"/>
       <c r="B121" s="28"/>
       <c r="C121" s="39">
@@ -15972,7 +15972,7 @@
       <c r="J121" s="30"/>
       <c r="K121" s="30"/>
     </row>
-    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A122" s="30"/>
       <c r="B122" s="28"/>
       <c r="C122" s="36">
@@ -15993,7 +15993,7 @@
       <c r="J122" s="30"/>
       <c r="K122" s="30"/>
     </row>
-    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A123" s="30"/>
       <c r="B123" s="28"/>
       <c r="C123" s="39">
@@ -16014,7 +16014,7 @@
       <c r="J123" s="30"/>
       <c r="K123" s="30"/>
     </row>
-    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A124" s="30"/>
       <c r="B124" s="28"/>
       <c r="C124" s="36">
@@ -16035,7 +16035,7 @@
       <c r="J124" s="30"/>
       <c r="K124" s="30"/>
     </row>
-    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A125" s="30"/>
       <c r="B125" s="28"/>
       <c r="C125" s="39">
@@ -16056,7 +16056,7 @@
       <c r="J125" s="30"/>
       <c r="K125" s="30"/>
     </row>
-    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A126" s="30"/>
       <c r="B126" s="28"/>
       <c r="C126" s="36">
@@ -16077,7 +16077,7 @@
       <c r="J126" s="30"/>
       <c r="K126" s="30"/>
     </row>
-    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A127" s="30"/>
       <c r="B127" s="28"/>
       <c r="C127" s="39">
@@ -16098,7 +16098,7 @@
       <c r="J127" s="30"/>
       <c r="K127" s="30"/>
     </row>
-    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A128" s="30"/>
       <c r="B128" s="28"/>
       <c r="C128" s="36">
@@ -16119,7 +16119,7 @@
       <c r="J128" s="30"/>
       <c r="K128" s="30"/>
     </row>
-    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A129" s="30"/>
       <c r="B129" s="28"/>
       <c r="C129" s="39">
@@ -16140,7 +16140,7 @@
       <c r="J129" s="30"/>
       <c r="K129" s="30"/>
     </row>
-    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A130" s="30"/>
       <c r="B130" s="28"/>
       <c r="C130" s="36">
@@ -16161,7 +16161,7 @@
       <c r="J130" s="30"/>
       <c r="K130" s="30"/>
     </row>
-    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A131" s="30"/>
       <c r="B131" s="28"/>
       <c r="C131" s="39">
@@ -16182,7 +16182,7 @@
       <c r="J131" s="30"/>
       <c r="K131" s="30"/>
     </row>
-    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A132" s="30"/>
       <c r="B132" s="28"/>
       <c r="C132" s="36">
@@ -16203,7 +16203,7 @@
       <c r="J132" s="30"/>
       <c r="K132" s="30"/>
     </row>
-    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C133" s="39">
         <v>76</v>
       </c>
@@ -16217,7 +16217,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C134" s="36">
         <v>77</v>
       </c>
@@ -16231,7 +16231,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C135" s="3">
         <v>78</v>
       </c>
@@ -16245,7 +16245,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C136" s="36">
         <v>79</v>
       </c>
@@ -16259,7 +16259,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C137" s="3">
         <v>80</v>
       </c>
@@ -16273,7 +16273,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="138" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C138" s="36">
         <v>81</v>
       </c>
@@ -16310,29 +16310,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R138"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C2" s="4" t="s">
         <v>262</v>
       </c>
@@ -16340,7 +16340,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -16348,7 +16348,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -16356,7 +16356,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -16364,13 +16364,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -16378,7 +16378,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -16393,7 +16393,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -16407,7 +16407,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -16421,7 +16421,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -16435,7 +16435,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -16449,7 +16449,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -16463,7 +16463,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -16477,7 +16477,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -16491,7 +16491,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -16505,7 +16505,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -16519,7 +16519,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -16533,7 +16533,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -16547,7 +16547,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -16561,7 +16561,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -16575,7 +16575,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -16589,7 +16589,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -16603,7 +16603,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -16617,7 +16617,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -16631,7 +16631,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -16645,7 +16645,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -16659,7 +16659,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -16673,7 +16673,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -16687,7 +16687,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -16701,7 +16701,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -16715,7 +16715,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -16729,7 +16729,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -16743,7 +16743,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -16757,7 +16757,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -16771,7 +16771,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -16785,7 +16785,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -16799,7 +16799,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -16813,7 +16813,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -16827,7 +16827,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -16841,7 +16841,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -16855,7 +16855,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -16869,7 +16869,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -16883,7 +16883,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -16897,7 +16897,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -16911,7 +16911,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -16925,7 +16925,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -16939,7 +16939,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -16953,7 +16953,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -16967,7 +16967,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -16981,7 +16981,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -16995,7 +16995,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -17009,7 +17009,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -17023,7 +17023,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -17037,12 +17037,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C57" s="34" t="s">
         <v>7</v>
       </c>
@@ -17056,7 +17056,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C58" s="36">
         <v>1</v>
       </c>
@@ -17070,7 +17070,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C59" s="39">
         <v>2</v>
       </c>
@@ -17084,7 +17084,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C60" s="36">
         <v>3</v>
       </c>
@@ -17098,7 +17098,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C61" s="39">
         <v>4</v>
       </c>
@@ -17112,7 +17112,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C62" s="36">
         <v>5</v>
       </c>
@@ -17126,7 +17126,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C63" s="39">
         <v>6</v>
       </c>
@@ -17140,7 +17140,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="30"/>
       <c r="B64" s="28"/>
       <c r="C64" s="36">
@@ -17161,7 +17161,7 @@
       <c r="J64" s="30"/>
       <c r="K64" s="30"/>
     </row>
-    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="30"/>
       <c r="B65" s="28"/>
       <c r="C65" s="39">
@@ -17182,7 +17182,7 @@
       <c r="J65" s="30"/>
       <c r="K65" s="30"/>
     </row>
-    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="30"/>
       <c r="B66" s="28"/>
       <c r="C66" s="36">
@@ -17203,7 +17203,7 @@
       <c r="J66" s="30"/>
       <c r="K66" s="30"/>
     </row>
-    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="30"/>
       <c r="B67" s="28"/>
       <c r="C67" s="39">
@@ -17224,7 +17224,7 @@
       <c r="J67" s="30"/>
       <c r="K67" s="30"/>
     </row>
-    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="30"/>
       <c r="B68" s="28"/>
       <c r="C68" s="36">
@@ -17245,7 +17245,7 @@
       <c r="J68" s="30"/>
       <c r="K68" s="30"/>
     </row>
-    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="30"/>
       <c r="B69" s="28"/>
       <c r="C69" s="39">
@@ -17266,7 +17266,7 @@
       <c r="J69" s="30"/>
       <c r="K69" s="30"/>
     </row>
-    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="30"/>
       <c r="B70" s="28"/>
       <c r="C70" s="36">
@@ -17287,7 +17287,7 @@
       <c r="J70" s="30"/>
       <c r="K70" s="30"/>
     </row>
-    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="30"/>
       <c r="B71" s="28"/>
       <c r="C71" s="39">
@@ -17308,7 +17308,7 @@
       <c r="J71" s="30"/>
       <c r="K71" s="30"/>
     </row>
-    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="30"/>
       <c r="B72" s="28"/>
       <c r="C72" s="36">
@@ -17329,7 +17329,7 @@
       <c r="J72" s="30"/>
       <c r="K72" s="30"/>
     </row>
-    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="30"/>
       <c r="B73" s="28"/>
       <c r="C73" s="39">
@@ -17350,7 +17350,7 @@
       <c r="J73" s="30"/>
       <c r="K73" s="30"/>
     </row>
-    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="30"/>
       <c r="B74" s="28"/>
       <c r="C74" s="36">
@@ -17371,7 +17371,7 @@
       <c r="J74" s="30"/>
       <c r="K74" s="30"/>
     </row>
-    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="30"/>
       <c r="B75" s="28"/>
       <c r="C75" s="39">
@@ -17392,7 +17392,7 @@
       <c r="J75" s="30"/>
       <c r="K75" s="30"/>
     </row>
-    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="30"/>
       <c r="B76" s="28"/>
       <c r="C76" s="36">
@@ -17413,7 +17413,7 @@
       <c r="J76" s="30"/>
       <c r="K76" s="30"/>
     </row>
-    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="30"/>
       <c r="B77" s="28"/>
       <c r="C77" s="39">
@@ -17434,7 +17434,7 @@
       <c r="J77" s="30"/>
       <c r="K77" s="30"/>
     </row>
-    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="30"/>
       <c r="B78" s="28"/>
       <c r="C78" s="36">
@@ -17455,7 +17455,7 @@
       <c r="J78" s="30"/>
       <c r="K78" s="30"/>
     </row>
-    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="30"/>
       <c r="B79" s="28"/>
       <c r="C79" s="39">
@@ -17476,7 +17476,7 @@
       <c r="J79" s="30"/>
       <c r="K79" s="30"/>
     </row>
-    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="30"/>
       <c r="B80" s="28"/>
       <c r="C80" s="36">
@@ -17497,7 +17497,7 @@
       <c r="J80" s="30"/>
       <c r="K80" s="30"/>
     </row>
-    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" s="30"/>
       <c r="B81" s="28"/>
       <c r="C81" s="39">
@@ -17518,7 +17518,7 @@
       <c r="J81" s="30"/>
       <c r="K81" s="30"/>
     </row>
-    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="30"/>
       <c r="B82" s="28"/>
       <c r="C82" s="36">
@@ -17539,7 +17539,7 @@
       <c r="J82" s="30"/>
       <c r="K82" s="30"/>
     </row>
-    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="30"/>
       <c r="B83" s="28"/>
       <c r="C83" s="39">
@@ -17560,7 +17560,7 @@
       <c r="J83" s="30"/>
       <c r="K83" s="30"/>
     </row>
-    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="30"/>
       <c r="B84" s="28"/>
       <c r="C84" s="36">
@@ -17581,7 +17581,7 @@
       <c r="J84" s="30"/>
       <c r="K84" s="30"/>
     </row>
-    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="30"/>
       <c r="B85" s="28"/>
       <c r="C85" s="39">
@@ -17602,7 +17602,7 @@
       <c r="J85" s="30"/>
       <c r="K85" s="30"/>
     </row>
-    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="30"/>
       <c r="B86" s="28"/>
       <c r="C86" s="36">
@@ -17623,7 +17623,7 @@
       <c r="J86" s="30"/>
       <c r="K86" s="30"/>
     </row>
-    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" s="30"/>
       <c r="B87" s="28"/>
       <c r="C87" s="39">
@@ -17644,7 +17644,7 @@
       <c r="J87" s="30"/>
       <c r="K87" s="30"/>
     </row>
-    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="30"/>
       <c r="B88" s="28"/>
       <c r="C88" s="36">
@@ -17665,7 +17665,7 @@
       <c r="J88" s="30"/>
       <c r="K88" s="30"/>
     </row>
-    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="30"/>
       <c r="B89" s="28"/>
       <c r="C89" s="39">
@@ -17686,7 +17686,7 @@
       <c r="J89" s="30"/>
       <c r="K89" s="30"/>
     </row>
-    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="30"/>
       <c r="B90" s="28"/>
       <c r="C90" s="36">
@@ -17707,7 +17707,7 @@
       <c r="J90" s="30"/>
       <c r="K90" s="30"/>
     </row>
-    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A91" s="30"/>
       <c r="B91" s="28"/>
       <c r="C91" s="39">
@@ -17728,7 +17728,7 @@
       <c r="J91" s="30"/>
       <c r="K91" s="30"/>
     </row>
-    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" s="30"/>
       <c r="B92" s="28"/>
       <c r="C92" s="36">
@@ -17749,7 +17749,7 @@
       <c r="J92" s="30"/>
       <c r="K92" s="30"/>
     </row>
-    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A93" s="30"/>
       <c r="B93" s="28"/>
       <c r="C93" s="39">
@@ -17770,7 +17770,7 @@
       <c r="J93" s="30"/>
       <c r="K93" s="30"/>
     </row>
-    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A94" s="30"/>
       <c r="B94" s="28"/>
       <c r="C94" s="36">
@@ -17791,7 +17791,7 @@
       <c r="J94" s="30"/>
       <c r="K94" s="30"/>
     </row>
-    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A95" s="30"/>
       <c r="B95" s="28"/>
       <c r="C95" s="39">
@@ -17812,7 +17812,7 @@
       <c r="J95" s="30"/>
       <c r="K95" s="30"/>
     </row>
-    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" s="30"/>
       <c r="B96" s="28"/>
       <c r="C96" s="36">
@@ -17833,7 +17833,7 @@
       <c r="J96" s="30"/>
       <c r="K96" s="30"/>
     </row>
-    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" s="30"/>
       <c r="B97" s="28"/>
       <c r="C97" s="39">
@@ -17854,7 +17854,7 @@
       <c r="J97" s="30"/>
       <c r="K97" s="30"/>
     </row>
-    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A98" s="30"/>
       <c r="B98" s="28"/>
       <c r="C98" s="36">
@@ -17875,7 +17875,7 @@
       <c r="J98" s="30"/>
       <c r="K98" s="30"/>
     </row>
-    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" s="30"/>
       <c r="B99" s="28"/>
       <c r="C99" s="39">
@@ -17896,7 +17896,7 @@
       <c r="J99" s="30"/>
       <c r="K99" s="30"/>
     </row>
-    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="30"/>
       <c r="B100" s="28"/>
       <c r="C100" s="36">
@@ -17917,7 +17917,7 @@
       <c r="J100" s="30"/>
       <c r="K100" s="30"/>
     </row>
-    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="30"/>
       <c r="B101" s="28"/>
       <c r="C101" s="39">
@@ -17938,7 +17938,7 @@
       <c r="J101" s="30"/>
       <c r="K101" s="30"/>
     </row>
-    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="30"/>
       <c r="B102" s="28"/>
       <c r="C102" s="36">
@@ -17959,7 +17959,7 @@
       <c r="J102" s="30"/>
       <c r="K102" s="30"/>
     </row>
-    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A103" s="30"/>
       <c r="B103" s="28"/>
       <c r="C103" s="39">
@@ -17980,7 +17980,7 @@
       <c r="J103" s="30"/>
       <c r="K103" s="30"/>
     </row>
-    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A104" s="30"/>
       <c r="B104" s="28"/>
       <c r="C104" s="36">
@@ -18001,7 +18001,7 @@
       <c r="J104" s="30"/>
       <c r="K104" s="30"/>
     </row>
-    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A105" s="30"/>
       <c r="B105" s="28"/>
       <c r="C105" s="39">
@@ -18022,7 +18022,7 @@
       <c r="J105" s="30"/>
       <c r="K105" s="30"/>
     </row>
-    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A106" s="30"/>
       <c r="B106" s="28"/>
       <c r="C106" s="36">
@@ -18043,7 +18043,7 @@
       <c r="J106" s="30"/>
       <c r="K106" s="30"/>
     </row>
-    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" s="30"/>
       <c r="B107" s="28"/>
       <c r="C107" s="39">
@@ -18064,7 +18064,7 @@
       <c r="J107" s="30"/>
       <c r="K107" s="30"/>
     </row>
-    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" s="30"/>
       <c r="B108" s="28"/>
       <c r="C108" s="36">
@@ -18085,7 +18085,7 @@
       <c r="J108" s="30"/>
       <c r="K108" s="30"/>
     </row>
-    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="30"/>
       <c r="B109" s="28"/>
       <c r="C109" s="39">
@@ -18106,7 +18106,7 @@
       <c r="J109" s="30"/>
       <c r="K109" s="30"/>
     </row>
-    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A110" s="30"/>
       <c r="B110" s="28"/>
       <c r="C110" s="36">
@@ -18127,7 +18127,7 @@
       <c r="J110" s="30"/>
       <c r="K110" s="30"/>
     </row>
-    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A111" s="30"/>
       <c r="B111" s="28"/>
       <c r="C111" s="39">
@@ -18148,7 +18148,7 @@
       <c r="J111" s="30"/>
       <c r="K111" s="30"/>
     </row>
-    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A112" s="30"/>
       <c r="B112" s="28"/>
       <c r="C112" s="36">
@@ -18169,7 +18169,7 @@
       <c r="J112" s="30"/>
       <c r="K112" s="30"/>
     </row>
-    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="30"/>
       <c r="B113" s="28"/>
       <c r="C113" s="39">
@@ -18190,7 +18190,7 @@
       <c r="J113" s="30"/>
       <c r="K113" s="30"/>
     </row>
-    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A114" s="30"/>
       <c r="B114" s="28"/>
       <c r="C114" s="36">
@@ -18211,7 +18211,7 @@
       <c r="J114" s="30"/>
       <c r="K114" s="30"/>
     </row>
-    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A115" s="30"/>
       <c r="B115" s="28"/>
       <c r="C115" s="39">
@@ -18232,7 +18232,7 @@
       <c r="J115" s="30"/>
       <c r="K115" s="30"/>
     </row>
-    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" s="30"/>
       <c r="B116" s="28"/>
       <c r="C116" s="36">
@@ -18253,7 +18253,7 @@
       <c r="J116" s="30"/>
       <c r="K116" s="30"/>
     </row>
-    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A117" s="30"/>
       <c r="B117" s="28"/>
       <c r="C117" s="39">
@@ -18274,7 +18274,7 @@
       <c r="J117" s="30"/>
       <c r="K117" s="30"/>
     </row>
-    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A118" s="30"/>
       <c r="B118" s="28"/>
       <c r="C118" s="36">
@@ -18295,7 +18295,7 @@
       <c r="J118" s="30"/>
       <c r="K118" s="30"/>
     </row>
-    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A119" s="30"/>
       <c r="B119" s="28"/>
       <c r="C119" s="39">
@@ -18316,7 +18316,7 @@
       <c r="J119" s="30"/>
       <c r="K119" s="30"/>
     </row>
-    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A120" s="30"/>
       <c r="B120" s="28"/>
       <c r="C120" s="36">
@@ -18337,7 +18337,7 @@
       <c r="J120" s="30"/>
       <c r="K120" s="30"/>
     </row>
-    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A121" s="30"/>
       <c r="B121" s="28"/>
       <c r="C121" s="39">
@@ -18358,7 +18358,7 @@
       <c r="J121" s="30"/>
       <c r="K121" s="30"/>
     </row>
-    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A122" s="30"/>
       <c r="B122" s="28"/>
       <c r="C122" s="36">
@@ -18379,7 +18379,7 @@
       <c r="J122" s="30"/>
       <c r="K122" s="30"/>
     </row>
-    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A123" s="30"/>
       <c r="B123" s="28"/>
       <c r="C123" s="39">
@@ -18400,7 +18400,7 @@
       <c r="J123" s="30"/>
       <c r="K123" s="30"/>
     </row>
-    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A124" s="30"/>
       <c r="B124" s="28"/>
       <c r="C124" s="36">
@@ -18421,7 +18421,7 @@
       <c r="J124" s="30"/>
       <c r="K124" s="30"/>
     </row>
-    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A125" s="30"/>
       <c r="B125" s="28"/>
       <c r="C125" s="39">
@@ -18442,7 +18442,7 @@
       <c r="J125" s="30"/>
       <c r="K125" s="30"/>
     </row>
-    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A126" s="30"/>
       <c r="B126" s="28"/>
       <c r="C126" s="36">
@@ -18463,7 +18463,7 @@
       <c r="J126" s="30"/>
       <c r="K126" s="30"/>
     </row>
-    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A127" s="30"/>
       <c r="B127" s="28"/>
       <c r="C127" s="39">
@@ -18484,7 +18484,7 @@
       <c r="J127" s="30"/>
       <c r="K127" s="30"/>
     </row>
-    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A128" s="30"/>
       <c r="B128" s="28"/>
       <c r="C128" s="36">
@@ -18505,7 +18505,7 @@
       <c r="J128" s="30"/>
       <c r="K128" s="30"/>
     </row>
-    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A129" s="30"/>
       <c r="B129" s="28"/>
       <c r="C129" s="39">
@@ -18526,7 +18526,7 @@
       <c r="J129" s="30"/>
       <c r="K129" s="30"/>
     </row>
-    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A130" s="30"/>
       <c r="B130" s="28"/>
       <c r="C130" s="36">
@@ -18547,7 +18547,7 @@
       <c r="J130" s="30"/>
       <c r="K130" s="30"/>
     </row>
-    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A131" s="30"/>
       <c r="B131" s="28"/>
       <c r="C131" s="39">
@@ -18568,7 +18568,7 @@
       <c r="J131" s="30"/>
       <c r="K131" s="30"/>
     </row>
-    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A132" s="30"/>
       <c r="B132" s="28"/>
       <c r="C132" s="36">
@@ -18589,7 +18589,7 @@
       <c r="J132" s="30"/>
       <c r="K132" s="30"/>
     </row>
-    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C133" s="39">
         <v>76</v>
       </c>
@@ -18603,7 +18603,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C134" s="36">
         <v>77</v>
       </c>
@@ -18617,7 +18617,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C135" s="3">
         <v>78</v>
       </c>
@@ -18631,7 +18631,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C136" s="36">
         <v>79</v>
       </c>
@@ -18645,7 +18645,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C137" s="3">
         <v>80</v>
       </c>
@@ -18659,7 +18659,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="138" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C138" s="36">
         <v>81</v>
       </c>

--- a/_Learn/Packaging.tutorial/OS.11/23H2/Expand/Install/Report/zh-TW.xlsx
+++ b/_Learn/Packaging.tutorial/OS.11/23H2/Expand/Install/Report/zh-TW.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\OneDrive\Documents\_Learn\Packaging.tutorial\OS.11\23H2\Expand\Install\Report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5924f5d6bcb7c7fc/Documents/_Learn/Packaging.tutorial/OS.11/23H2/Expand/Install/Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F4A645-927D-40D6-BDF2-801766CF9CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{02F4A645-927D-40D6-BDF2-801766CF9CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62D313B3-BC72-42DD-9EC6-100CC2C48553}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="27634" windowHeight="16629" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="5" r:id="rId1"/>
@@ -4378,22 +4378,22 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L34"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="8" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="84.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="50.3984375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="20.59765625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="84.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="50.3828125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="20.61328125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="16.69140625" style="3" customWidth="1"/>
     <col min="7" max="7" width="122" style="3" customWidth="1"/>
-    <col min="8" max="10" width="16.6640625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="16.6640625" style="8" customWidth="1"/>
-    <col min="12" max="12" width="2.6640625" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.1328125" style="1" hidden="1"/>
+    <col min="8" max="10" width="16.69140625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="16.69140625" style="8" customWidth="1"/>
+    <col min="12" max="12" width="2.69140625" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.15234375" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4406,7 +4406,7 @@
       <c r="J1" s="2"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:12" ht="80.2" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:12" ht="80.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1"/>
       <c r="C2" s="4" t="s">
         <v>263</v>
@@ -4421,7 +4421,7 @@
       <c r="J2" s="2"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1"/>
       <c r="C3" s="7"/>
       <c r="D3" s="5"/>
@@ -4433,7 +4433,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:12" ht="5.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -4443,7 +4443,7 @@
       <c r="I4" s="10"/>
       <c r="J4" s="11"/>
     </row>
-    <row r="5" spans="1:12" ht="62.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" ht="62.8" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="12"/>
       <c r="C5" s="12" t="s">
         <v>9</v>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="L5" s="8"/>
     </row>
-    <row r="6" spans="1:12" ht="110.25" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" ht="111" x14ac:dyDescent="0.4">
       <c r="B6" s="14"/>
       <c r="C6" s="15" t="s">
         <v>267</v>
@@ -4503,7 +4503,7 @@
       <c r="K6" s="14"/>
       <c r="L6" s="8"/>
     </row>
-    <row r="7" spans="1:12" ht="78.75" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" ht="79.3" x14ac:dyDescent="0.4">
       <c r="B7" s="14"/>
       <c r="C7" s="42" t="s">
         <v>264</v>
@@ -4532,17 +4532,13 @@
       <c r="K7" s="43"/>
       <c r="L7" s="8"/>
     </row>
-    <row r="8" spans="1:12" ht="20.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" s="15" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="8"/>
+      <c r="B8" s="3"/>
       <c r="C8" s="14"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-    </row>
-    <row r="9" spans="1:12" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="9" spans="1:12" s="3" customFormat="1" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="8"/>
       <c r="B9" s="17"/>
       <c r="C9" s="18" t="s">
         <v>2</v>
@@ -4551,7 +4547,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:12" s="8" customFormat="1" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B10" s="20"/>
       <c r="C10" s="21" t="s">
         <v>0</v>
@@ -4559,14 +4555,8 @@
       <c r="D10" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-    </row>
-    <row r="11" spans="1:12" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="11" spans="1:12" s="8" customFormat="1" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B11" s="22"/>
       <c r="C11" s="21" t="s">
         <v>1</v>
@@ -4574,14 +4564,8 @@
       <c r="D11" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-    </row>
-    <row r="12" spans="1:12" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="12" spans="1:12" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="8"/>
@@ -4591,14 +4575,14 @@
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
     </row>
-    <row r="13" spans="1:12" ht="30" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:12" ht="30" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
     </row>
-    <row r="14" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -4609,7 +4593,7 @@
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
     </row>
-    <row r="15" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -4620,7 +4604,7 @@
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
     </row>
-    <row r="16" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -4631,7 +4615,7 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -4642,7 +4626,7 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
     </row>
-    <row r="18" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -4653,7 +4637,7 @@
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -4664,7 +4648,7 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
     </row>
-    <row r="20" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -4675,7 +4659,7 @@
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
     </row>
-    <row r="21" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
@@ -4686,7 +4670,7 @@
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
     </row>
-    <row r="22" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -4697,7 +4681,7 @@
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -4708,7 +4692,7 @@
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
     </row>
-    <row r="24" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
@@ -4719,7 +4703,7 @@
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -4730,7 +4714,7 @@
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
@@ -4741,7 +4725,7 @@
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
@@ -4752,7 +4736,7 @@
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
@@ -4763,7 +4747,7 @@
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
@@ -4774,7 +4758,7 @@
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
@@ -4785,7 +4769,7 @@
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
@@ -4796,7 +4780,7 @@
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
@@ -4807,7 +4791,7 @@
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
@@ -4818,7 +4802,7 @@
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
@@ -4832,7 +4816,7 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <dataConsolidate/>
-  <conditionalFormatting sqref="F8:I1048576 F1:I1 F3:I3 G2:I2 H4:J5">
+  <conditionalFormatting sqref="F12:I1048576 F1:I1 F3:I3 G2:I2 H4:J5">
     <cfRule type="iconSet" priority="282">
       <iconSet iconSet="3Symbols2" showValue="0">
         <cfvo type="percent" val="0"/>
@@ -4851,7 +4835,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:I8 H6:J7" xr:uid="{23AE6323-BC7F-40E9-A5AD-9DE77137CC3B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H6:J7" xr:uid="{23AE6323-BC7F-40E9-A5AD-9DE77137CC3B}">
       <formula1>"1,0"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4877,29 +4861,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R137"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="4" t="s">
         <v>257</v>
       </c>
@@ -4907,7 +4891,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -4915,7 +4899,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -4923,7 +4907,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -4931,13 +4915,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -4945,7 +4929,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -4960,7 +4944,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -4974,7 +4958,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -4988,7 +4972,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -5002,7 +4986,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -5016,7 +5000,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -5030,7 +5014,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -5044,7 +5028,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -5058,7 +5042,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -5072,7 +5056,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -5086,7 +5070,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -5100,7 +5084,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -5114,7 +5098,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -5128,7 +5112,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -5142,7 +5126,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -5156,7 +5140,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -5170,7 +5154,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -5184,7 +5168,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -5198,7 +5182,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -5212,7 +5196,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -5226,7 +5210,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -5240,7 +5224,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -5254,7 +5238,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -5268,7 +5252,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -5282,7 +5266,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -5296,7 +5280,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -5310,7 +5294,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -5324,7 +5308,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -5338,7 +5322,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -5352,7 +5336,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -5366,7 +5350,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -5380,7 +5364,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -5394,7 +5378,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -5408,7 +5392,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -5422,7 +5406,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -5436,7 +5420,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -5450,7 +5434,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -5464,7 +5448,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -5478,7 +5462,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -5492,7 +5476,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -5506,7 +5490,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -5520,7 +5504,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -5534,7 +5518,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -5548,7 +5532,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -5562,7 +5546,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -5576,7 +5560,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -5590,7 +5574,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="54" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -5604,7 +5588,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="55" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C55" s="3">
         <v>47</v>
       </c>
@@ -5618,12 +5602,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="57" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="34" t="s">
         <v>7</v>
       </c>
@@ -5637,7 +5621,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="59" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C59" s="36">
         <v>1</v>
       </c>
@@ -5651,7 +5635,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C60" s="39">
         <v>2</v>
       </c>
@@ -5665,7 +5649,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="61" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C61" s="36">
         <v>3</v>
       </c>
@@ -5679,7 +5663,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="62" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C62" s="39">
         <v>4</v>
       </c>
@@ -5693,7 +5677,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C63" s="36">
         <v>5</v>
       </c>
@@ -5707,7 +5691,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C64" s="39">
         <v>6</v>
       </c>
@@ -5721,7 +5705,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="65" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C65" s="36">
         <v>7</v>
       </c>
@@ -5735,7 +5719,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="66" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C66" s="39">
         <v>8</v>
       </c>
@@ -5749,7 +5733,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="67" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C67" s="36">
         <v>9</v>
       </c>
@@ -5763,7 +5747,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="68" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C68" s="39">
         <v>10</v>
       </c>
@@ -5777,7 +5761,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="69" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C69" s="36">
         <v>11</v>
       </c>
@@ -5791,7 +5775,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="70" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C70" s="39">
         <v>12</v>
       </c>
@@ -5805,7 +5789,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="71" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C71" s="36">
         <v>13</v>
       </c>
@@ -5819,7 +5803,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="72" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C72" s="39">
         <v>14</v>
       </c>
@@ -5833,7 +5817,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="73" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C73" s="36">
         <v>15</v>
       </c>
@@ -5847,7 +5831,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="74" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C74" s="39">
         <v>16</v>
       </c>
@@ -5861,7 +5845,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="75" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C75" s="36">
         <v>17</v>
       </c>
@@ -5875,7 +5859,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="76" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C76" s="39">
         <v>18</v>
       </c>
@@ -5889,7 +5873,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="77" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C77" s="36">
         <v>19</v>
       </c>
@@ -5903,7 +5887,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="78" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C78" s="39">
         <v>20</v>
       </c>
@@ -5917,7 +5901,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="79" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C79" s="36">
         <v>21</v>
       </c>
@@ -5931,7 +5915,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="80" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C80" s="39">
         <v>22</v>
       </c>
@@ -5945,7 +5929,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="81" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C81" s="36">
         <v>23</v>
       </c>
@@ -5959,7 +5943,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="82" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C82" s="39">
         <v>24</v>
       </c>
@@ -5973,7 +5957,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="83" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C83" s="36">
         <v>25</v>
       </c>
@@ -5987,7 +5971,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="84" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C84" s="39">
         <v>26</v>
       </c>
@@ -6001,7 +5985,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="85" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C85" s="36">
         <v>27</v>
       </c>
@@ -6015,7 +5999,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="86" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C86" s="39">
         <v>28</v>
       </c>
@@ -6029,7 +6013,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="87" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C87" s="36">
         <v>29</v>
       </c>
@@ -6043,7 +6027,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="88" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C88" s="39">
         <v>30</v>
       </c>
@@ -6057,7 +6041,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="89" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C89" s="36">
         <v>31</v>
       </c>
@@ -6071,7 +6055,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="90" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C90" s="39">
         <v>32</v>
       </c>
@@ -6085,7 +6069,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="91" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C91" s="36">
         <v>33</v>
       </c>
@@ -6099,7 +6083,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="92" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C92" s="39">
         <v>34</v>
       </c>
@@ -6113,7 +6097,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="93" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C93" s="36">
         <v>35</v>
       </c>
@@ -6127,7 +6111,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="94" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C94" s="39">
         <v>36</v>
       </c>
@@ -6141,7 +6125,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="95" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C95" s="36">
         <v>37</v>
       </c>
@@ -6155,7 +6139,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="96" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C96" s="39">
         <v>38</v>
       </c>
@@ -6169,7 +6153,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="97" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C97" s="36">
         <v>39</v>
       </c>
@@ -6183,7 +6167,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="98" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C98" s="39">
         <v>40</v>
       </c>
@@ -6197,7 +6181,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="99" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C99" s="36">
         <v>41</v>
       </c>
@@ -6211,7 +6195,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="100" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C100" s="39">
         <v>42</v>
       </c>
@@ -6225,7 +6209,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="101" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C101" s="36">
         <v>43</v>
       </c>
@@ -6239,7 +6223,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="102" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C102" s="39">
         <v>44</v>
       </c>
@@ -6253,7 +6237,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="103" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C103" s="36">
         <v>45</v>
       </c>
@@ -6267,7 +6251,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="104" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C104" s="39">
         <v>46</v>
       </c>
@@ -6281,7 +6265,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="105" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C105" s="36">
         <v>47</v>
       </c>
@@ -6295,7 +6279,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="106" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C106" s="39">
         <v>48</v>
       </c>
@@ -6309,7 +6293,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="107" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C107" s="36">
         <v>49</v>
       </c>
@@ -6323,7 +6307,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="108" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C108" s="39">
         <v>50</v>
       </c>
@@ -6337,7 +6321,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="109" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C109" s="36">
         <v>51</v>
       </c>
@@ -6351,7 +6335,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="110" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C110" s="39">
         <v>52</v>
       </c>
@@ -6365,7 +6349,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="111" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C111" s="36">
         <v>53</v>
       </c>
@@ -6379,7 +6363,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="112" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C112" s="39">
         <v>54</v>
       </c>
@@ -6393,7 +6377,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="113" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C113" s="36">
         <v>55</v>
       </c>
@@ -6407,7 +6391,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="114" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C114" s="39">
         <v>56</v>
       </c>
@@ -6421,7 +6405,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="115" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C115" s="36">
         <v>57</v>
       </c>
@@ -6435,7 +6419,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="116" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C116" s="39">
         <v>58</v>
       </c>
@@ -6449,7 +6433,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="117" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C117" s="36">
         <v>59</v>
       </c>
@@ -6463,7 +6447,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="118" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C118" s="39">
         <v>60</v>
       </c>
@@ -6477,7 +6461,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="119" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C119" s="36">
         <v>61</v>
       </c>
@@ -6491,7 +6475,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="120" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C120" s="39">
         <v>62</v>
       </c>
@@ -6505,7 +6489,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="121" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C121" s="36">
         <v>63</v>
       </c>
@@ -6519,7 +6503,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="122" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C122" s="39">
         <v>64</v>
       </c>
@@ -6533,7 +6517,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="123" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C123" s="36">
         <v>65</v>
       </c>
@@ -6547,7 +6531,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="124" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C124" s="39">
         <v>66</v>
       </c>
@@ -6561,7 +6545,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="125" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C125" s="36">
         <v>67</v>
       </c>
@@ -6575,7 +6559,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="126" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C126" s="39">
         <v>68</v>
       </c>
@@ -6589,7 +6573,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="127" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C127" s="36">
         <v>69</v>
       </c>
@@ -6603,7 +6587,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="128" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C128" s="39">
         <v>70</v>
       </c>
@@ -6617,7 +6601,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="129" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C129" s="36">
         <v>71</v>
       </c>
@@ -6631,7 +6615,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="130" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C130" s="39">
         <v>72</v>
       </c>
@@ -6645,7 +6629,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="131" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C131" s="36">
         <v>73</v>
       </c>
@@ -6659,7 +6643,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="132" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C132" s="39">
         <v>74</v>
       </c>
@@ -6673,7 +6657,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="133" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C133" s="36">
         <v>75</v>
       </c>
@@ -6687,7 +6671,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="134" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C134" s="39">
         <v>76</v>
       </c>
@@ -6701,7 +6685,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="135" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C135" s="36">
         <v>77</v>
       </c>
@@ -6715,7 +6699,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="136" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C136" s="39">
         <v>78</v>
       </c>
@@ -6729,7 +6713,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="137" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="137" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C137" s="3">
         <v>79</v>
       </c>
@@ -6766,29 +6750,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R138"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="13" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="14" max="15" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="14" max="15" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="16" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="4" t="s">
         <v>258</v>
       </c>
@@ -6796,7 +6780,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -6804,7 +6788,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -6812,7 +6796,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -6820,13 +6804,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -6834,7 +6818,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -6849,7 +6833,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -6863,7 +6847,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -6877,7 +6861,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -6891,7 +6875,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -6905,7 +6889,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -6919,7 +6903,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -6933,7 +6917,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -6947,7 +6931,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -6961,7 +6945,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -6975,7 +6959,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -6989,7 +6973,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -7003,7 +6987,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -7017,7 +7001,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -7031,7 +7015,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -7045,7 +7029,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -7059,7 +7043,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -7073,7 +7057,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -7087,7 +7071,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -7101,7 +7085,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -7115,7 +7099,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -7129,7 +7113,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -7143,7 +7127,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -7157,7 +7141,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -7171,7 +7155,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -7185,7 +7169,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -7199,7 +7183,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -7213,7 +7197,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -7227,7 +7211,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -7241,7 +7225,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -7255,7 +7239,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -7269,7 +7253,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -7283,7 +7267,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -7297,7 +7281,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -7311,7 +7295,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -7325,7 +7309,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -7339,7 +7323,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -7353,7 +7337,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -7367,7 +7351,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -7381,7 +7365,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -7395,7 +7379,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -7409,7 +7393,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -7423,7 +7407,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -7437,7 +7421,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -7451,7 +7435,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -7465,7 +7449,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -7479,7 +7463,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -7493,12 +7477,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="34" t="s">
         <v>7</v>
       </c>
@@ -7512,7 +7496,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="36">
         <v>1</v>
       </c>
@@ -7526,7 +7510,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C59" s="39">
         <v>2</v>
       </c>
@@ -7540,7 +7524,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C60" s="36">
         <v>3</v>
       </c>
@@ -7554,7 +7538,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C61" s="39">
         <v>4</v>
       </c>
@@ -7568,7 +7552,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C62" s="36">
         <v>5</v>
       </c>
@@ -7582,7 +7566,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C63" s="39">
         <v>6</v>
       </c>
@@ -7596,7 +7580,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="30"/>
       <c r="B64" s="28"/>
       <c r="C64" s="36">
@@ -7617,7 +7601,7 @@
       <c r="J64" s="30"/>
       <c r="K64" s="30"/>
     </row>
-    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="30"/>
       <c r="B65" s="28"/>
       <c r="C65" s="39">
@@ -7638,7 +7622,7 @@
       <c r="J65" s="30"/>
       <c r="K65" s="30"/>
     </row>
-    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="30"/>
       <c r="B66" s="28"/>
       <c r="C66" s="36">
@@ -7659,7 +7643,7 @@
       <c r="J66" s="30"/>
       <c r="K66" s="30"/>
     </row>
-    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="30"/>
       <c r="B67" s="28"/>
       <c r="C67" s="39">
@@ -7680,7 +7664,7 @@
       <c r="J67" s="30"/>
       <c r="K67" s="30"/>
     </row>
-    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="30"/>
       <c r="B68" s="28"/>
       <c r="C68" s="36">
@@ -7701,7 +7685,7 @@
       <c r="J68" s="30"/>
       <c r="K68" s="30"/>
     </row>
-    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="30"/>
       <c r="B69" s="28"/>
       <c r="C69" s="39">
@@ -7722,7 +7706,7 @@
       <c r="J69" s="30"/>
       <c r="K69" s="30"/>
     </row>
-    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="30"/>
       <c r="B70" s="28"/>
       <c r="C70" s="36">
@@ -7743,7 +7727,7 @@
       <c r="J70" s="30"/>
       <c r="K70" s="30"/>
     </row>
-    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="30"/>
       <c r="B71" s="28"/>
       <c r="C71" s="39">
@@ -7764,7 +7748,7 @@
       <c r="J71" s="30"/>
       <c r="K71" s="30"/>
     </row>
-    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="30"/>
       <c r="B72" s="28"/>
       <c r="C72" s="36">
@@ -7785,7 +7769,7 @@
       <c r="J72" s="30"/>
       <c r="K72" s="30"/>
     </row>
-    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="30"/>
       <c r="B73" s="28"/>
       <c r="C73" s="39">
@@ -7806,7 +7790,7 @@
       <c r="J73" s="30"/>
       <c r="K73" s="30"/>
     </row>
-    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="30"/>
       <c r="B74" s="28"/>
       <c r="C74" s="36">
@@ -7827,7 +7811,7 @@
       <c r="J74" s="30"/>
       <c r="K74" s="30"/>
     </row>
-    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="30"/>
       <c r="B75" s="28"/>
       <c r="C75" s="39">
@@ -7848,7 +7832,7 @@
       <c r="J75" s="30"/>
       <c r="K75" s="30"/>
     </row>
-    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="30"/>
       <c r="B76" s="28"/>
       <c r="C76" s="36">
@@ -7869,7 +7853,7 @@
       <c r="J76" s="30"/>
       <c r="K76" s="30"/>
     </row>
-    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="30"/>
       <c r="B77" s="28"/>
       <c r="C77" s="39">
@@ -7890,7 +7874,7 @@
       <c r="J77" s="30"/>
       <c r="K77" s="30"/>
     </row>
-    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="30"/>
       <c r="B78" s="28"/>
       <c r="C78" s="36">
@@ -7911,7 +7895,7 @@
       <c r="J78" s="30"/>
       <c r="K78" s="30"/>
     </row>
-    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="30"/>
       <c r="B79" s="28"/>
       <c r="C79" s="39">
@@ -7932,7 +7916,7 @@
       <c r="J79" s="30"/>
       <c r="K79" s="30"/>
     </row>
-    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="30"/>
       <c r="B80" s="28"/>
       <c r="C80" s="36">
@@ -7953,7 +7937,7 @@
       <c r="J80" s="30"/>
       <c r="K80" s="30"/>
     </row>
-    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="30"/>
       <c r="B81" s="28"/>
       <c r="C81" s="39">
@@ -7974,7 +7958,7 @@
       <c r="J81" s="30"/>
       <c r="K81" s="30"/>
     </row>
-    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="30"/>
       <c r="B82" s="28"/>
       <c r="C82" s="36">
@@ -7995,7 +7979,7 @@
       <c r="J82" s="30"/>
       <c r="K82" s="30"/>
     </row>
-    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="30"/>
       <c r="B83" s="28"/>
       <c r="C83" s="39">
@@ -8016,7 +8000,7 @@
       <c r="J83" s="30"/>
       <c r="K83" s="30"/>
     </row>
-    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="30"/>
       <c r="B84" s="28"/>
       <c r="C84" s="36">
@@ -8037,7 +8021,7 @@
       <c r="J84" s="30"/>
       <c r="K84" s="30"/>
     </row>
-    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="30"/>
       <c r="B85" s="28"/>
       <c r="C85" s="39">
@@ -8058,7 +8042,7 @@
       <c r="J85" s="30"/>
       <c r="K85" s="30"/>
     </row>
-    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="30"/>
       <c r="B86" s="28"/>
       <c r="C86" s="36">
@@ -8079,7 +8063,7 @@
       <c r="J86" s="30"/>
       <c r="K86" s="30"/>
     </row>
-    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="30"/>
       <c r="B87" s="28"/>
       <c r="C87" s="39">
@@ -8100,7 +8084,7 @@
       <c r="J87" s="30"/>
       <c r="K87" s="30"/>
     </row>
-    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="30"/>
       <c r="B88" s="28"/>
       <c r="C88" s="36">
@@ -8121,7 +8105,7 @@
       <c r="J88" s="30"/>
       <c r="K88" s="30"/>
     </row>
-    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="30"/>
       <c r="B89" s="28"/>
       <c r="C89" s="39">
@@ -8142,7 +8126,7 @@
       <c r="J89" s="30"/>
       <c r="K89" s="30"/>
     </row>
-    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="30"/>
       <c r="B90" s="28"/>
       <c r="C90" s="36">
@@ -8163,7 +8147,7 @@
       <c r="J90" s="30"/>
       <c r="K90" s="30"/>
     </row>
-    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="30"/>
       <c r="B91" s="28"/>
       <c r="C91" s="39">
@@ -8184,7 +8168,7 @@
       <c r="J91" s="30"/>
       <c r="K91" s="30"/>
     </row>
-    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="30"/>
       <c r="B92" s="28"/>
       <c r="C92" s="36">
@@ -8205,7 +8189,7 @@
       <c r="J92" s="30"/>
       <c r="K92" s="30"/>
     </row>
-    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="30"/>
       <c r="B93" s="28"/>
       <c r="C93" s="39">
@@ -8226,7 +8210,7 @@
       <c r="J93" s="30"/>
       <c r="K93" s="30"/>
     </row>
-    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="30"/>
       <c r="B94" s="28"/>
       <c r="C94" s="36">
@@ -8247,7 +8231,7 @@
       <c r="J94" s="30"/>
       <c r="K94" s="30"/>
     </row>
-    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="30"/>
       <c r="B95" s="28"/>
       <c r="C95" s="39">
@@ -8268,7 +8252,7 @@
       <c r="J95" s="30"/>
       <c r="K95" s="30"/>
     </row>
-    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="30"/>
       <c r="B96" s="28"/>
       <c r="C96" s="36">
@@ -8289,7 +8273,7 @@
       <c r="J96" s="30"/>
       <c r="K96" s="30"/>
     </row>
-    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="30"/>
       <c r="B97" s="28"/>
       <c r="C97" s="39">
@@ -8310,7 +8294,7 @@
       <c r="J97" s="30"/>
       <c r="K97" s="30"/>
     </row>
-    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="30"/>
       <c r="B98" s="28"/>
       <c r="C98" s="36">
@@ -8331,7 +8315,7 @@
       <c r="J98" s="30"/>
       <c r="K98" s="30"/>
     </row>
-    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="30"/>
       <c r="B99" s="28"/>
       <c r="C99" s="39">
@@ -8352,7 +8336,7 @@
       <c r="J99" s="30"/>
       <c r="K99" s="30"/>
     </row>
-    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="30"/>
       <c r="B100" s="28"/>
       <c r="C100" s="36">
@@ -8373,7 +8357,7 @@
       <c r="J100" s="30"/>
       <c r="K100" s="30"/>
     </row>
-    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="30"/>
       <c r="B101" s="28"/>
       <c r="C101" s="39">
@@ -8394,7 +8378,7 @@
       <c r="J101" s="30"/>
       <c r="K101" s="30"/>
     </row>
-    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="30"/>
       <c r="B102" s="28"/>
       <c r="C102" s="36">
@@ -8415,7 +8399,7 @@
       <c r="J102" s="30"/>
       <c r="K102" s="30"/>
     </row>
-    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="30"/>
       <c r="B103" s="28"/>
       <c r="C103" s="39">
@@ -8436,7 +8420,7 @@
       <c r="J103" s="30"/>
       <c r="K103" s="30"/>
     </row>
-    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="30"/>
       <c r="B104" s="28"/>
       <c r="C104" s="36">
@@ -8457,7 +8441,7 @@
       <c r="J104" s="30"/>
       <c r="K104" s="30"/>
     </row>
-    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="30"/>
       <c r="B105" s="28"/>
       <c r="C105" s="39">
@@ -8478,7 +8462,7 @@
       <c r="J105" s="30"/>
       <c r="K105" s="30"/>
     </row>
-    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="30"/>
       <c r="B106" s="28"/>
       <c r="C106" s="36">
@@ -8499,7 +8483,7 @@
       <c r="J106" s="30"/>
       <c r="K106" s="30"/>
     </row>
-    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="30"/>
       <c r="B107" s="28"/>
       <c r="C107" s="39">
@@ -8520,7 +8504,7 @@
       <c r="J107" s="30"/>
       <c r="K107" s="30"/>
     </row>
-    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="30"/>
       <c r="B108" s="28"/>
       <c r="C108" s="36">
@@ -8541,7 +8525,7 @@
       <c r="J108" s="30"/>
       <c r="K108" s="30"/>
     </row>
-    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="30"/>
       <c r="B109" s="28"/>
       <c r="C109" s="39">
@@ -8562,7 +8546,7 @@
       <c r="J109" s="30"/>
       <c r="K109" s="30"/>
     </row>
-    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="30"/>
       <c r="B110" s="28"/>
       <c r="C110" s="36">
@@ -8583,7 +8567,7 @@
       <c r="J110" s="30"/>
       <c r="K110" s="30"/>
     </row>
-    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="30"/>
       <c r="B111" s="28"/>
       <c r="C111" s="39">
@@ -8604,7 +8588,7 @@
       <c r="J111" s="30"/>
       <c r="K111" s="30"/>
     </row>
-    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="30"/>
       <c r="B112" s="28"/>
       <c r="C112" s="36">
@@ -8625,7 +8609,7 @@
       <c r="J112" s="30"/>
       <c r="K112" s="30"/>
     </row>
-    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="30"/>
       <c r="B113" s="28"/>
       <c r="C113" s="39">
@@ -8646,7 +8630,7 @@
       <c r="J113" s="30"/>
       <c r="K113" s="30"/>
     </row>
-    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="30"/>
       <c r="B114" s="28"/>
       <c r="C114" s="36">
@@ -8667,7 +8651,7 @@
       <c r="J114" s="30"/>
       <c r="K114" s="30"/>
     </row>
-    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="30"/>
       <c r="B115" s="28"/>
       <c r="C115" s="39">
@@ -8688,7 +8672,7 @@
       <c r="J115" s="30"/>
       <c r="K115" s="30"/>
     </row>
-    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="30"/>
       <c r="B116" s="28"/>
       <c r="C116" s="36">
@@ -8709,7 +8693,7 @@
       <c r="J116" s="30"/>
       <c r="K116" s="30"/>
     </row>
-    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="30"/>
       <c r="B117" s="28"/>
       <c r="C117" s="39">
@@ -8730,7 +8714,7 @@
       <c r="J117" s="30"/>
       <c r="K117" s="30"/>
     </row>
-    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="30"/>
       <c r="B118" s="28"/>
       <c r="C118" s="36">
@@ -8751,7 +8735,7 @@
       <c r="J118" s="30"/>
       <c r="K118" s="30"/>
     </row>
-    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="30"/>
       <c r="B119" s="28"/>
       <c r="C119" s="39">
@@ -8772,7 +8756,7 @@
       <c r="J119" s="30"/>
       <c r="K119" s="30"/>
     </row>
-    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="30"/>
       <c r="B120" s="28"/>
       <c r="C120" s="36">
@@ -8793,7 +8777,7 @@
       <c r="J120" s="30"/>
       <c r="K120" s="30"/>
     </row>
-    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="30"/>
       <c r="B121" s="28"/>
       <c r="C121" s="39">
@@ -8814,7 +8798,7 @@
       <c r="J121" s="30"/>
       <c r="K121" s="30"/>
     </row>
-    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="30"/>
       <c r="B122" s="28"/>
       <c r="C122" s="36">
@@ -8835,7 +8819,7 @@
       <c r="J122" s="30"/>
       <c r="K122" s="30"/>
     </row>
-    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="30"/>
       <c r="B123" s="28"/>
       <c r="C123" s="39">
@@ -8856,7 +8840,7 @@
       <c r="J123" s="30"/>
       <c r="K123" s="30"/>
     </row>
-    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="30"/>
       <c r="B124" s="28"/>
       <c r="C124" s="36">
@@ -8877,7 +8861,7 @@
       <c r="J124" s="30"/>
       <c r="K124" s="30"/>
     </row>
-    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="30"/>
       <c r="B125" s="28"/>
       <c r="C125" s="39">
@@ -8898,7 +8882,7 @@
       <c r="J125" s="30"/>
       <c r="K125" s="30"/>
     </row>
-    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="30"/>
       <c r="B126" s="28"/>
       <c r="C126" s="36">
@@ -8919,7 +8903,7 @@
       <c r="J126" s="30"/>
       <c r="K126" s="30"/>
     </row>
-    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="30"/>
       <c r="B127" s="28"/>
       <c r="C127" s="39">
@@ -8940,7 +8924,7 @@
       <c r="J127" s="30"/>
       <c r="K127" s="30"/>
     </row>
-    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="30"/>
       <c r="B128" s="28"/>
       <c r="C128" s="36">
@@ -8961,7 +8945,7 @@
       <c r="J128" s="30"/>
       <c r="K128" s="30"/>
     </row>
-    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="30"/>
       <c r="B129" s="28"/>
       <c r="C129" s="39">
@@ -8982,7 +8966,7 @@
       <c r="J129" s="30"/>
       <c r="K129" s="30"/>
     </row>
-    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="30"/>
       <c r="B130" s="28"/>
       <c r="C130" s="36">
@@ -9003,7 +8987,7 @@
       <c r="J130" s="30"/>
       <c r="K130" s="30"/>
     </row>
-    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="30"/>
       <c r="B131" s="28"/>
       <c r="C131" s="39">
@@ -9024,7 +9008,7 @@
       <c r="J131" s="30"/>
       <c r="K131" s="30"/>
     </row>
-    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="30"/>
       <c r="B132" s="28"/>
       <c r="C132" s="36">
@@ -9045,7 +9029,7 @@
       <c r="J132" s="30"/>
       <c r="K132" s="30"/>
     </row>
-    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C133" s="39">
         <v>76</v>
       </c>
@@ -9059,7 +9043,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C134" s="36">
         <v>77</v>
       </c>
@@ -9073,7 +9057,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C135" s="39">
         <v>78</v>
       </c>
@@ -9087,7 +9071,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C136" s="36">
         <v>79</v>
       </c>
@@ -9101,7 +9085,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C137" s="39">
         <v>80</v>
       </c>
@@ -9115,7 +9099,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="138" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C138" s="36">
         <v>81</v>
       </c>
@@ -9152,29 +9136,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R138"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="4" t="s">
         <v>259</v>
       </c>
@@ -9182,7 +9166,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -9190,7 +9174,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -9198,7 +9182,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -9206,13 +9190,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -9220,7 +9204,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -9235,7 +9219,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -9249,7 +9233,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -9263,7 +9247,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -9277,7 +9261,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -9291,7 +9275,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -9305,7 +9289,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -9319,7 +9303,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -9333,7 +9317,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -9347,7 +9331,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -9361,7 +9345,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -9375,7 +9359,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -9389,7 +9373,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -9403,7 +9387,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -9417,7 +9401,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -9431,7 +9415,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -9445,7 +9429,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -9459,7 +9443,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -9473,7 +9457,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -9487,7 +9471,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -9501,7 +9485,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -9515,7 +9499,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -9529,7 +9513,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -9543,7 +9527,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -9557,7 +9541,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -9571,7 +9555,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -9585,7 +9569,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -9599,7 +9583,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -9613,7 +9597,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -9627,7 +9611,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -9641,7 +9625,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -9655,7 +9639,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -9669,7 +9653,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -9683,7 +9667,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -9697,7 +9681,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -9711,7 +9695,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -9725,7 +9709,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -9739,7 +9723,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -9753,7 +9737,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -9767,7 +9751,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -9781,7 +9765,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -9795,7 +9779,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -9809,7 +9793,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -9823,7 +9807,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -9837,7 +9821,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -9851,7 +9835,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -9865,7 +9849,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -9879,12 +9863,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="34" t="s">
         <v>7</v>
       </c>
@@ -9898,7 +9882,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="36">
         <v>1</v>
       </c>
@@ -9912,7 +9896,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C59" s="39">
         <v>2</v>
       </c>
@@ -9926,7 +9910,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C60" s="36">
         <v>3</v>
       </c>
@@ -9940,7 +9924,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C61" s="39">
         <v>4</v>
       </c>
@@ -9954,7 +9938,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C62" s="36">
         <v>5</v>
       </c>
@@ -9968,7 +9952,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C63" s="39">
         <v>6</v>
       </c>
@@ -9982,7 +9966,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="30"/>
       <c r="B64" s="28"/>
       <c r="C64" s="36">
@@ -10003,7 +9987,7 @@
       <c r="J64" s="30"/>
       <c r="K64" s="30"/>
     </row>
-    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="30"/>
       <c r="B65" s="28"/>
       <c r="C65" s="39">
@@ -10024,7 +10008,7 @@
       <c r="J65" s="30"/>
       <c r="K65" s="30"/>
     </row>
-    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="30"/>
       <c r="B66" s="28"/>
       <c r="C66" s="36">
@@ -10045,7 +10029,7 @@
       <c r="J66" s="30"/>
       <c r="K66" s="30"/>
     </row>
-    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="30"/>
       <c r="B67" s="28"/>
       <c r="C67" s="39">
@@ -10066,7 +10050,7 @@
       <c r="J67" s="30"/>
       <c r="K67" s="30"/>
     </row>
-    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="30"/>
       <c r="B68" s="28"/>
       <c r="C68" s="36">
@@ -10087,7 +10071,7 @@
       <c r="J68" s="30"/>
       <c r="K68" s="30"/>
     </row>
-    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="30"/>
       <c r="B69" s="28"/>
       <c r="C69" s="39">
@@ -10108,7 +10092,7 @@
       <c r="J69" s="30"/>
       <c r="K69" s="30"/>
     </row>
-    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="30"/>
       <c r="B70" s="28"/>
       <c r="C70" s="36">
@@ -10129,7 +10113,7 @@
       <c r="J70" s="30"/>
       <c r="K70" s="30"/>
     </row>
-    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="30"/>
       <c r="B71" s="28"/>
       <c r="C71" s="39">
@@ -10150,7 +10134,7 @@
       <c r="J71" s="30"/>
       <c r="K71" s="30"/>
     </row>
-    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="30"/>
       <c r="B72" s="28"/>
       <c r="C72" s="36">
@@ -10171,7 +10155,7 @@
       <c r="J72" s="30"/>
       <c r="K72" s="30"/>
     </row>
-    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="30"/>
       <c r="B73" s="28"/>
       <c r="C73" s="39">
@@ -10192,7 +10176,7 @@
       <c r="J73" s="30"/>
       <c r="K73" s="30"/>
     </row>
-    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="30"/>
       <c r="B74" s="28"/>
       <c r="C74" s="36">
@@ -10213,7 +10197,7 @@
       <c r="J74" s="30"/>
       <c r="K74" s="30"/>
     </row>
-    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="30"/>
       <c r="B75" s="28"/>
       <c r="C75" s="39">
@@ -10234,7 +10218,7 @@
       <c r="J75" s="30"/>
       <c r="K75" s="30"/>
     </row>
-    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="30"/>
       <c r="B76" s="28"/>
       <c r="C76" s="36">
@@ -10255,7 +10239,7 @@
       <c r="J76" s="30"/>
       <c r="K76" s="30"/>
     </row>
-    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="30"/>
       <c r="B77" s="28"/>
       <c r="C77" s="39">
@@ -10276,7 +10260,7 @@
       <c r="J77" s="30"/>
       <c r="K77" s="30"/>
     </row>
-    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="30"/>
       <c r="B78" s="28"/>
       <c r="C78" s="36">
@@ -10297,7 +10281,7 @@
       <c r="J78" s="30"/>
       <c r="K78" s="30"/>
     </row>
-    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="30"/>
       <c r="B79" s="28"/>
       <c r="C79" s="39">
@@ -10318,7 +10302,7 @@
       <c r="J79" s="30"/>
       <c r="K79" s="30"/>
     </row>
-    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="30"/>
       <c r="B80" s="28"/>
       <c r="C80" s="36">
@@ -10339,7 +10323,7 @@
       <c r="J80" s="30"/>
       <c r="K80" s="30"/>
     </row>
-    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="30"/>
       <c r="B81" s="28"/>
       <c r="C81" s="39">
@@ -10360,7 +10344,7 @@
       <c r="J81" s="30"/>
       <c r="K81" s="30"/>
     </row>
-    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="30"/>
       <c r="B82" s="28"/>
       <c r="C82" s="36">
@@ -10381,7 +10365,7 @@
       <c r="J82" s="30"/>
       <c r="K82" s="30"/>
     </row>
-    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="30"/>
       <c r="B83" s="28"/>
       <c r="C83" s="39">
@@ -10402,7 +10386,7 @@
       <c r="J83" s="30"/>
       <c r="K83" s="30"/>
     </row>
-    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="30"/>
       <c r="B84" s="28"/>
       <c r="C84" s="36">
@@ -10423,7 +10407,7 @@
       <c r="J84" s="30"/>
       <c r="K84" s="30"/>
     </row>
-    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="30"/>
       <c r="B85" s="28"/>
       <c r="C85" s="39">
@@ -10444,7 +10428,7 @@
       <c r="J85" s="30"/>
       <c r="K85" s="30"/>
     </row>
-    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="30"/>
       <c r="B86" s="28"/>
       <c r="C86" s="36">
@@ -10465,7 +10449,7 @@
       <c r="J86" s="30"/>
       <c r="K86" s="30"/>
     </row>
-    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="30"/>
       <c r="B87" s="28"/>
       <c r="C87" s="39">
@@ -10486,7 +10470,7 @@
       <c r="J87" s="30"/>
       <c r="K87" s="30"/>
     </row>
-    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="30"/>
       <c r="B88" s="28"/>
       <c r="C88" s="36">
@@ -10507,7 +10491,7 @@
       <c r="J88" s="30"/>
       <c r="K88" s="30"/>
     </row>
-    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="30"/>
       <c r="B89" s="28"/>
       <c r="C89" s="39">
@@ -10528,7 +10512,7 @@
       <c r="J89" s="30"/>
       <c r="K89" s="30"/>
     </row>
-    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="30"/>
       <c r="B90" s="28"/>
       <c r="C90" s="36">
@@ -10549,7 +10533,7 @@
       <c r="J90" s="30"/>
       <c r="K90" s="30"/>
     </row>
-    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="30"/>
       <c r="B91" s="28"/>
       <c r="C91" s="39">
@@ -10570,7 +10554,7 @@
       <c r="J91" s="30"/>
       <c r="K91" s="30"/>
     </row>
-    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="30"/>
       <c r="B92" s="28"/>
       <c r="C92" s="36">
@@ -10591,7 +10575,7 @@
       <c r="J92" s="30"/>
       <c r="K92" s="30"/>
     </row>
-    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="30"/>
       <c r="B93" s="28"/>
       <c r="C93" s="39">
@@ -10612,7 +10596,7 @@
       <c r="J93" s="30"/>
       <c r="K93" s="30"/>
     </row>
-    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="30"/>
       <c r="B94" s="28"/>
       <c r="C94" s="36">
@@ -10633,7 +10617,7 @@
       <c r="J94" s="30"/>
       <c r="K94" s="30"/>
     </row>
-    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="30"/>
       <c r="B95" s="28"/>
       <c r="C95" s="39">
@@ -10654,7 +10638,7 @@
       <c r="J95" s="30"/>
       <c r="K95" s="30"/>
     </row>
-    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="30"/>
       <c r="B96" s="28"/>
       <c r="C96" s="36">
@@ -10675,7 +10659,7 @@
       <c r="J96" s="30"/>
       <c r="K96" s="30"/>
     </row>
-    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="30"/>
       <c r="B97" s="28"/>
       <c r="C97" s="39">
@@ -10696,7 +10680,7 @@
       <c r="J97" s="30"/>
       <c r="K97" s="30"/>
     </row>
-    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="30"/>
       <c r="B98" s="28"/>
       <c r="C98" s="36">
@@ -10717,7 +10701,7 @@
       <c r="J98" s="30"/>
       <c r="K98" s="30"/>
     </row>
-    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="30"/>
       <c r="B99" s="28"/>
       <c r="C99" s="39">
@@ -10738,7 +10722,7 @@
       <c r="J99" s="30"/>
       <c r="K99" s="30"/>
     </row>
-    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="30"/>
       <c r="B100" s="28"/>
       <c r="C100" s="36">
@@ -10759,7 +10743,7 @@
       <c r="J100" s="30"/>
       <c r="K100" s="30"/>
     </row>
-    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="30"/>
       <c r="B101" s="28"/>
       <c r="C101" s="39">
@@ -10780,7 +10764,7 @@
       <c r="J101" s="30"/>
       <c r="K101" s="30"/>
     </row>
-    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="30"/>
       <c r="B102" s="28"/>
       <c r="C102" s="36">
@@ -10801,7 +10785,7 @@
       <c r="J102" s="30"/>
       <c r="K102" s="30"/>
     </row>
-    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="30"/>
       <c r="B103" s="28"/>
       <c r="C103" s="39">
@@ -10822,7 +10806,7 @@
       <c r="J103" s="30"/>
       <c r="K103" s="30"/>
     </row>
-    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="30"/>
       <c r="B104" s="28"/>
       <c r="C104" s="36">
@@ -10843,7 +10827,7 @@
       <c r="J104" s="30"/>
       <c r="K104" s="30"/>
     </row>
-    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="30"/>
       <c r="B105" s="28"/>
       <c r="C105" s="39">
@@ -10864,7 +10848,7 @@
       <c r="J105" s="30"/>
       <c r="K105" s="30"/>
     </row>
-    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="30"/>
       <c r="B106" s="28"/>
       <c r="C106" s="36">
@@ -10885,7 +10869,7 @@
       <c r="J106" s="30"/>
       <c r="K106" s="30"/>
     </row>
-    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="30"/>
       <c r="B107" s="28"/>
       <c r="C107" s="39">
@@ -10906,7 +10890,7 @@
       <c r="J107" s="30"/>
       <c r="K107" s="30"/>
     </row>
-    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="30"/>
       <c r="B108" s="28"/>
       <c r="C108" s="36">
@@ -10927,7 +10911,7 @@
       <c r="J108" s="30"/>
       <c r="K108" s="30"/>
     </row>
-    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="30"/>
       <c r="B109" s="28"/>
       <c r="C109" s="39">
@@ -10948,7 +10932,7 @@
       <c r="J109" s="30"/>
       <c r="K109" s="30"/>
     </row>
-    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="30"/>
       <c r="B110" s="28"/>
       <c r="C110" s="36">
@@ -10969,7 +10953,7 @@
       <c r="J110" s="30"/>
       <c r="K110" s="30"/>
     </row>
-    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="30"/>
       <c r="B111" s="28"/>
       <c r="C111" s="39">
@@ -10990,7 +10974,7 @@
       <c r="J111" s="30"/>
       <c r="K111" s="30"/>
     </row>
-    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="30"/>
       <c r="B112" s="28"/>
       <c r="C112" s="36">
@@ -11011,7 +10995,7 @@
       <c r="J112" s="30"/>
       <c r="K112" s="30"/>
     </row>
-    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="30"/>
       <c r="B113" s="28"/>
       <c r="C113" s="39">
@@ -11032,7 +11016,7 @@
       <c r="J113" s="30"/>
       <c r="K113" s="30"/>
     </row>
-    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="30"/>
       <c r="B114" s="28"/>
       <c r="C114" s="36">
@@ -11053,7 +11037,7 @@
       <c r="J114" s="30"/>
       <c r="K114" s="30"/>
     </row>
-    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="30"/>
       <c r="B115" s="28"/>
       <c r="C115" s="39">
@@ -11074,7 +11058,7 @@
       <c r="J115" s="30"/>
       <c r="K115" s="30"/>
     </row>
-    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="30"/>
       <c r="B116" s="28"/>
       <c r="C116" s="36">
@@ -11095,7 +11079,7 @@
       <c r="J116" s="30"/>
       <c r="K116" s="30"/>
     </row>
-    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="30"/>
       <c r="B117" s="28"/>
       <c r="C117" s="39">
@@ -11116,7 +11100,7 @@
       <c r="J117" s="30"/>
       <c r="K117" s="30"/>
     </row>
-    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="30"/>
       <c r="B118" s="28"/>
       <c r="C118" s="36">
@@ -11137,7 +11121,7 @@
       <c r="J118" s="30"/>
       <c r="K118" s="30"/>
     </row>
-    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="30"/>
       <c r="B119" s="28"/>
       <c r="C119" s="39">
@@ -11158,7 +11142,7 @@
       <c r="J119" s="30"/>
       <c r="K119" s="30"/>
     </row>
-    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="30"/>
       <c r="B120" s="28"/>
       <c r="C120" s="36">
@@ -11179,7 +11163,7 @@
       <c r="J120" s="30"/>
       <c r="K120" s="30"/>
     </row>
-    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="30"/>
       <c r="B121" s="28"/>
       <c r="C121" s="39">
@@ -11200,7 +11184,7 @@
       <c r="J121" s="30"/>
       <c r="K121" s="30"/>
     </row>
-    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="30"/>
       <c r="B122" s="28"/>
       <c r="C122" s="36">
@@ -11221,7 +11205,7 @@
       <c r="J122" s="30"/>
       <c r="K122" s="30"/>
     </row>
-    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="30"/>
       <c r="B123" s="28"/>
       <c r="C123" s="39">
@@ -11242,7 +11226,7 @@
       <c r="J123" s="30"/>
       <c r="K123" s="30"/>
     </row>
-    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="30"/>
       <c r="B124" s="28"/>
       <c r="C124" s="36">
@@ -11263,7 +11247,7 @@
       <c r="J124" s="30"/>
       <c r="K124" s="30"/>
     </row>
-    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="30"/>
       <c r="B125" s="28"/>
       <c r="C125" s="39">
@@ -11284,7 +11268,7 @@
       <c r="J125" s="30"/>
       <c r="K125" s="30"/>
     </row>
-    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="30"/>
       <c r="B126" s="28"/>
       <c r="C126" s="36">
@@ -11305,7 +11289,7 @@
       <c r="J126" s="30"/>
       <c r="K126" s="30"/>
     </row>
-    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="30"/>
       <c r="B127" s="28"/>
       <c r="C127" s="39">
@@ -11326,7 +11310,7 @@
       <c r="J127" s="30"/>
       <c r="K127" s="30"/>
     </row>
-    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="30"/>
       <c r="B128" s="28"/>
       <c r="C128" s="36">
@@ -11347,7 +11331,7 @@
       <c r="J128" s="30"/>
       <c r="K128" s="30"/>
     </row>
-    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="30"/>
       <c r="B129" s="28"/>
       <c r="C129" s="39">
@@ -11368,7 +11352,7 @@
       <c r="J129" s="30"/>
       <c r="K129" s="30"/>
     </row>
-    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="30"/>
       <c r="B130" s="28"/>
       <c r="C130" s="36">
@@ -11389,7 +11373,7 @@
       <c r="J130" s="30"/>
       <c r="K130" s="30"/>
     </row>
-    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="30"/>
       <c r="B131" s="28"/>
       <c r="C131" s="39">
@@ -11410,7 +11394,7 @@
       <c r="J131" s="30"/>
       <c r="K131" s="30"/>
     </row>
-    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="30"/>
       <c r="B132" s="28"/>
       <c r="C132" s="36">
@@ -11431,7 +11415,7 @@
       <c r="J132" s="30"/>
       <c r="K132" s="30"/>
     </row>
-    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C133" s="39">
         <v>76</v>
       </c>
@@ -11445,7 +11429,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C134" s="36">
         <v>77</v>
       </c>
@@ -11459,7 +11443,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C135" s="39">
         <v>78</v>
       </c>
@@ -11473,7 +11457,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C136" s="36">
         <v>79</v>
       </c>
@@ -11487,7 +11471,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C137" s="39">
         <v>80</v>
       </c>
@@ -11501,7 +11485,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="138" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C138" s="36">
         <v>81</v>
       </c>
@@ -11538,29 +11522,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R138"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="4" t="s">
         <v>260</v>
       </c>
@@ -11568,7 +11552,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -11576,7 +11560,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -11584,7 +11568,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -11592,13 +11576,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -11606,7 +11590,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -11621,7 +11605,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -11635,7 +11619,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -11649,7 +11633,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -11663,7 +11647,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -11677,7 +11661,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -11691,7 +11675,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -11705,7 +11689,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -11719,7 +11703,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -11733,7 +11717,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -11747,7 +11731,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -11761,7 +11745,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -11775,7 +11759,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -11789,7 +11773,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -11803,7 +11787,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -11817,7 +11801,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -11831,7 +11815,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -11845,7 +11829,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -11859,7 +11843,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -11873,7 +11857,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -11887,7 +11871,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -11901,7 +11885,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -11915,7 +11899,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -11929,7 +11913,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -11943,7 +11927,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -11957,7 +11941,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -11971,7 +11955,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -11985,7 +11969,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -11999,7 +11983,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -12013,7 +11997,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -12027,7 +12011,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -12041,7 +12025,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -12055,7 +12039,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -12069,7 +12053,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -12083,7 +12067,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -12097,7 +12081,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -12111,7 +12095,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -12125,7 +12109,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -12139,7 +12123,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -12153,7 +12137,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -12167,7 +12151,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -12181,7 +12165,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -12195,7 +12179,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -12209,7 +12193,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -12223,7 +12207,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -12237,7 +12221,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -12251,7 +12235,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -12265,12 +12249,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="34" t="s">
         <v>7</v>
       </c>
@@ -12284,7 +12268,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="36">
         <v>1</v>
       </c>
@@ -12298,7 +12282,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C59" s="39">
         <v>2</v>
       </c>
@@ -12312,7 +12296,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C60" s="36">
         <v>3</v>
       </c>
@@ -12326,7 +12310,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C61" s="39">
         <v>4</v>
       </c>
@@ -12340,7 +12324,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C62" s="36">
         <v>5</v>
       </c>
@@ -12354,7 +12338,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C63" s="39">
         <v>6</v>
       </c>
@@ -12368,7 +12352,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="30"/>
       <c r="B64" s="28"/>
       <c r="C64" s="36">
@@ -12389,7 +12373,7 @@
       <c r="J64" s="30"/>
       <c r="K64" s="30"/>
     </row>
-    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="30"/>
       <c r="B65" s="28"/>
       <c r="C65" s="39">
@@ -12410,7 +12394,7 @@
       <c r="J65" s="30"/>
       <c r="K65" s="30"/>
     </row>
-    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="30"/>
       <c r="B66" s="28"/>
       <c r="C66" s="36">
@@ -12431,7 +12415,7 @@
       <c r="J66" s="30"/>
       <c r="K66" s="30"/>
     </row>
-    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="30"/>
       <c r="B67" s="28"/>
       <c r="C67" s="39">
@@ -12452,7 +12436,7 @@
       <c r="J67" s="30"/>
       <c r="K67" s="30"/>
     </row>
-    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="30"/>
       <c r="B68" s="28"/>
       <c r="C68" s="36">
@@ -12473,7 +12457,7 @@
       <c r="J68" s="30"/>
       <c r="K68" s="30"/>
     </row>
-    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="30"/>
       <c r="B69" s="28"/>
       <c r="C69" s="39">
@@ -12494,7 +12478,7 @@
       <c r="J69" s="30"/>
       <c r="K69" s="30"/>
     </row>
-    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="30"/>
       <c r="B70" s="28"/>
       <c r="C70" s="36">
@@ -12515,7 +12499,7 @@
       <c r="J70" s="30"/>
       <c r="K70" s="30"/>
     </row>
-    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="30"/>
       <c r="B71" s="28"/>
       <c r="C71" s="39">
@@ -12536,7 +12520,7 @@
       <c r="J71" s="30"/>
       <c r="K71" s="30"/>
     </row>
-    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="30"/>
       <c r="B72" s="28"/>
       <c r="C72" s="36">
@@ -12557,7 +12541,7 @@
       <c r="J72" s="30"/>
       <c r="K72" s="30"/>
     </row>
-    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="30"/>
       <c r="B73" s="28"/>
       <c r="C73" s="39">
@@ -12578,7 +12562,7 @@
       <c r="J73" s="30"/>
       <c r="K73" s="30"/>
     </row>
-    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="30"/>
       <c r="B74" s="28"/>
       <c r="C74" s="36">
@@ -12599,7 +12583,7 @@
       <c r="J74" s="30"/>
       <c r="K74" s="30"/>
     </row>
-    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="30"/>
       <c r="B75" s="28"/>
       <c r="C75" s="39">
@@ -12620,7 +12604,7 @@
       <c r="J75" s="30"/>
       <c r="K75" s="30"/>
     </row>
-    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="30"/>
       <c r="B76" s="28"/>
       <c r="C76" s="36">
@@ -12641,7 +12625,7 @@
       <c r="J76" s="30"/>
       <c r="K76" s="30"/>
     </row>
-    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="30"/>
       <c r="B77" s="28"/>
       <c r="C77" s="39">
@@ -12662,7 +12646,7 @@
       <c r="J77" s="30"/>
       <c r="K77" s="30"/>
     </row>
-    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="30"/>
       <c r="B78" s="28"/>
       <c r="C78" s="36">
@@ -12683,7 +12667,7 @@
       <c r="J78" s="30"/>
       <c r="K78" s="30"/>
     </row>
-    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="30"/>
       <c r="B79" s="28"/>
       <c r="C79" s="39">
@@ -12704,7 +12688,7 @@
       <c r="J79" s="30"/>
       <c r="K79" s="30"/>
     </row>
-    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="30"/>
       <c r="B80" s="28"/>
       <c r="C80" s="36">
@@ -12725,7 +12709,7 @@
       <c r="J80" s="30"/>
       <c r="K80" s="30"/>
     </row>
-    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="30"/>
       <c r="B81" s="28"/>
       <c r="C81" s="39">
@@ -12746,7 +12730,7 @@
       <c r="J81" s="30"/>
       <c r="K81" s="30"/>
     </row>
-    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="30"/>
       <c r="B82" s="28"/>
       <c r="C82" s="36">
@@ -12767,7 +12751,7 @@
       <c r="J82" s="30"/>
       <c r="K82" s="30"/>
     </row>
-    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="30"/>
       <c r="B83" s="28"/>
       <c r="C83" s="39">
@@ -12788,7 +12772,7 @@
       <c r="J83" s="30"/>
       <c r="K83" s="30"/>
     </row>
-    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="30"/>
       <c r="B84" s="28"/>
       <c r="C84" s="36">
@@ -12809,7 +12793,7 @@
       <c r="J84" s="30"/>
       <c r="K84" s="30"/>
     </row>
-    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="30"/>
       <c r="B85" s="28"/>
       <c r="C85" s="39">
@@ -12830,7 +12814,7 @@
       <c r="J85" s="30"/>
       <c r="K85" s="30"/>
     </row>
-    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="30"/>
       <c r="B86" s="28"/>
       <c r="C86" s="36">
@@ -12851,7 +12835,7 @@
       <c r="J86" s="30"/>
       <c r="K86" s="30"/>
     </row>
-    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="30"/>
       <c r="B87" s="28"/>
       <c r="C87" s="39">
@@ -12872,7 +12856,7 @@
       <c r="J87" s="30"/>
       <c r="K87" s="30"/>
     </row>
-    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="30"/>
       <c r="B88" s="28"/>
       <c r="C88" s="36">
@@ -12893,7 +12877,7 @@
       <c r="J88" s="30"/>
       <c r="K88" s="30"/>
     </row>
-    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="30"/>
       <c r="B89" s="28"/>
       <c r="C89" s="39">
@@ -12914,7 +12898,7 @@
       <c r="J89" s="30"/>
       <c r="K89" s="30"/>
     </row>
-    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="30"/>
       <c r="B90" s="28"/>
       <c r="C90" s="36">
@@ -12935,7 +12919,7 @@
       <c r="J90" s="30"/>
       <c r="K90" s="30"/>
     </row>
-    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="30"/>
       <c r="B91" s="28"/>
       <c r="C91" s="39">
@@ -12956,7 +12940,7 @@
       <c r="J91" s="30"/>
       <c r="K91" s="30"/>
     </row>
-    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="30"/>
       <c r="B92" s="28"/>
       <c r="C92" s="36">
@@ -12977,7 +12961,7 @@
       <c r="J92" s="30"/>
       <c r="K92" s="30"/>
     </row>
-    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="30"/>
       <c r="B93" s="28"/>
       <c r="C93" s="39">
@@ -12998,7 +12982,7 @@
       <c r="J93" s="30"/>
       <c r="K93" s="30"/>
     </row>
-    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="30"/>
       <c r="B94" s="28"/>
       <c r="C94" s="36">
@@ -13019,7 +13003,7 @@
       <c r="J94" s="30"/>
       <c r="K94" s="30"/>
     </row>
-    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="30"/>
       <c r="B95" s="28"/>
       <c r="C95" s="39">
@@ -13040,7 +13024,7 @@
       <c r="J95" s="30"/>
       <c r="K95" s="30"/>
     </row>
-    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="30"/>
       <c r="B96" s="28"/>
       <c r="C96" s="36">
@@ -13061,7 +13045,7 @@
       <c r="J96" s="30"/>
       <c r="K96" s="30"/>
     </row>
-    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="30"/>
       <c r="B97" s="28"/>
       <c r="C97" s="39">
@@ -13082,7 +13066,7 @@
       <c r="J97" s="30"/>
       <c r="K97" s="30"/>
     </row>
-    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="30"/>
       <c r="B98" s="28"/>
       <c r="C98" s="36">
@@ -13103,7 +13087,7 @@
       <c r="J98" s="30"/>
       <c r="K98" s="30"/>
     </row>
-    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="30"/>
       <c r="B99" s="28"/>
       <c r="C99" s="39">
@@ -13124,7 +13108,7 @@
       <c r="J99" s="30"/>
       <c r="K99" s="30"/>
     </row>
-    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="30"/>
       <c r="B100" s="28"/>
       <c r="C100" s="36">
@@ -13145,7 +13129,7 @@
       <c r="J100" s="30"/>
       <c r="K100" s="30"/>
     </row>
-    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="30"/>
       <c r="B101" s="28"/>
       <c r="C101" s="39">
@@ -13166,7 +13150,7 @@
       <c r="J101" s="30"/>
       <c r="K101" s="30"/>
     </row>
-    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="30"/>
       <c r="B102" s="28"/>
       <c r="C102" s="36">
@@ -13187,7 +13171,7 @@
       <c r="J102" s="30"/>
       <c r="K102" s="30"/>
     </row>
-    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="30"/>
       <c r="B103" s="28"/>
       <c r="C103" s="39">
@@ -13208,7 +13192,7 @@
       <c r="J103" s="30"/>
       <c r="K103" s="30"/>
     </row>
-    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="30"/>
       <c r="B104" s="28"/>
       <c r="C104" s="36">
@@ -13229,7 +13213,7 @@
       <c r="J104" s="30"/>
       <c r="K104" s="30"/>
     </row>
-    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="30"/>
       <c r="B105" s="28"/>
       <c r="C105" s="39">
@@ -13250,7 +13234,7 @@
       <c r="J105" s="30"/>
       <c r="K105" s="30"/>
     </row>
-    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="30"/>
       <c r="B106" s="28"/>
       <c r="C106" s="36">
@@ -13271,7 +13255,7 @@
       <c r="J106" s="30"/>
       <c r="K106" s="30"/>
     </row>
-    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="30"/>
       <c r="B107" s="28"/>
       <c r="C107" s="39">
@@ -13292,7 +13276,7 @@
       <c r="J107" s="30"/>
       <c r="K107" s="30"/>
     </row>
-    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="30"/>
       <c r="B108" s="28"/>
       <c r="C108" s="36">
@@ -13313,7 +13297,7 @@
       <c r="J108" s="30"/>
       <c r="K108" s="30"/>
     </row>
-    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="30"/>
       <c r="B109" s="28"/>
       <c r="C109" s="39">
@@ -13334,7 +13318,7 @@
       <c r="J109" s="30"/>
       <c r="K109" s="30"/>
     </row>
-    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="30"/>
       <c r="B110" s="28"/>
       <c r="C110" s="36">
@@ -13355,7 +13339,7 @@
       <c r="J110" s="30"/>
       <c r="K110" s="30"/>
     </row>
-    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="30"/>
       <c r="B111" s="28"/>
       <c r="C111" s="39">
@@ -13376,7 +13360,7 @@
       <c r="J111" s="30"/>
       <c r="K111" s="30"/>
     </row>
-    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="30"/>
       <c r="B112" s="28"/>
       <c r="C112" s="36">
@@ -13397,7 +13381,7 @@
       <c r="J112" s="30"/>
       <c r="K112" s="30"/>
     </row>
-    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="30"/>
       <c r="B113" s="28"/>
       <c r="C113" s="39">
@@ -13418,7 +13402,7 @@
       <c r="J113" s="30"/>
       <c r="K113" s="30"/>
     </row>
-    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="30"/>
       <c r="B114" s="28"/>
       <c r="C114" s="36">
@@ -13439,7 +13423,7 @@
       <c r="J114" s="30"/>
       <c r="K114" s="30"/>
     </row>
-    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="30"/>
       <c r="B115" s="28"/>
       <c r="C115" s="39">
@@ -13460,7 +13444,7 @@
       <c r="J115" s="30"/>
       <c r="K115" s="30"/>
     </row>
-    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="30"/>
       <c r="B116" s="28"/>
       <c r="C116" s="36">
@@ -13481,7 +13465,7 @@
       <c r="J116" s="30"/>
       <c r="K116" s="30"/>
     </row>
-    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="30"/>
       <c r="B117" s="28"/>
       <c r="C117" s="39">
@@ -13502,7 +13486,7 @@
       <c r="J117" s="30"/>
       <c r="K117" s="30"/>
     </row>
-    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="30"/>
       <c r="B118" s="28"/>
       <c r="C118" s="36">
@@ -13523,7 +13507,7 @@
       <c r="J118" s="30"/>
       <c r="K118" s="30"/>
     </row>
-    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="30"/>
       <c r="B119" s="28"/>
       <c r="C119" s="39">
@@ -13544,7 +13528,7 @@
       <c r="J119" s="30"/>
       <c r="K119" s="30"/>
     </row>
-    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="30"/>
       <c r="B120" s="28"/>
       <c r="C120" s="36">
@@ -13565,7 +13549,7 @@
       <c r="J120" s="30"/>
       <c r="K120" s="30"/>
     </row>
-    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="30"/>
       <c r="B121" s="28"/>
       <c r="C121" s="39">
@@ -13586,7 +13570,7 @@
       <c r="J121" s="30"/>
       <c r="K121" s="30"/>
     </row>
-    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="30"/>
       <c r="B122" s="28"/>
       <c r="C122" s="36">
@@ -13607,7 +13591,7 @@
       <c r="J122" s="30"/>
       <c r="K122" s="30"/>
     </row>
-    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="30"/>
       <c r="B123" s="28"/>
       <c r="C123" s="39">
@@ -13628,7 +13612,7 @@
       <c r="J123" s="30"/>
       <c r="K123" s="30"/>
     </row>
-    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="30"/>
       <c r="B124" s="28"/>
       <c r="C124" s="36">
@@ -13649,7 +13633,7 @@
       <c r="J124" s="30"/>
       <c r="K124" s="30"/>
     </row>
-    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="30"/>
       <c r="B125" s="28"/>
       <c r="C125" s="39">
@@ -13670,7 +13654,7 @@
       <c r="J125" s="30"/>
       <c r="K125" s="30"/>
     </row>
-    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="30"/>
       <c r="B126" s="28"/>
       <c r="C126" s="36">
@@ -13691,7 +13675,7 @@
       <c r="J126" s="30"/>
       <c r="K126" s="30"/>
     </row>
-    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="30"/>
       <c r="B127" s="28"/>
       <c r="C127" s="39">
@@ -13712,7 +13696,7 @@
       <c r="J127" s="30"/>
       <c r="K127" s="30"/>
     </row>
-    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="30"/>
       <c r="B128" s="28"/>
       <c r="C128" s="36">
@@ -13733,7 +13717,7 @@
       <c r="J128" s="30"/>
       <c r="K128" s="30"/>
     </row>
-    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="30"/>
       <c r="B129" s="28"/>
       <c r="C129" s="39">
@@ -13754,7 +13738,7 @@
       <c r="J129" s="30"/>
       <c r="K129" s="30"/>
     </row>
-    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="30"/>
       <c r="B130" s="28"/>
       <c r="C130" s="36">
@@ -13775,7 +13759,7 @@
       <c r="J130" s="30"/>
       <c r="K130" s="30"/>
     </row>
-    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="30"/>
       <c r="B131" s="28"/>
       <c r="C131" s="39">
@@ -13796,7 +13780,7 @@
       <c r="J131" s="30"/>
       <c r="K131" s="30"/>
     </row>
-    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="30"/>
       <c r="B132" s="28"/>
       <c r="C132" s="36">
@@ -13817,7 +13801,7 @@
       <c r="J132" s="30"/>
       <c r="K132" s="30"/>
     </row>
-    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C133" s="39">
         <v>76</v>
       </c>
@@ -13831,7 +13815,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C134" s="36">
         <v>77</v>
       </c>
@@ -13845,7 +13829,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C135" s="3">
         <v>78</v>
       </c>
@@ -13859,7 +13843,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C136" s="36">
         <v>79</v>
       </c>
@@ -13873,7 +13857,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C137" s="3">
         <v>80</v>
       </c>
@@ -13887,7 +13871,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="138" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C138" s="36">
         <v>81</v>
       </c>
@@ -13924,29 +13908,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R138"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="4" t="s">
         <v>261</v>
       </c>
@@ -13954,7 +13938,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -13962,7 +13946,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -13970,7 +13954,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -13978,13 +13962,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -13992,7 +13976,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -14007,7 +13991,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -14021,7 +14005,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -14035,7 +14019,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -14049,7 +14033,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -14063,7 +14047,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -14077,7 +14061,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -14091,7 +14075,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -14105,7 +14089,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -14119,7 +14103,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -14133,7 +14117,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -14147,7 +14131,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -14161,7 +14145,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -14175,7 +14159,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -14189,7 +14173,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -14203,7 +14187,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -14217,7 +14201,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -14231,7 +14215,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -14245,7 +14229,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -14259,7 +14243,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -14273,7 +14257,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -14287,7 +14271,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -14301,7 +14285,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -14315,7 +14299,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -14329,7 +14313,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -14343,7 +14327,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -14357,7 +14341,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -14371,7 +14355,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -14385,7 +14369,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -14399,7 +14383,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -14413,7 +14397,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -14427,7 +14411,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -14441,7 +14425,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -14455,7 +14439,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -14469,7 +14453,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -14483,7 +14467,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -14497,7 +14481,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -14511,7 +14495,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -14525,7 +14509,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -14539,7 +14523,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -14553,7 +14537,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -14567,7 +14551,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -14581,7 +14565,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -14595,7 +14579,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -14609,7 +14593,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -14623,7 +14607,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -14637,7 +14621,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -14651,12 +14635,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="34" t="s">
         <v>7</v>
       </c>
@@ -14670,7 +14654,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="36">
         <v>1</v>
       </c>
@@ -14684,7 +14668,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C59" s="39">
         <v>2</v>
       </c>
@@ -14698,7 +14682,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C60" s="36">
         <v>3</v>
       </c>
@@ -14712,7 +14696,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C61" s="39">
         <v>4</v>
       </c>
@@ -14726,7 +14710,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C62" s="36">
         <v>5</v>
       </c>
@@ -14740,7 +14724,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C63" s="39">
         <v>6</v>
       </c>
@@ -14754,7 +14738,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="30"/>
       <c r="B64" s="28"/>
       <c r="C64" s="36">
@@ -14775,7 +14759,7 @@
       <c r="J64" s="30"/>
       <c r="K64" s="30"/>
     </row>
-    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="30"/>
       <c r="B65" s="28"/>
       <c r="C65" s="39">
@@ -14796,7 +14780,7 @@
       <c r="J65" s="30"/>
       <c r="K65" s="30"/>
     </row>
-    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="30"/>
       <c r="B66" s="28"/>
       <c r="C66" s="36">
@@ -14817,7 +14801,7 @@
       <c r="J66" s="30"/>
       <c r="K66" s="30"/>
     </row>
-    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="30"/>
       <c r="B67" s="28"/>
       <c r="C67" s="39">
@@ -14838,7 +14822,7 @@
       <c r="J67" s="30"/>
       <c r="K67" s="30"/>
     </row>
-    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="30"/>
       <c r="B68" s="28"/>
       <c r="C68" s="36">
@@ -14859,7 +14843,7 @@
       <c r="J68" s="30"/>
       <c r="K68" s="30"/>
     </row>
-    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="30"/>
       <c r="B69" s="28"/>
       <c r="C69" s="39">
@@ -14880,7 +14864,7 @@
       <c r="J69" s="30"/>
       <c r="K69" s="30"/>
     </row>
-    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="30"/>
       <c r="B70" s="28"/>
       <c r="C70" s="36">
@@ -14901,7 +14885,7 @@
       <c r="J70" s="30"/>
       <c r="K70" s="30"/>
     </row>
-    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="30"/>
       <c r="B71" s="28"/>
       <c r="C71" s="39">
@@ -14922,7 +14906,7 @@
       <c r="J71" s="30"/>
       <c r="K71" s="30"/>
     </row>
-    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="30"/>
       <c r="B72" s="28"/>
       <c r="C72" s="36">
@@ -14943,7 +14927,7 @@
       <c r="J72" s="30"/>
       <c r="K72" s="30"/>
     </row>
-    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="30"/>
       <c r="B73" s="28"/>
       <c r="C73" s="39">
@@ -14964,7 +14948,7 @@
       <c r="J73" s="30"/>
       <c r="K73" s="30"/>
     </row>
-    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="30"/>
       <c r="B74" s="28"/>
       <c r="C74" s="36">
@@ -14985,7 +14969,7 @@
       <c r="J74" s="30"/>
       <c r="K74" s="30"/>
     </row>
-    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="30"/>
       <c r="B75" s="28"/>
       <c r="C75" s="39">
@@ -15006,7 +14990,7 @@
       <c r="J75" s="30"/>
       <c r="K75" s="30"/>
     </row>
-    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="30"/>
       <c r="B76" s="28"/>
       <c r="C76" s="36">
@@ -15027,7 +15011,7 @@
       <c r="J76" s="30"/>
       <c r="K76" s="30"/>
     </row>
-    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="30"/>
       <c r="B77" s="28"/>
       <c r="C77" s="39">
@@ -15048,7 +15032,7 @@
       <c r="J77" s="30"/>
       <c r="K77" s="30"/>
     </row>
-    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="30"/>
       <c r="B78" s="28"/>
       <c r="C78" s="36">
@@ -15069,7 +15053,7 @@
       <c r="J78" s="30"/>
       <c r="K78" s="30"/>
     </row>
-    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="30"/>
       <c r="B79" s="28"/>
       <c r="C79" s="39">
@@ -15090,7 +15074,7 @@
       <c r="J79" s="30"/>
       <c r="K79" s="30"/>
     </row>
-    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="30"/>
       <c r="B80" s="28"/>
       <c r="C80" s="36">
@@ -15111,7 +15095,7 @@
       <c r="J80" s="30"/>
       <c r="K80" s="30"/>
     </row>
-    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="30"/>
       <c r="B81" s="28"/>
       <c r="C81" s="39">
@@ -15132,7 +15116,7 @@
       <c r="J81" s="30"/>
       <c r="K81" s="30"/>
     </row>
-    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="30"/>
       <c r="B82" s="28"/>
       <c r="C82" s="36">
@@ -15153,7 +15137,7 @@
       <c r="J82" s="30"/>
       <c r="K82" s="30"/>
     </row>
-    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="30"/>
       <c r="B83" s="28"/>
       <c r="C83" s="39">
@@ -15174,7 +15158,7 @@
       <c r="J83" s="30"/>
       <c r="K83" s="30"/>
     </row>
-    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="30"/>
       <c r="B84" s="28"/>
       <c r="C84" s="36">
@@ -15195,7 +15179,7 @@
       <c r="J84" s="30"/>
       <c r="K84" s="30"/>
     </row>
-    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="30"/>
       <c r="B85" s="28"/>
       <c r="C85" s="39">
@@ -15216,7 +15200,7 @@
       <c r="J85" s="30"/>
       <c r="K85" s="30"/>
     </row>
-    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="30"/>
       <c r="B86" s="28"/>
       <c r="C86" s="36">
@@ -15237,7 +15221,7 @@
       <c r="J86" s="30"/>
       <c r="K86" s="30"/>
     </row>
-    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="30"/>
       <c r="B87" s="28"/>
       <c r="C87" s="39">
@@ -15258,7 +15242,7 @@
       <c r="J87" s="30"/>
       <c r="K87" s="30"/>
     </row>
-    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="30"/>
       <c r="B88" s="28"/>
       <c r="C88" s="36">
@@ -15279,7 +15263,7 @@
       <c r="J88" s="30"/>
       <c r="K88" s="30"/>
     </row>
-    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="30"/>
       <c r="B89" s="28"/>
       <c r="C89" s="39">
@@ -15300,7 +15284,7 @@
       <c r="J89" s="30"/>
       <c r="K89" s="30"/>
     </row>
-    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="30"/>
       <c r="B90" s="28"/>
       <c r="C90" s="36">
@@ -15321,7 +15305,7 @@
       <c r="J90" s="30"/>
       <c r="K90" s="30"/>
     </row>
-    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="30"/>
       <c r="B91" s="28"/>
       <c r="C91" s="39">
@@ -15342,7 +15326,7 @@
       <c r="J91" s="30"/>
       <c r="K91" s="30"/>
     </row>
-    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="30"/>
       <c r="B92" s="28"/>
       <c r="C92" s="36">
@@ -15363,7 +15347,7 @@
       <c r="J92" s="30"/>
       <c r="K92" s="30"/>
     </row>
-    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="30"/>
       <c r="B93" s="28"/>
       <c r="C93" s="39">
@@ -15384,7 +15368,7 @@
       <c r="J93" s="30"/>
       <c r="K93" s="30"/>
     </row>
-    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="30"/>
       <c r="B94" s="28"/>
       <c r="C94" s="36">
@@ -15405,7 +15389,7 @@
       <c r="J94" s="30"/>
       <c r="K94" s="30"/>
     </row>
-    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="30"/>
       <c r="B95" s="28"/>
       <c r="C95" s="39">
@@ -15426,7 +15410,7 @@
       <c r="J95" s="30"/>
       <c r="K95" s="30"/>
     </row>
-    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="30"/>
       <c r="B96" s="28"/>
       <c r="C96" s="36">
@@ -15447,7 +15431,7 @@
       <c r="J96" s="30"/>
       <c r="K96" s="30"/>
     </row>
-    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="30"/>
       <c r="B97" s="28"/>
       <c r="C97" s="39">
@@ -15468,7 +15452,7 @@
       <c r="J97" s="30"/>
       <c r="K97" s="30"/>
     </row>
-    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="30"/>
       <c r="B98" s="28"/>
       <c r="C98" s="36">
@@ -15489,7 +15473,7 @@
       <c r="J98" s="30"/>
       <c r="K98" s="30"/>
     </row>
-    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="30"/>
       <c r="B99" s="28"/>
       <c r="C99" s="39">
@@ -15510,7 +15494,7 @@
       <c r="J99" s="30"/>
       <c r="K99" s="30"/>
     </row>
-    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="30"/>
       <c r="B100" s="28"/>
       <c r="C100" s="36">
@@ -15531,7 +15515,7 @@
       <c r="J100" s="30"/>
       <c r="K100" s="30"/>
     </row>
-    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="30"/>
       <c r="B101" s="28"/>
       <c r="C101" s="39">
@@ -15552,7 +15536,7 @@
       <c r="J101" s="30"/>
       <c r="K101" s="30"/>
     </row>
-    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="30"/>
       <c r="B102" s="28"/>
       <c r="C102" s="36">
@@ -15573,7 +15557,7 @@
       <c r="J102" s="30"/>
       <c r="K102" s="30"/>
     </row>
-    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="30"/>
       <c r="B103" s="28"/>
       <c r="C103" s="39">
@@ -15594,7 +15578,7 @@
       <c r="J103" s="30"/>
       <c r="K103" s="30"/>
     </row>
-    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="30"/>
       <c r="B104" s="28"/>
       <c r="C104" s="36">
@@ -15615,7 +15599,7 @@
       <c r="J104" s="30"/>
       <c r="K104" s="30"/>
     </row>
-    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="30"/>
       <c r="B105" s="28"/>
       <c r="C105" s="39">
@@ -15636,7 +15620,7 @@
       <c r="J105" s="30"/>
       <c r="K105" s="30"/>
     </row>
-    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="30"/>
       <c r="B106" s="28"/>
       <c r="C106" s="36">
@@ -15657,7 +15641,7 @@
       <c r="J106" s="30"/>
       <c r="K106" s="30"/>
     </row>
-    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="30"/>
       <c r="B107" s="28"/>
       <c r="C107" s="39">
@@ -15678,7 +15662,7 @@
       <c r="J107" s="30"/>
       <c r="K107" s="30"/>
     </row>
-    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="30"/>
       <c r="B108" s="28"/>
       <c r="C108" s="36">
@@ -15699,7 +15683,7 @@
       <c r="J108" s="30"/>
       <c r="K108" s="30"/>
     </row>
-    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="30"/>
       <c r="B109" s="28"/>
       <c r="C109" s="39">
@@ -15720,7 +15704,7 @@
       <c r="J109" s="30"/>
       <c r="K109" s="30"/>
     </row>
-    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="30"/>
       <c r="B110" s="28"/>
       <c r="C110" s="36">
@@ -15741,7 +15725,7 @@
       <c r="J110" s="30"/>
       <c r="K110" s="30"/>
     </row>
-    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="30"/>
       <c r="B111" s="28"/>
       <c r="C111" s="39">
@@ -15762,7 +15746,7 @@
       <c r="J111" s="30"/>
       <c r="K111" s="30"/>
     </row>
-    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="30"/>
       <c r="B112" s="28"/>
       <c r="C112" s="36">
@@ -15783,7 +15767,7 @@
       <c r="J112" s="30"/>
       <c r="K112" s="30"/>
     </row>
-    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="30"/>
       <c r="B113" s="28"/>
       <c r="C113" s="39">
@@ -15804,7 +15788,7 @@
       <c r="J113" s="30"/>
       <c r="K113" s="30"/>
     </row>
-    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="30"/>
       <c r="B114" s="28"/>
       <c r="C114" s="36">
@@ -15825,7 +15809,7 @@
       <c r="J114" s="30"/>
       <c r="K114" s="30"/>
     </row>
-    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="30"/>
       <c r="B115" s="28"/>
       <c r="C115" s="39">
@@ -15846,7 +15830,7 @@
       <c r="J115" s="30"/>
       <c r="K115" s="30"/>
     </row>
-    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="30"/>
       <c r="B116" s="28"/>
       <c r="C116" s="36">
@@ -15867,7 +15851,7 @@
       <c r="J116" s="30"/>
       <c r="K116" s="30"/>
     </row>
-    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="30"/>
       <c r="B117" s="28"/>
       <c r="C117" s="39">
@@ -15888,7 +15872,7 @@
       <c r="J117" s="30"/>
       <c r="K117" s="30"/>
     </row>
-    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="30"/>
       <c r="B118" s="28"/>
       <c r="C118" s="36">
@@ -15909,7 +15893,7 @@
       <c r="J118" s="30"/>
       <c r="K118" s="30"/>
     </row>
-    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="30"/>
       <c r="B119" s="28"/>
       <c r="C119" s="39">
@@ -15930,7 +15914,7 @@
       <c r="J119" s="30"/>
       <c r="K119" s="30"/>
     </row>
-    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="30"/>
       <c r="B120" s="28"/>
       <c r="C120" s="36">
@@ -15951,7 +15935,7 @@
       <c r="J120" s="30"/>
       <c r="K120" s="30"/>
     </row>
-    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="30"/>
       <c r="B121" s="28"/>
       <c r="C121" s="39">
@@ -15972,7 +15956,7 @@
       <c r="J121" s="30"/>
       <c r="K121" s="30"/>
     </row>
-    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="30"/>
       <c r="B122" s="28"/>
       <c r="C122" s="36">
@@ -15993,7 +15977,7 @@
       <c r="J122" s="30"/>
       <c r="K122" s="30"/>
     </row>
-    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="30"/>
       <c r="B123" s="28"/>
       <c r="C123" s="39">
@@ -16014,7 +15998,7 @@
       <c r="J123" s="30"/>
       <c r="K123" s="30"/>
     </row>
-    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="30"/>
       <c r="B124" s="28"/>
       <c r="C124" s="36">
@@ -16035,7 +16019,7 @@
       <c r="J124" s="30"/>
       <c r="K124" s="30"/>
     </row>
-    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="30"/>
       <c r="B125" s="28"/>
       <c r="C125" s="39">
@@ -16056,7 +16040,7 @@
       <c r="J125" s="30"/>
       <c r="K125" s="30"/>
     </row>
-    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="30"/>
       <c r="B126" s="28"/>
       <c r="C126" s="36">
@@ -16077,7 +16061,7 @@
       <c r="J126" s="30"/>
       <c r="K126" s="30"/>
     </row>
-    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="30"/>
       <c r="B127" s="28"/>
       <c r="C127" s="39">
@@ -16098,7 +16082,7 @@
       <c r="J127" s="30"/>
       <c r="K127" s="30"/>
     </row>
-    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="30"/>
       <c r="B128" s="28"/>
       <c r="C128" s="36">
@@ -16119,7 +16103,7 @@
       <c r="J128" s="30"/>
       <c r="K128" s="30"/>
     </row>
-    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="30"/>
       <c r="B129" s="28"/>
       <c r="C129" s="39">
@@ -16140,7 +16124,7 @@
       <c r="J129" s="30"/>
       <c r="K129" s="30"/>
     </row>
-    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="30"/>
       <c r="B130" s="28"/>
       <c r="C130" s="36">
@@ -16161,7 +16145,7 @@
       <c r="J130" s="30"/>
       <c r="K130" s="30"/>
     </row>
-    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="30"/>
       <c r="B131" s="28"/>
       <c r="C131" s="39">
@@ -16182,7 +16166,7 @@
       <c r="J131" s="30"/>
       <c r="K131" s="30"/>
     </row>
-    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="30"/>
       <c r="B132" s="28"/>
       <c r="C132" s="36">
@@ -16203,7 +16187,7 @@
       <c r="J132" s="30"/>
       <c r="K132" s="30"/>
     </row>
-    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C133" s="39">
         <v>76</v>
       </c>
@@ -16217,7 +16201,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C134" s="36">
         <v>77</v>
       </c>
@@ -16231,7 +16215,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C135" s="3">
         <v>78</v>
       </c>
@@ -16245,7 +16229,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C136" s="36">
         <v>79</v>
       </c>
@@ -16259,7 +16243,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C137" s="3">
         <v>80</v>
       </c>
@@ -16273,7 +16257,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="138" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C138" s="36">
         <v>81</v>
       </c>
@@ -16310,29 +16294,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R138"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="4" t="s">
         <v>262</v>
       </c>
@@ -16340,7 +16324,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -16348,7 +16332,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -16356,7 +16340,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -16364,13 +16348,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -16378,7 +16362,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -16393,7 +16377,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -16407,7 +16391,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -16421,7 +16405,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -16435,7 +16419,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -16449,7 +16433,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -16463,7 +16447,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -16477,7 +16461,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -16491,7 +16475,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -16505,7 +16489,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -16519,7 +16503,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -16533,7 +16517,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -16547,7 +16531,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -16561,7 +16545,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -16575,7 +16559,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -16589,7 +16573,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -16603,7 +16587,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -16617,7 +16601,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -16631,7 +16615,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -16645,7 +16629,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -16659,7 +16643,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -16673,7 +16657,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -16687,7 +16671,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -16701,7 +16685,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -16715,7 +16699,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -16729,7 +16713,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -16743,7 +16727,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -16757,7 +16741,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -16771,7 +16755,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -16785,7 +16769,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -16799,7 +16783,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -16813,7 +16797,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -16827,7 +16811,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -16841,7 +16825,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -16855,7 +16839,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -16869,7 +16853,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -16883,7 +16867,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -16897,7 +16881,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -16911,7 +16895,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -16925,7 +16909,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -16939,7 +16923,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -16953,7 +16937,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -16967,7 +16951,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -16981,7 +16965,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -16995,7 +16979,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -17009,7 +16993,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -17023,7 +17007,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -17037,12 +17021,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="34" t="s">
         <v>7</v>
       </c>
@@ -17056,7 +17040,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="36">
         <v>1</v>
       </c>
@@ -17070,7 +17054,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C59" s="39">
         <v>2</v>
       </c>
@@ -17084,7 +17068,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C60" s="36">
         <v>3</v>
       </c>
@@ -17098,7 +17082,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C61" s="39">
         <v>4</v>
       </c>
@@ -17112,7 +17096,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C62" s="36">
         <v>5</v>
       </c>
@@ -17126,7 +17110,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C63" s="39">
         <v>6</v>
       </c>
@@ -17140,7 +17124,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="30"/>
       <c r="B64" s="28"/>
       <c r="C64" s="36">
@@ -17161,7 +17145,7 @@
       <c r="J64" s="30"/>
       <c r="K64" s="30"/>
     </row>
-    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="30"/>
       <c r="B65" s="28"/>
       <c r="C65" s="39">
@@ -17182,7 +17166,7 @@
       <c r="J65" s="30"/>
       <c r="K65" s="30"/>
     </row>
-    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="30"/>
       <c r="B66" s="28"/>
       <c r="C66" s="36">
@@ -17203,7 +17187,7 @@
       <c r="J66" s="30"/>
       <c r="K66" s="30"/>
     </row>
-    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="30"/>
       <c r="B67" s="28"/>
       <c r="C67" s="39">
@@ -17224,7 +17208,7 @@
       <c r="J67" s="30"/>
       <c r="K67" s="30"/>
     </row>
-    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="30"/>
       <c r="B68" s="28"/>
       <c r="C68" s="36">
@@ -17245,7 +17229,7 @@
       <c r="J68" s="30"/>
       <c r="K68" s="30"/>
     </row>
-    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="30"/>
       <c r="B69" s="28"/>
       <c r="C69" s="39">
@@ -17266,7 +17250,7 @@
       <c r="J69" s="30"/>
       <c r="K69" s="30"/>
     </row>
-    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="30"/>
       <c r="B70" s="28"/>
       <c r="C70" s="36">
@@ -17287,7 +17271,7 @@
       <c r="J70" s="30"/>
       <c r="K70" s="30"/>
     </row>
-    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="30"/>
       <c r="B71" s="28"/>
       <c r="C71" s="39">
@@ -17308,7 +17292,7 @@
       <c r="J71" s="30"/>
       <c r="K71" s="30"/>
     </row>
-    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="30"/>
       <c r="B72" s="28"/>
       <c r="C72" s="36">
@@ -17329,7 +17313,7 @@
       <c r="J72" s="30"/>
       <c r="K72" s="30"/>
     </row>
-    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="30"/>
       <c r="B73" s="28"/>
       <c r="C73" s="39">
@@ -17350,7 +17334,7 @@
       <c r="J73" s="30"/>
       <c r="K73" s="30"/>
     </row>
-    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="30"/>
       <c r="B74" s="28"/>
       <c r="C74" s="36">
@@ -17371,7 +17355,7 @@
       <c r="J74" s="30"/>
       <c r="K74" s="30"/>
     </row>
-    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="30"/>
       <c r="B75" s="28"/>
       <c r="C75" s="39">
@@ -17392,7 +17376,7 @@
       <c r="J75" s="30"/>
       <c r="K75" s="30"/>
     </row>
-    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="30"/>
       <c r="B76" s="28"/>
       <c r="C76" s="36">
@@ -17413,7 +17397,7 @@
       <c r="J76" s="30"/>
       <c r="K76" s="30"/>
     </row>
-    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="30"/>
       <c r="B77" s="28"/>
       <c r="C77" s="39">
@@ -17434,7 +17418,7 @@
       <c r="J77" s="30"/>
       <c r="K77" s="30"/>
     </row>
-    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="30"/>
       <c r="B78" s="28"/>
       <c r="C78" s="36">
@@ -17455,7 +17439,7 @@
       <c r="J78" s="30"/>
       <c r="K78" s="30"/>
     </row>
-    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="30"/>
       <c r="B79" s="28"/>
       <c r="C79" s="39">
@@ -17476,7 +17460,7 @@
       <c r="J79" s="30"/>
       <c r="K79" s="30"/>
     </row>
-    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="30"/>
       <c r="B80" s="28"/>
       <c r="C80" s="36">
@@ -17497,7 +17481,7 @@
       <c r="J80" s="30"/>
       <c r="K80" s="30"/>
     </row>
-    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="30"/>
       <c r="B81" s="28"/>
       <c r="C81" s="39">
@@ -17518,7 +17502,7 @@
       <c r="J81" s="30"/>
       <c r="K81" s="30"/>
     </row>
-    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="30"/>
       <c r="B82" s="28"/>
       <c r="C82" s="36">
@@ -17539,7 +17523,7 @@
       <c r="J82" s="30"/>
       <c r="K82" s="30"/>
     </row>
-    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="30"/>
       <c r="B83" s="28"/>
       <c r="C83" s="39">
@@ -17560,7 +17544,7 @@
       <c r="J83" s="30"/>
       <c r="K83" s="30"/>
     </row>
-    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="30"/>
       <c r="B84" s="28"/>
       <c r="C84" s="36">
@@ -17581,7 +17565,7 @@
       <c r="J84" s="30"/>
       <c r="K84" s="30"/>
     </row>
-    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="30"/>
       <c r="B85" s="28"/>
       <c r="C85" s="39">
@@ -17602,7 +17586,7 @@
       <c r="J85" s="30"/>
       <c r="K85" s="30"/>
     </row>
-    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="30"/>
       <c r="B86" s="28"/>
       <c r="C86" s="36">
@@ -17623,7 +17607,7 @@
       <c r="J86" s="30"/>
       <c r="K86" s="30"/>
     </row>
-    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="30"/>
       <c r="B87" s="28"/>
       <c r="C87" s="39">
@@ -17644,7 +17628,7 @@
       <c r="J87" s="30"/>
       <c r="K87" s="30"/>
     </row>
-    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="30"/>
       <c r="B88" s="28"/>
       <c r="C88" s="36">
@@ -17665,7 +17649,7 @@
       <c r="J88" s="30"/>
       <c r="K88" s="30"/>
     </row>
-    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="30"/>
       <c r="B89" s="28"/>
       <c r="C89" s="39">
@@ -17686,7 +17670,7 @@
       <c r="J89" s="30"/>
       <c r="K89" s="30"/>
     </row>
-    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="30"/>
       <c r="B90" s="28"/>
       <c r="C90" s="36">
@@ -17707,7 +17691,7 @@
       <c r="J90" s="30"/>
       <c r="K90" s="30"/>
     </row>
-    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="30"/>
       <c r="B91" s="28"/>
       <c r="C91" s="39">
@@ -17728,7 +17712,7 @@
       <c r="J91" s="30"/>
       <c r="K91" s="30"/>
     </row>
-    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="30"/>
       <c r="B92" s="28"/>
       <c r="C92" s="36">
@@ -17749,7 +17733,7 @@
       <c r="J92" s="30"/>
       <c r="K92" s="30"/>
     </row>
-    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="30"/>
       <c r="B93" s="28"/>
       <c r="C93" s="39">
@@ -17770,7 +17754,7 @@
       <c r="J93" s="30"/>
       <c r="K93" s="30"/>
     </row>
-    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="30"/>
       <c r="B94" s="28"/>
       <c r="C94" s="36">
@@ -17791,7 +17775,7 @@
       <c r="J94" s="30"/>
       <c r="K94" s="30"/>
     </row>
-    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="30"/>
       <c r="B95" s="28"/>
       <c r="C95" s="39">
@@ -17812,7 +17796,7 @@
       <c r="J95" s="30"/>
       <c r="K95" s="30"/>
     </row>
-    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="30"/>
       <c r="B96" s="28"/>
       <c r="C96" s="36">
@@ -17833,7 +17817,7 @@
       <c r="J96" s="30"/>
       <c r="K96" s="30"/>
     </row>
-    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="30"/>
       <c r="B97" s="28"/>
       <c r="C97" s="39">
@@ -17854,7 +17838,7 @@
       <c r="J97" s="30"/>
       <c r="K97" s="30"/>
     </row>
-    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="30"/>
       <c r="B98" s="28"/>
       <c r="C98" s="36">
@@ -17875,7 +17859,7 @@
       <c r="J98" s="30"/>
       <c r="K98" s="30"/>
     </row>
-    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="30"/>
       <c r="B99" s="28"/>
       <c r="C99" s="39">
@@ -17896,7 +17880,7 @@
       <c r="J99" s="30"/>
       <c r="K99" s="30"/>
     </row>
-    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="30"/>
       <c r="B100" s="28"/>
       <c r="C100" s="36">
@@ -17917,7 +17901,7 @@
       <c r="J100" s="30"/>
       <c r="K100" s="30"/>
     </row>
-    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="30"/>
       <c r="B101" s="28"/>
       <c r="C101" s="39">
@@ -17938,7 +17922,7 @@
       <c r="J101" s="30"/>
       <c r="K101" s="30"/>
     </row>
-    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="30"/>
       <c r="B102" s="28"/>
       <c r="C102" s="36">
@@ -17959,7 +17943,7 @@
       <c r="J102" s="30"/>
       <c r="K102" s="30"/>
     </row>
-    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="30"/>
       <c r="B103" s="28"/>
       <c r="C103" s="39">
@@ -17980,7 +17964,7 @@
       <c r="J103" s="30"/>
       <c r="K103" s="30"/>
     </row>
-    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="30"/>
       <c r="B104" s="28"/>
       <c r="C104" s="36">
@@ -18001,7 +17985,7 @@
       <c r="J104" s="30"/>
       <c r="K104" s="30"/>
     </row>
-    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="30"/>
       <c r="B105" s="28"/>
       <c r="C105" s="39">
@@ -18022,7 +18006,7 @@
       <c r="J105" s="30"/>
       <c r="K105" s="30"/>
     </row>
-    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="30"/>
       <c r="B106" s="28"/>
       <c r="C106" s="36">
@@ -18043,7 +18027,7 @@
       <c r="J106" s="30"/>
       <c r="K106" s="30"/>
     </row>
-    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="30"/>
       <c r="B107" s="28"/>
       <c r="C107" s="39">
@@ -18064,7 +18048,7 @@
       <c r="J107" s="30"/>
       <c r="K107" s="30"/>
     </row>
-    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="30"/>
       <c r="B108" s="28"/>
       <c r="C108" s="36">
@@ -18085,7 +18069,7 @@
       <c r="J108" s="30"/>
       <c r="K108" s="30"/>
     </row>
-    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="30"/>
       <c r="B109" s="28"/>
       <c r="C109" s="39">
@@ -18106,7 +18090,7 @@
       <c r="J109" s="30"/>
       <c r="K109" s="30"/>
     </row>
-    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="30"/>
       <c r="B110" s="28"/>
       <c r="C110" s="36">
@@ -18127,7 +18111,7 @@
       <c r="J110" s="30"/>
       <c r="K110" s="30"/>
     </row>
-    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="30"/>
       <c r="B111" s="28"/>
       <c r="C111" s="39">
@@ -18148,7 +18132,7 @@
       <c r="J111" s="30"/>
       <c r="K111" s="30"/>
     </row>
-    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="30"/>
       <c r="B112" s="28"/>
       <c r="C112" s="36">
@@ -18169,7 +18153,7 @@
       <c r="J112" s="30"/>
       <c r="K112" s="30"/>
     </row>
-    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="30"/>
       <c r="B113" s="28"/>
       <c r="C113" s="39">
@@ -18190,7 +18174,7 @@
       <c r="J113" s="30"/>
       <c r="K113" s="30"/>
     </row>
-    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="30"/>
       <c r="B114" s="28"/>
       <c r="C114" s="36">
@@ -18211,7 +18195,7 @@
       <c r="J114" s="30"/>
       <c r="K114" s="30"/>
     </row>
-    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="30"/>
       <c r="B115" s="28"/>
       <c r="C115" s="39">
@@ -18232,7 +18216,7 @@
       <c r="J115" s="30"/>
       <c r="K115" s="30"/>
     </row>
-    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="30"/>
       <c r="B116" s="28"/>
       <c r="C116" s="36">
@@ -18253,7 +18237,7 @@
       <c r="J116" s="30"/>
       <c r="K116" s="30"/>
     </row>
-    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="30"/>
       <c r="B117" s="28"/>
       <c r="C117" s="39">
@@ -18274,7 +18258,7 @@
       <c r="J117" s="30"/>
       <c r="K117" s="30"/>
     </row>
-    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="30"/>
       <c r="B118" s="28"/>
       <c r="C118" s="36">
@@ -18295,7 +18279,7 @@
       <c r="J118" s="30"/>
       <c r="K118" s="30"/>
     </row>
-    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="30"/>
       <c r="B119" s="28"/>
       <c r="C119" s="39">
@@ -18316,7 +18300,7 @@
       <c r="J119" s="30"/>
       <c r="K119" s="30"/>
     </row>
-    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="30"/>
       <c r="B120" s="28"/>
       <c r="C120" s="36">
@@ -18337,7 +18321,7 @@
       <c r="J120" s="30"/>
       <c r="K120" s="30"/>
     </row>
-    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="30"/>
       <c r="B121" s="28"/>
       <c r="C121" s="39">
@@ -18358,7 +18342,7 @@
       <c r="J121" s="30"/>
       <c r="K121" s="30"/>
     </row>
-    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="30"/>
       <c r="B122" s="28"/>
       <c r="C122" s="36">
@@ -18379,7 +18363,7 @@
       <c r="J122" s="30"/>
       <c r="K122" s="30"/>
     </row>
-    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="30"/>
       <c r="B123" s="28"/>
       <c r="C123" s="39">
@@ -18400,7 +18384,7 @@
       <c r="J123" s="30"/>
       <c r="K123" s="30"/>
     </row>
-    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="30"/>
       <c r="B124" s="28"/>
       <c r="C124" s="36">
@@ -18421,7 +18405,7 @@
       <c r="J124" s="30"/>
       <c r="K124" s="30"/>
     </row>
-    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="30"/>
       <c r="B125" s="28"/>
       <c r="C125" s="39">
@@ -18442,7 +18426,7 @@
       <c r="J125" s="30"/>
       <c r="K125" s="30"/>
     </row>
-    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="30"/>
       <c r="B126" s="28"/>
       <c r="C126" s="36">
@@ -18463,7 +18447,7 @@
       <c r="J126" s="30"/>
       <c r="K126" s="30"/>
     </row>
-    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="30"/>
       <c r="B127" s="28"/>
       <c r="C127" s="39">
@@ -18484,7 +18468,7 @@
       <c r="J127" s="30"/>
       <c r="K127" s="30"/>
     </row>
-    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="30"/>
       <c r="B128" s="28"/>
       <c r="C128" s="36">
@@ -18505,7 +18489,7 @@
       <c r="J128" s="30"/>
       <c r="K128" s="30"/>
     </row>
-    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="30"/>
       <c r="B129" s="28"/>
       <c r="C129" s="39">
@@ -18526,7 +18510,7 @@
       <c r="J129" s="30"/>
       <c r="K129" s="30"/>
     </row>
-    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="30"/>
       <c r="B130" s="28"/>
       <c r="C130" s="36">
@@ -18547,7 +18531,7 @@
       <c r="J130" s="30"/>
       <c r="K130" s="30"/>
     </row>
-    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="30"/>
       <c r="B131" s="28"/>
       <c r="C131" s="39">
@@ -18568,7 +18552,7 @@
       <c r="J131" s="30"/>
       <c r="K131" s="30"/>
     </row>
-    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="30"/>
       <c r="B132" s="28"/>
       <c r="C132" s="36">
@@ -18589,7 +18573,7 @@
       <c r="J132" s="30"/>
       <c r="K132" s="30"/>
     </row>
-    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C133" s="39">
         <v>76</v>
       </c>
@@ -18603,7 +18587,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C134" s="36">
         <v>77</v>
       </c>
@@ -18617,7 +18601,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C135" s="3">
         <v>78</v>
       </c>
@@ -18631,7 +18615,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C136" s="36">
         <v>79</v>
       </c>
@@ -18645,7 +18629,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C137" s="3">
         <v>80</v>
       </c>
@@ -18659,7 +18643,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="138" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C138" s="36">
         <v>81</v>
       </c>
